--- a/Results/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication marine results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001965158088279968</v>
+        <v>0.001965158088279958</v>
       </c>
       <c r="C2" t="n">
         <v>0.001882299464714898</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002436254609911235</v>
+        <v>0.002436254609911233</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001922527732824529</v>
+        <v>0.001922527732824526</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00176287661408807</v>
+        <v>0.001762876614088069</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00208811398266538</v>
+        <v>0.002088113982665379</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002619118952497439</v>
+        <v>0.00261911895249744</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001731792481240243</v>
+        <v>0.001731792481240241</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002266345628208428</v>
+        <v>0.002266345628208429</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001918662506463394</v>
+        <v>0.001918662506463396</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003190219778389426</v>
+        <v>0.003190219778389428</v>
       </c>
     </row>
     <row r="3">
@@ -555,7 +555,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00213318913135173</v>
+        <v>0.00213318913135174</v>
       </c>
       <c r="C3" t="n">
         <v>0.002015150632650059</v>
@@ -567,25 +567,25 @@
         <v>0.002055520962909799</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00189586984417334</v>
+        <v>0.001895869844173341</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002274613880131762</v>
+        <v>0.00227461388013176</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002885614714441802</v>
+        <v>0.002885614714441803</v>
       </c>
       <c r="I3" t="n">
         <v>0.001864640897507633</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0024452507756825</v>
+        <v>0.002445250775682498</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002052579455640577</v>
+        <v>0.002052579455640571</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003542208862400056</v>
+        <v>0.003542208862400057</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001591217299454622</v>
+        <v>0.001004254226357975</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001395580847345201</v>
+        <v>0.0008555620181352514</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00187126421951146</v>
+        <v>0.001284301146414817</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001414705871993295</v>
+        <v>0.000858928141198734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001414705871993295</v>
+        <v>0.0008589281411987345</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001662137468415665</v>
+        <v>0.001076964041059431</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001979859155130284</v>
+        <v>0.001392896082033641</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00143861639860081</v>
+        <v>0.0008630906681908021</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001634252496641508</v>
+        <v>0.001047289423544866</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001456207858373994</v>
+        <v>0.0008692447852773497</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002319247446236225</v>
+        <v>0.00173228437313958</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02976004762650156</v>
+        <v>0.005961968337054251</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01587964818772311</v>
+        <v>0.003404757856228678</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05981627018723534</v>
+        <v>0.01148262214147353</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01587964833182947</v>
+        <v>0.003404758000335059</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01587964833182947</v>
+        <v>0.003404758000335059</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03908829044230722</v>
+        <v>0.007663966928771969</v>
       </c>
       <c r="H5" t="n">
-        <v>0.08007150559894606</v>
+        <v>0.01513702578167123</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01587959283951398</v>
+        <v>0.003404702508019527</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03696222392527234</v>
+        <v>0.007265012361292491</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0164876790519316</v>
+        <v>0.003514783701008337</v>
       </c>
       <c r="L5" t="n">
-        <v>0.124003325167785</v>
+        <v>0.007260504885285009</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003447222915721628</v>
+        <v>0.001169292996374263</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002338489644462041</v>
+        <v>0.001021513965528589</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00286923664962094</v>
+        <v>0.001459943265224399</v>
       </c>
       <c r="E6" t="n">
-        <v>0.002244960834588661</v>
+        <v>0.001005053013823727</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002374761286977052</v>
+        <v>0.001027897893320295</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003518143084682671</v>
+        <v>0.001403621027752399</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003892877496587164</v>
+        <v>0.001729587308305658</v>
       </c>
       <c r="I6" t="n">
-        <v>0.003294622014867814</v>
+        <v>0.001028129438207088</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002643674179615146</v>
+        <v>0.00122494763878557</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00236801884632388</v>
+        <v>0.001029723518286959</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003290194858524303</v>
+        <v>0.001903171116776317</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.002254197489275311</v>
+        <v>0.001120938739134154</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002101651936630654</v>
+        <v>0.0009798305291761284</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002534184399648271</v>
+        <v>0.001400975097486688</v>
       </c>
       <c r="E7" t="n">
-        <v>0.002100775445519631</v>
+        <v>0.0009796763854850816</v>
       </c>
       <c r="F7" t="n">
-        <v>0.002100775445519631</v>
+        <v>0.0009796763854850816</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002325117658236357</v>
+        <v>0.001193648553835607</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002642839344950975</v>
+        <v>0.001509580594809819</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002101596588421501</v>
+        <v>0.0009797751809669771</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002297232686462202</v>
+        <v>0.001163973936321043</v>
       </c>
       <c r="K7" t="n">
-        <v>0.002119188048194681</v>
+        <v>0.0009859292980535241</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002982227636056915</v>
+        <v>0.001848968885915756</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002827774038736245</v>
+        <v>0.001221888211292269</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003672978051844995</v>
+        <v>0.001256383923955319</v>
       </c>
       <c r="D8" t="n">
-        <v>0.004313145259131363</v>
+        <v>0.00171407220705916</v>
       </c>
       <c r="E8" t="n">
-        <v>0.003399992369666438</v>
+        <v>0.001208338562895889</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002706386574793043</v>
+        <v>0.001086263943659646</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003897011014687379</v>
+        <v>0.001470301783071913</v>
       </c>
       <c r="H8" t="n">
-        <v>0.004214732701402028</v>
+        <v>0.001786233824046124</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00367348994487252</v>
+        <v>0.001256428410203281</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003869322240622167</v>
+        <v>0.001440661696353934</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002674220350440796</v>
+        <v>0.001083614982719522</v>
       </c>
       <c r="L8" t="n">
-        <v>0.005596946375166031</v>
+        <v>0.002309159381505374</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.004400653174898126</v>
+        <v>0.001498714937756751</v>
       </c>
       <c r="C9" t="n">
-        <v>0.005117615994750017</v>
+        <v>0.00151064020052889</v>
       </c>
       <c r="D9" t="n">
-        <v>0.005550208746644717</v>
+        <v>0.001931795379681757</v>
       </c>
       <c r="E9" t="n">
-        <v>0.006121009283728826</v>
+        <v>0.001687237537175906</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005117615072600131</v>
+        <v>0.001510640156974167</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005341081716355727</v>
+        <v>0.001724458225188367</v>
       </c>
       <c r="H9" t="n">
-        <v>0.005658803403070345</v>
+        <v>0.002040390266162578</v>
       </c>
       <c r="I9" t="n">
-        <v>0.005117560646540879</v>
+        <v>0.00151058485231974</v>
       </c>
       <c r="J9" t="n">
-        <v>0.005313196744581564</v>
+        <v>0.001694783607673802</v>
       </c>
       <c r="K9" t="n">
-        <v>0.004040285786285552</v>
+        <v>0.001428070794965016</v>
       </c>
       <c r="L9" t="n">
-        <v>0.005998191694176288</v>
+        <v>0.002379778557268513</v>
       </c>
     </row>
   </sheetData>
@@ -911,7 +911,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001490192711251398</v>
+        <v>0.001490192711251397</v>
       </c>
       <c r="C2" t="n">
         <v>0.001672855341773082</v>
@@ -920,7 +920,7 @@
         <v>0.001539795388426546</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001698542885147367</v>
+        <v>0.001698542885147366</v>
       </c>
       <c r="F2" t="n">
         <v>0.001585588259067473</v>
@@ -935,10 +935,10 @@
         <v>0.001558633146106919</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001765781149476129</v>
+        <v>0.001765781149476128</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001712442107942769</v>
+        <v>0.001712442107942768</v>
       </c>
       <c r="L2" t="n">
         <v>0.00150250850291529</v>
@@ -954,7 +954,7 @@
         <v>0.001590721646794565</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001783547186966442</v>
+        <v>0.001783547186966441</v>
       </c>
       <c r="D3" t="n">
         <v>0.001647775000709608</v>
@@ -963,16 +963,16 @@
         <v>0.00180937510416077</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001696420478080877</v>
+        <v>0.001696420478080876</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001688941311194978</v>
+        <v>0.001688941311194977</v>
       </c>
       <c r="H3" t="n">
         <v>0.001639983902729756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001669496060238634</v>
+        <v>0.001669496060238633</v>
       </c>
       <c r="J3" t="n">
         <v>0.001884832036276117</v>
@@ -981,7 +981,7 @@
         <v>0.001819996938865391</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001604886342061263</v>
+        <v>0.001604886342061262</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001153955474745763</v>
+        <v>0.0006966513093931535</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001145910403814444</v>
+        <v>0.0007288347455321233</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001183442164482663</v>
+        <v>0.0007261379991300533</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00115983602533689</v>
+        <v>0.0007312858129851609</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001159836025336891</v>
+        <v>0.0007312858129851611</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001203016273189126</v>
+        <v>0.0007471143372480536</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001179330057083051</v>
+        <v>0.0007220258917304416</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001183729914159871</v>
+        <v>0.000735483520340774</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001227257679243178</v>
+        <v>0.0007699535138905687</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001181761055958086</v>
+        <v>0.0007244568906054769</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001161308273801091</v>
+        <v>0.0007040041084484814</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002956428781190066</v>
+        <v>0.001013886609608379</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006436466479325826</v>
+        <v>0.00165997260977666</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005454135255098801</v>
+        <v>0.001477779979005644</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006436466671168505</v>
+        <v>0.001659972801619339</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006436466671168505</v>
+        <v>0.001659972801619339</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007469589244591544</v>
+        <v>0.00185003117423862</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005677417637553272</v>
+        <v>0.001513689301603488</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00643645742717041</v>
+        <v>0.001659963557621235</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01008378309171777</v>
+        <v>0.002328701978039853</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005183676628862775</v>
+        <v>0.001428794027620178</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004898606373919368</v>
+        <v>0.001212919401791342</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00252305239392112</v>
+        <v>0.0009376123658623435</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001933644204402436</v>
+        <v>0.0008674758936843676</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001938264138272652</v>
+        <v>0.000969017081393014</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001854371691468016</v>
+        <v>0.0008535240895618781</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001942160669517583</v>
+        <v>0.0008689749496148797</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002572113192364482</v>
+        <v>0.0008806745694591476</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002583758483844235</v>
+        <v>0.0009692052935010425</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001942594874016708</v>
+        <v>0.0008690437525518674</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002609071091580191</v>
+        <v>0.001013152673144083</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001940822558856505</v>
+        <v>0.0008580517143916922</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001920203458362177</v>
+        <v>0.0008375696602074936</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001600749881140186</v>
+        <v>0.0007752871244924751</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001630533372709716</v>
+        <v>0.0008141283875955185</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001630186071572506</v>
+        <v>0.0008047649263518174</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001629839703809092</v>
+        <v>0.0008140064599480379</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001629839703809092</v>
+        <v>0.0008140064599480379</v>
       </c>
       <c r="G7" t="n">
-        <v>0.00164981067958355</v>
+        <v>0.0008257501523473755</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001626124463477474</v>
+        <v>0.0008006617068297635</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001630524320554295</v>
+        <v>0.0008141193354400958</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001674052085637601</v>
+        <v>0.0008485893289898903</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001628555462352507</v>
+        <v>0.0008030927057047988</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001608102680195512</v>
+        <v>0.000782639923547803</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001979529382753575</v>
+        <v>0.0008419523164151991</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002690921407890809</v>
+        <v>0.001000756680776125</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002832524061820873</v>
+        <v>0.001016376411488891</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002504416932163301</v>
+        <v>0.0009679320513043164</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002030550001933211</v>
+        <v>0.0008845314720357356</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0027106654253509</v>
+        <v>0.001012460586590718</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002686979209244794</v>
+        <v>0.0009873721410731014</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002691379066321644</v>
+        <v>0.001000829769683439</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002735040878650004</v>
+        <v>0.001035323355548235</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001994665066134037</v>
+        <v>0.0008675279956211984</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003381442052609173</v>
+        <v>0.001094747651401418</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002297195884321298</v>
+        <v>0.0008978616203881675</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002711707014597399</v>
+        <v>0.001004414947536662</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002711410534110011</v>
+        <v>0.0009950604307272812</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003155674951964121</v>
+        <v>0.001082553462168171</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00271170714044709</v>
+        <v>0.001004415127764574</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002730984321471228</v>
+        <v>0.001016036712288519</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002707298105365151</v>
+        <v>0.0009909482667709072</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002711697962441977</v>
+        <v>0.001004405895381239</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002755225727525282</v>
+        <v>0.001038875888931034</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002486816534588908</v>
+        <v>0.0009541466535999027</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002689276322083193</v>
+        <v>0.0009729264834889468</v>
       </c>
     </row>
   </sheetData>
@@ -1310,10 +1310,10 @@
         <v>0.001617191545522628</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001624422352944586</v>
+        <v>0.001624422352944587</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001800215756712902</v>
+        <v>0.001800215756712903</v>
       </c>
       <c r="E2" t="n">
         <v>0.001595929616741028</v>
@@ -1322,7 +1322,7 @@
         <v>0.001595929616741028</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00176157978893573</v>
+        <v>0.001761579788935728</v>
       </c>
       <c r="H2" t="n">
         <v>0.00203895412367625</v>
@@ -1337,7 +1337,7 @@
         <v>0.001732291575321202</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001876142676648458</v>
+        <v>0.001876142676648459</v>
       </c>
     </row>
     <row r="3">
@@ -1350,7 +1350,7 @@
         <v>0.001721987442610255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001737176115118066</v>
+        <v>0.001737176115118068</v>
       </c>
       <c r="D3" t="n">
         <v>0.001932503198830202</v>
@@ -1362,10 +1362,10 @@
         <v>0.001705014117908087</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001888063832469839</v>
+        <v>0.001888063832469838</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002207335289687631</v>
+        <v>0.00220733528968763</v>
       </c>
       <c r="I3" t="n">
         <v>0.001754709338920543</v>
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001207710882472904</v>
+        <v>0.0007428084159521828</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001160853360731684</v>
+        <v>0.0007609564817462417</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001316511020631824</v>
+        <v>0.0008516085541111023</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001194475014167418</v>
+        <v>0.0007544642571965637</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00119447501416742</v>
+        <v>0.0007544642571965637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001291377466350287</v>
+        <v>0.0008282598733038883</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001458377649026442</v>
+        <v>0.0009934751825057175</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001210652295599942</v>
+        <v>0.0007572926141965779</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001422582638780828</v>
+        <v>0.0009576801722601027</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001219866190174851</v>
+        <v>0.0007549637236541304</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001361641100311647</v>
+        <v>0.0008967386337909161</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006945587745952348</v>
+        <v>0.001752674738452496</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0102699523432716</v>
+        <v>0.002364157893986158</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01746480183221838</v>
+        <v>0.003693707721550134</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008623783373856421</v>
+        <v>0.002062022521416695</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008623783373856421</v>
+        <v>0.002062022521416695</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01566010068053078</v>
+        <v>0.0033571551452966</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03522708301064249</v>
+        <v>0.006936767293945805</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008623760504297379</v>
+        <v>0.002061999651857643</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02916244199481652</v>
+        <v>0.005839895392467594</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008123298308563507</v>
+        <v>0.001969967769906914</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02507723481417793</v>
+        <v>0.005070683104814434</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002699883736649793</v>
+        <v>0.0008832788790938815</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002016195836159825</v>
+        <v>0.0009114967566058753</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002124359293646302</v>
+        <v>0.0009937890808401006</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001909472017816948</v>
+        <v>0.0008803037291570069</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002007855417795424</v>
+        <v>0.0008976192074593928</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002783550320527168</v>
+        <v>0.001090882294215973</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003004556990148499</v>
+        <v>0.001265602745068647</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002702825149776823</v>
+        <v>0.001019915035108662</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002923973980976998</v>
+        <v>0.001221925047054791</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002002966467488822</v>
+        <v>0.0008927893717145603</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002163001243627755</v>
+        <v>0.001037778018250316</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001728015010763893</v>
+        <v>0.0008343819420351964</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001758980731097769</v>
+        <v>0.0008662268983602556</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001836766027158661</v>
+        <v>0.0009431734347636725</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001732348476931234</v>
+        <v>0.0008491299861300391</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001732348476931234</v>
+        <v>0.0008491299861300391</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001811681594641276</v>
+        <v>0.0009198333993869029</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001978681777317424</v>
+        <v>0.001085048708588731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001730956423890923</v>
+        <v>0.0008488661402795912</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001942886767071807</v>
+        <v>0.001049253698343117</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001740170318465837</v>
+        <v>0.000846537249737144</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001881945228602625</v>
+        <v>0.0009883121598739302</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002175062803094441</v>
+        <v>0.0009130623530590341</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003000267030049662</v>
+        <v>0.001084693285792964</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003240951829265449</v>
+        <v>0.001190310134595332</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002755293015570138</v>
+        <v>0.001029168223954927</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002204000996043312</v>
+        <v>0.0009321408290439609</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003051443781277093</v>
+        <v>0.001138031543052472</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003218443963954146</v>
+        <v>0.001303246852254464</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002970718610526729</v>
+        <v>0.001067064283945164</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003182804744668288</v>
+        <v>0.001267479261217618</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002172493033951613</v>
+        <v>0.0009226260472503432</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003949763885674058</v>
+        <v>0.001352248241546477</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002813139898332669</v>
+        <v>0.001025363921212444</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003365600608234355</v>
+        <v>0.001148991995204103</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003443435256531392</v>
+        <v>0.001225947217601034</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003939393016680085</v>
+        <v>0.001237569823021035</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003337598752400962</v>
+        <v>0.001131654033081824</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003418301471777865</v>
+        <v>0.001202598496230748</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003585301654454004</v>
+        <v>0.001367813805432577</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003337576301027508</v>
+        <v>0.001131631237123438</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003549506644208393</v>
+        <v>0.001332018795186963</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002690134857477754</v>
+        <v>0.001076122864805661</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003488565105739209</v>
+        <v>0.001271077256717776</v>
       </c>
     </row>
   </sheetData>
@@ -1718,7 +1718,7 @@
         <v>0.001546923216764795</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001662604271263258</v>
+        <v>0.001662604271263257</v>
       </c>
       <c r="H2" t="n">
         <v>0.001783750233240226</v>
@@ -1727,10 +1727,10 @@
         <v>0.001590201785409731</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001911276859462252</v>
+        <v>0.001911276859462251</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001670012306872453</v>
+        <v>0.001670012306872454</v>
       </c>
       <c r="L2" t="n">
         <v>0.00163069448533306</v>
@@ -1746,7 +1746,7 @@
         <v>0.001657810667741961</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001682663089327618</v>
+        <v>0.001682663089327617</v>
       </c>
       <c r="D3" t="n">
         <v>0.001833127541099064</v>
@@ -1764,13 +1764,13 @@
         <v>0.001916065071934505</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001693462970021779</v>
+        <v>0.001693462970021778</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002048466392587469</v>
+        <v>0.002048466392587468</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001769707993700482</v>
+        <v>0.001769707993700483</v>
       </c>
       <c r="L3" t="n">
         <v>0.001739791940525136</v>
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001151325603434502</v>
+        <v>0.0007071109476301037</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001120436752782861</v>
+        <v>0.0007303527325139781</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001241934023371076</v>
+        <v>0.0007977193675666789</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001211027115396976</v>
+        <v>0.00073277088567054</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001211027115396976</v>
+        <v>0.0007327708856705402</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001210737586446427</v>
+        <v>0.0007681119049705942</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001284664803816794</v>
+        <v>0.0008404501480123987</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00115721527271834</v>
+        <v>0.000723286249388649</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001304864290394642</v>
+        <v>0.0008606496345902495</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001156479190436081</v>
+        <v>0.0007122645346316782</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001193721811080796</v>
+        <v>0.0007495071552764042</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003889591142047765</v>
+        <v>0.001189045679814624</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007310042218639052</v>
+        <v>0.001819723288601799</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01226876045504093</v>
+        <v>0.002738440809024565</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005667028217612845</v>
+        <v>0.001517027075410957</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005667028217612845</v>
+        <v>0.001517027075410957</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009832801225136245</v>
+        <v>0.002285595097157355</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0182119887402409</v>
+        <v>0.003819659144679897</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005667011528266059</v>
+        <v>0.001517010386064166</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01895283953764934</v>
+        <v>0.00396669326127665</v>
       </c>
       <c r="K5" t="n">
-        <v>0.004430197253908153</v>
+        <v>0.001288438910680704</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008904158834271959</v>
+        <v>0.002106544064004801</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002555447894265181</v>
+        <v>0.0009542364694772312</v>
       </c>
       <c r="C6" t="n">
-        <v>0.00193285164259127</v>
+        <v>0.0008733377523454794</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002013105321486544</v>
+        <v>0.001046211041978334</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001838953313882234</v>
+        <v>0.0008432858960051085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001925235317651908</v>
+        <v>0.0008584715285862863</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001974108288705507</v>
+        <v>0.0009024651478401882</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002734980506560726</v>
+        <v>0.001095705710312202</v>
       </c>
       <c r="I6" t="n">
-        <v>0.00192058597497743</v>
+        <v>0.0008576394922582419</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002127437373396535</v>
+        <v>0.001005422496414116</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001911752930771674</v>
+        <v>0.0008451927122104595</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001954777907549712</v>
+        <v>0.0008834530275291332</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001633067858369033</v>
+        <v>0.0007918975840391573</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001666985270835431</v>
+        <v>0.0008265452711700011</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001723630152588206</v>
+        <v>0.0008824978858495135</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001647780245553623</v>
+        <v>0.0008096394361615895</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001647780245553623</v>
+        <v>0.0008096394361615895</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001692479841380956</v>
+        <v>0.0008528985413796474</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001766407058751334</v>
+        <v>0.0009252367844214523</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001638957527652876</v>
+        <v>0.0008080728857977019</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001786606545329181</v>
+        <v>0.0009454362709993015</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001638221445370614</v>
+        <v>0.0007970511710407313</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001675464066015336</v>
+        <v>0.0008342937916854577</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002044229683654242</v>
+        <v>0.0008642620648972405</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002822396932525759</v>
+        <v>0.001029897722526583</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003023009842614882</v>
+        <v>0.001111188710055022</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002592276320992003</v>
+        <v>0.000975870744538003</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002078735223965915</v>
+        <v>0.0008854875119511623</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002839275034646146</v>
+        <v>0.001054734494300654</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002913202252018359</v>
+        <v>0.001127072737342776</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002785752720918074</v>
+        <v>0.001009908838718707</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002933546311434739</v>
+        <v>0.001147297668740074</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002035718503186303</v>
+        <v>0.0008670106528372088</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003590689824622787</v>
+        <v>0.001171373523373868</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002445481763023249</v>
+        <v>0.000934882430483521</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002910554234403377</v>
+        <v>0.001045413407572</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002967245522798794</v>
+        <v>0.001101374189820571</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003380086980659144</v>
+        <v>0.001114525419888104</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002882542980660676</v>
+        <v>0.001026957676362869</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002936048804948901</v>
+        <v>0.001071766677781645</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003009976022319272</v>
+        <v>0.001144104920823452</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002882526491220823</v>
+        <v>0.0010269410221997</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003030175508897121</v>
+        <v>0.001164304407401299</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002631977592684202</v>
+        <v>0.0009719522520202023</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002919033029583276</v>
+        <v>0.001053161928087454</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001509386368156187</v>
+        <v>0.001509386368156186</v>
       </c>
       <c r="C2" t="n">
         <v>0.001540398679815981</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001615941892640544</v>
+        <v>0.001615941892640543</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00148784128915378</v>
+        <v>0.001487841289153779</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00148784128915378</v>
+        <v>0.001487841289153779</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001575531489253624</v>
+        <v>0.001575531489253625</v>
       </c>
       <c r="H2" t="n">
         <v>0.001621334475864535</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001516941847401349</v>
+        <v>0.001516941847401348</v>
       </c>
       <c r="J2" t="n">
         <v>0.001691086542761538</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001632132760658256</v>
+        <v>0.001632132760658254</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001531735233372031</v>
+        <v>0.00153173523337203</v>
       </c>
     </row>
     <row r="3">
@@ -2139,13 +2139,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001611231086021554</v>
+        <v>0.001611231086021553</v>
       </c>
       <c r="C3" t="n">
         <v>0.001650778993604956</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001733792012088966</v>
+        <v>0.001733792012088964</v>
       </c>
       <c r="E3" t="n">
         <v>0.001590843872856487</v>
@@ -2160,16 +2160,16 @@
         <v>0.001740212981015543</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001620212465867153</v>
+        <v>0.001620212465867151</v>
       </c>
       <c r="J3" t="n">
         <v>0.001811272366923898</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001734932686343598</v>
+        <v>0.001734932686343599</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001636934025146604</v>
+        <v>0.001636934025146603</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00111327815599655</v>
+        <v>0.0006836141607568969</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001089264250716391</v>
+        <v>0.0007076534405288514</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001176620900161919</v>
+        <v>0.0007469569049222659</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001156899849291803</v>
+        <v>0.0006950674375885695</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001156899849291802</v>
+        <v>0.0006950674375885695</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001150817134673801</v>
+        <v>0.0007226210896749653</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00117982630842517</v>
+        <v>0.0007501623131855148</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001106336938050525</v>
+        <v>0.0006861563371098329</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001185864651115192</v>
+        <v>0.0007562006558755382</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001117058472551022</v>
+        <v>0.0006873944773113688</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001126588336702385</v>
+        <v>0.0006969243414627317</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002232450143485652</v>
+        <v>0.0008805884294876514</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005611679215625942</v>
+        <v>0.001503598470040024</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008156062165316294</v>
+        <v>0.001975338560933318</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002763050692539993</v>
+        <v>0.0009777499844685032</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002763050692539993</v>
+        <v>0.0009777499844685032</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006094096759112666</v>
+        <v>0.00159263829886193</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009443595246982512</v>
+        <v>0.002204585638490659</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00276303609527247</v>
+        <v>0.0009777353872009319</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009430260300991993</v>
+        <v>0.002207214282391385</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002689741701824607</v>
+        <v>0.0009641867241636928</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003963138634442811</v>
+        <v>0.001196157191159903</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00249379685738233</v>
+        <v>0.0008167373051211132</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001891597164221279</v>
+        <v>0.0008488640325405371</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001935389023842085</v>
+        <v>0.0008805000939663293</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001781072813550925</v>
+        <v>0.000804921878702918</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001866720576151283</v>
+        <v>0.0008199958848388995</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001907198640841745</v>
+        <v>0.0009655923798022985</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002601022249249537</v>
+        <v>0.001000292797415246</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001862718444218469</v>
+        <v>0.000929127627237165</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001998380391153812</v>
+        <v>0.001000153363680227</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001870143099975019</v>
+        <v>0.0008199373710197941</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001878933515086955</v>
+        <v>0.0008293370921409259</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001576877164704146</v>
+        <v>0.0007652075858473108</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001610407318888814</v>
+        <v>0.0007993746200301969</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001640173444650309</v>
+        <v>0.0008285421523101442</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001580393901534344</v>
+        <v>0.000769602390379381</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001580393901534344</v>
+        <v>0.000769602390379381</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001614416143381397</v>
+        <v>0.0008042145147653806</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001643425317132764</v>
+        <v>0.0008317557382759289</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001569935946758123</v>
+        <v>0.0007677497622002469</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001649463659822785</v>
+        <v>0.0008377940809659523</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001580657481258618</v>
+        <v>0.000768987902401783</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001590187345409984</v>
+        <v>0.0007785177665531463</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001973463632973414</v>
+        <v>0.0008350068038844876</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00272883839362261</v>
+        <v>0.0009962184881157324</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00289603941656686</v>
+        <v>0.00104957456216977</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002492659475723504</v>
+        <v>0.0009301611305666694</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001995353373078217</v>
+        <v>0.0008426352569753665</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002722667334702731</v>
+        <v>0.0009992667233810232</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002751676508455893</v>
+        <v>0.001026807946891889</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002678187138079459</v>
+        <v>0.0009628019708158913</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002757854713444367</v>
+        <v>0.001032870905346307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001964024411944486</v>
+        <v>0.0008364604818368892</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003441831848207023</v>
+        <v>0.00110440719727956</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002215231066984814</v>
+        <v>0.0008775578720399273</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002625377556599531</v>
+        <v>0.0009780093808993313</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002655190424687184</v>
+        <v>0.001007185139828639</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003019528151820312</v>
+        <v>0.001022890017057246</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002584920664255469</v>
+        <v>0.0009463990996603076</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002629386381092115</v>
+        <v>0.0009828492756345142</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002658395554843482</v>
+        <v>0.001010390499145064</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002584906184468834</v>
+        <v>0.0009463845230693821</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002664433897533508</v>
+        <v>0.001016428841835087</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002368561669169535</v>
+        <v>0.0008641586652304996</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002605157583120696</v>
+        <v>0.0009571525274222809</v>
       </c>
     </row>
   </sheetData>
@@ -2495,7 +2495,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001541534369961889</v>
+        <v>0.001541534369961888</v>
       </c>
       <c r="C2" t="n">
         <v>0.001485299617695341</v>
@@ -2504,25 +2504,25 @@
         <v>0.001663796036425617</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001535596792780808</v>
+        <v>0.001535596792780807</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001535596792780808</v>
+        <v>0.001535596792780807</v>
       </c>
       <c r="G2" t="n">
         <v>0.001666526974569658</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001918939474355036</v>
+        <v>0.001918939474355035</v>
       </c>
       <c r="I2" t="n">
         <v>0.001580309815146055</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002034000655356313</v>
+        <v>0.002034000655356312</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001694580471999912</v>
+        <v>0.00169458047199991</v>
       </c>
       <c r="L2" t="n">
         <v>0.001845204354413269</v>
@@ -2544,10 +2544,10 @@
         <v>0.001776381369867538</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001635664457336111</v>
+        <v>0.001635664457336112</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001635664457336111</v>
+        <v>0.001635664457336112</v>
       </c>
       <c r="G3" t="n">
         <v>0.001779522514445316</v>
@@ -2562,7 +2562,7 @@
         <v>0.002188772091817945</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001796428471512687</v>
+        <v>0.001796428471512686</v>
       </c>
       <c r="L3" t="n">
         <v>0.001985025254231036</v>
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001145197866137749</v>
+        <v>0.000696484552240747</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001053451844942871</v>
+        <v>0.0006750301571116856</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001217877246184165</v>
+        <v>0.0007691639322871624</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00118142288177871</v>
+        <v>0.000721927215042647</v>
       </c>
       <c r="F4" t="n">
-        <v>0.00118142288177871</v>
+        <v>0.000721927215042647</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001217452876836611</v>
+        <v>0.0007704269471376858</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001369501617649134</v>
+        <v>0.0009207883037521312</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001155037739690553</v>
+        <v>0.0007172680954166978</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001384832352998905</v>
+        <v>0.000936119039101901</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001175383329829569</v>
+        <v>0.000726670015932566</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001325693273623771</v>
+        <v>0.0008769799597267685</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002896005693023853</v>
+        <v>0.001004626728103001</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002400408900315435</v>
+        <v>0.0009120945975726986</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01003599339554009</v>
+        <v>0.002321152366164199</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005262500155102394</v>
+        <v>0.001440196811255598</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005262500155102394</v>
+        <v>0.001440196811255598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01046546125039896</v>
+        <v>0.002398076412065068</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02788853303661882</v>
+        <v>0.005588137808200288</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005262481545098046</v>
+        <v>0.001440178201251254</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02755799557437638</v>
+        <v>0.005542595741103659</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005936237830664154</v>
+        <v>0.001564580403539144</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02352101789494395</v>
+        <v>0.004783357071912022</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002598176763956453</v>
+        <v>0.0008338502805622346</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001890491736552436</v>
+        <v>0.0008223491772367044</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002001051464060681</v>
+        <v>0.0009070025938865399</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001844959091427785</v>
+        <v>0.0008387095873080888</v>
       </c>
       <c r="F6" t="n">
-        <v>0.00193756499899446</v>
+        <v>0.0008550082269515057</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001997939973801489</v>
+        <v>0.0009077926754591744</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002873644245911567</v>
+        <v>0.001185517404891857</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002608016637509254</v>
+        <v>0.0008546338237381862</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002848383865424645</v>
+        <v>0.001193704103893081</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001944796262105661</v>
+        <v>0.0008620866912793891</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002110038140485514</v>
+        <v>0.001015024655546426</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001656345535697761</v>
+        <v>0.0007864465415958402</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001648885264021853</v>
+        <v>0.0007798264383017364</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001728977238805576</v>
+        <v>0.000859117530501107</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001679200231562564</v>
+        <v>0.0008095360281298879</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001679200231562564</v>
+        <v>0.0008095360281298879</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001728600546396621</v>
+        <v>0.0008603889364927794</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001880649287209145</v>
+        <v>0.001010750293107224</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001666185409250563</v>
+        <v>0.0008072300847717916</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001895980022558916</v>
+        <v>0.001026081028456995</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00168653099938958</v>
+        <v>0.000816632005287659</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001836840943183783</v>
+        <v>0.0009669419490818617</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002090616415998815</v>
+        <v>0.0008628782161146728</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002874708792600786</v>
+        <v>0.0009955713781625928</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003103733286225209</v>
+        <v>0.001101074593535892</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002677655931052883</v>
+        <v>0.0009852642302879823</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00213294686207709</v>
+        <v>0.0008893954346677174</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002941794204668953</v>
+        <v>0.001073911019191717</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003093842945481072</v>
+        <v>0.001224272375806092</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002879379067522894</v>
+        <v>0.00102075216747073</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003109326761264967</v>
+        <v>0.001239630053312123</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002106332989208057</v>
+        <v>0.0008905171550953569</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003863684575317678</v>
+        <v>0.001323666426404479</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002629429286597956</v>
+        <v>0.00095770928082627</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003110009145516489</v>
+        <v>0.001036984240051356</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003190149011344825</v>
+        <v>0.001116283761074533</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003690515665812666</v>
+        <v>0.001163527542639766</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003127327587893373</v>
+        <v>0.001064406441463069</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003189724427891256</v>
+        <v>0.001117546738242399</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003341773168703783</v>
+        <v>0.001267908094856843</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0031273092907452</v>
+        <v>0.001064387886521411</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003357103904053551</v>
+        <v>0.001283238830206614</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002533125186119935</v>
+        <v>0.0009656325813448261</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003297964824678418</v>
+        <v>0.001224099750831483</v>
       </c>
     </row>
   </sheetData>
@@ -2894,10 +2894,10 @@
         <v>0.001511859679359501</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001476674776609511</v>
+        <v>0.00147667477660951</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001522279071660817</v>
+        <v>0.001522279071660818</v>
       </c>
       <c r="E2" t="n">
         <v>0.001508429143775071</v>
@@ -2906,10 +2906,10 @@
         <v>0.001508429143775071</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00153164939624341</v>
+        <v>0.001531649396243409</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001539832324635502</v>
+        <v>0.001539832324635501</v>
       </c>
       <c r="I2" t="n">
         <v>0.001542026654739009</v>
@@ -2921,7 +2921,7 @@
         <v>0.001629637972012708</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001550877685155772</v>
+        <v>0.001550877685155771</v>
       </c>
     </row>
     <row r="3">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001604286065553183</v>
+        <v>0.001604286065553182</v>
       </c>
       <c r="C3" t="n">
         <v>0.001568943973507749</v>
@@ -2949,13 +2949,13 @@
         <v>0.001627048339397181</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00163668479687387</v>
+        <v>0.001636684796873869</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001639454257161998</v>
+        <v>0.001639454257161999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001860266051910874</v>
+        <v>0.001860266051910873</v>
       </c>
       <c r="K3" t="n">
         <v>0.001722874727525549</v>
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00110730346259131</v>
+        <v>0.0006803359845698502</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001039634092402827</v>
+        <v>0.0006683488434830096</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001113497349807338</v>
+        <v>0.0006865298717858792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001195821239615601</v>
+        <v>0.0007107744551970254</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001195821239615602</v>
+        <v>0.0007107744551970254</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001117347637909956</v>
+        <v>0.0006917974174834343</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001123940508475855</v>
+        <v>0.0006969730304543958</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0011141641162492</v>
+        <v>0.000696398538662093</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001186946864103885</v>
+        <v>0.0007599793860824258</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001110510568404718</v>
+        <v>0.0006835430903832594</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001130506252400023</v>
+        <v>0.0007035387743785638</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002015708078055775</v>
+        <v>0.0008402151960252735</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002142931815947115</v>
+        <v>0.0008625292417746179</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00269053126276953</v>
+        <v>0.0009640878389632488</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003796136727193307</v>
+        <v>0.001168429978530846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003796136727193307</v>
+        <v>0.001168429978530846</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003266001976092524</v>
+        <v>0.001069960578954451</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004007960722212918</v>
+        <v>0.001204560585321703</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003796131553770594</v>
+        <v>0.00116842480510813</v>
       </c>
       <c r="J5" t="n">
-        <v>0.009888163268556998</v>
+        <v>0.002291393464968044</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002422184199718789</v>
+        <v>0.0009143976482436264</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004767030211800996</v>
+        <v>0.001343566987765076</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00185296203135947</v>
+        <v>0.0008115718919619306</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001835775348040682</v>
+        <v>0.0008084697037160128</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002478092060853474</v>
+        <v>0.000817282303102742</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001788781137909784</v>
+        <v>0.0008151353967313108</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001866663083622612</v>
+        <v>0.0008288426191024943</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001863006206678116</v>
+        <v>0.0009310902348593727</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00252098330255259</v>
+        <v>0.0009428525608795766</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001859822685017362</v>
+        <v>0.0009356913560380311</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001987993987981598</v>
+        <v>0.0009009636791209655</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001853422174832172</v>
+        <v>0.0008142955324059952</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001873072006594989</v>
+        <v>0.0008342303464087111</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001566767437767442</v>
+        <v>0.0007612016437626699</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001565961716541275</v>
+        <v>0.0007609825048294308</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001572916134669359</v>
+        <v>0.0007673875774834581</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001589622893910102</v>
+        <v>0.0007800835459772982</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001589622893910102</v>
+        <v>0.0007800835459772982</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001576811613086089</v>
+        <v>0.0007726630766762538</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001583404483651988</v>
+        <v>0.0007778386896472154</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001573628091425333</v>
+        <v>0.0007772641978549123</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001646410839280018</v>
+        <v>0.0008408450452752453</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001569974543580851</v>
+        <v>0.0007644087495760787</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001589970227576156</v>
+        <v>0.0007844044335713835</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001957090958843223</v>
+        <v>0.0008298985830997663</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002676880350134564</v>
+        <v>0.0009565041832823949</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002814616754104395</v>
+        <v>0.0009859268853198465</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002490063435348042</v>
+        <v>0.0009385610804116493</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00199587356728641</v>
+        <v>0.0008515836641040984</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002672255699556577</v>
+        <v>0.0009654612348503639</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00267884857012282</v>
+        <v>0.0009706368478213853</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002669072177895823</v>
+        <v>0.0009700623560290221</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002741993501896098</v>
+        <v>0.001033667592850847</v>
       </c>
       <c r="K8" t="n">
-        <v>0.00194720008816649</v>
+        <v>0.0008308004450634012</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003421971705596223</v>
+        <v>0.001106836691955783</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002264458865676514</v>
+        <v>0.0008839953344092975</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002655563252233592</v>
+        <v>0.0009527523740721544</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002662563142319204</v>
+        <v>0.0009591654497906629</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003115490991255574</v>
+        <v>0.001048636329654921</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002663234785794775</v>
+        <v>0.0009690392379251258</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002666413148778407</v>
+        <v>0.0009644329459189778</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002673006019344307</v>
+        <v>0.0009696085588899396</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00266322962711765</v>
+        <v>0.0009690340670976362</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002736012374972337</v>
+        <v>0.001032614914517969</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002432501942132693</v>
+        <v>0.0008693252849148683</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002679571763268472</v>
+        <v>0.0009761743028141071</v>
       </c>
     </row>
   </sheetData>
@@ -3296,10 +3296,10 @@
         <v>0.00149543373430603</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001485492217682603</v>
+        <v>0.001485492217682602</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001485492217682603</v>
+        <v>0.001485492217682602</v>
       </c>
       <c r="G2" t="n">
         <v>0.001494105437576195</v>
@@ -3314,7 +3314,7 @@
         <v>0.001584984271364612</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001615439528323431</v>
+        <v>0.00161543952832343</v>
       </c>
       <c r="L2" t="n">
         <v>0.001491145823430079</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00109432711159549</v>
+        <v>0.0006755108416758825</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001036383265457682</v>
+        <v>0.000666145704620068</v>
       </c>
       <c r="D4" t="n">
-        <v>0.00109962877416597</v>
+        <v>0.0006808125042463619</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001153727085729494</v>
+        <v>0.0006933507670463458</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001153727085729494</v>
+        <v>0.0006933507670463461</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001097208510122624</v>
+        <v>0.0006797358940924385</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001101623919971631</v>
+        <v>0.000682807650052023</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001092735706110254</v>
+        <v>0.0006826117741108868</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001110741672094587</v>
+        <v>0.0006919254021749803</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001094113826628609</v>
+        <v>0.0006752975567090009</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001097092330177154</v>
+        <v>0.0006782760602575471</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001858725988038424</v>
+        <v>0.0008100450432008508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002091555275781307</v>
+        <v>0.0008518559774307533</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002456628916634557</v>
+        <v>0.0009196445280266965</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002801378555291308</v>
+        <v>0.0009833374241179004</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002801378555291308</v>
+        <v>0.0009833374241179004</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002423421830010938</v>
+        <v>0.0009131494371280025</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00286488333527289</v>
+        <v>0.0009931413054634689</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002801373081771124</v>
+        <v>0.000983331950597716</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003611602945237667</v>
+        <v>0.001132076983863157</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001954038010601221</v>
+        <v>0.0008266442122680926</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002423255505918492</v>
+        <v>0.0009116807779232941</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002448856848001949</v>
+        <v>0.0009139080739916388</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001828602146633934</v>
+        <v>0.0008055762269515686</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001842178875776825</v>
+        <v>0.0008115013214217213</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001765362685982679</v>
+        <v>0.0008009986321076048</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001845239001231464</v>
+        <v>0.0008150568635152157</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002451738246529082</v>
+        <v>0.0009181331264081917</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00249079123349649</v>
+        <v>0.0009273010959075849</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001840063151512208</v>
+        <v>0.0008141414037889245</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002468929214181863</v>
+        <v>0.0009309664082870722</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001841749698131011</v>
+        <v>0.0008068814693804371</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001840005070147143</v>
+        <v>0.0008090287017837678</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001540109868315248</v>
+        <v>0.0007539686064334285</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001540428506466082</v>
+        <v>0.0007548576665568513</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001545365422106352</v>
+        <v>0.0007592621538587815</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001551376890936227</v>
+        <v>0.0007633371323835026</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001551376890936227</v>
+        <v>0.0007633371323835026</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001542991266842381</v>
+        <v>0.0007581936588499812</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001547406676691388</v>
+        <v>0.0007612654148095686</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001538518462830013</v>
+        <v>0.0007610695388684339</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001556524428814346</v>
+        <v>0.0007703831669325261</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001539896583348367</v>
+        <v>0.0007537553214665466</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001542875086896912</v>
+        <v>0.0007567338250150925</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00192146763733268</v>
+        <v>0.0008210875734168048</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002621572349587649</v>
+        <v>0.0009451389819151877</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002756595418064104</v>
+        <v>0.0009724386319922266</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002430364062307676</v>
+        <v>0.0009180388737066104</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001949363233815128</v>
+        <v>0.0008333827283506406</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002611657306683749</v>
+        <v>0.0009462788808429022</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002616072716533764</v>
+        <v>0.0009493506368026675</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002607184502671379</v>
+        <v>0.0009491547608613553</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002625325544196395</v>
+        <v>0.0009584921622204776</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001908487248389662</v>
+        <v>0.0008186272781622991</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003329492087189598</v>
+        <v>0.001071178415362754</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002124959136118294</v>
+        <v>0.0008569020770090084</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00248070748912164</v>
+        <v>0.0009203467666075086</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00248569077554565</v>
+        <v>0.0009247594151673335</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002888961490542471</v>
+        <v>0.0009987520206385819</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002478802903066226</v>
+        <v>0.0009265641096339204</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002483270249497936</v>
+        <v>0.0009236827589006387</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002487685659346942</v>
+        <v>0.0009267545148602264</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002478797445485566</v>
+        <v>0.0009265586389190915</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0024968034114699</v>
+        <v>0.0009358722669831835</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002274238303536966</v>
+        <v>0.000881528957918231</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002483154069552465</v>
+        <v>0.00092222292506575</v>
       </c>
     </row>
   </sheetData>
@@ -3683,7 +3683,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001526955170351368</v>
+        <v>0.001526955170351366</v>
       </c>
       <c r="C2" t="n">
         <v>0.001479775951347989</v>
@@ -3692,28 +3692,28 @@
         <v>0.001549127004071958</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001525914204487412</v>
+        <v>0.00152591420448741</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001525914204487412</v>
+        <v>0.00152591420448741</v>
       </c>
       <c r="G2" t="n">
         <v>0.001576908368541464</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001841253243392558</v>
+        <v>0.001841253243392557</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001564082618346278</v>
+        <v>0.001564082618346277</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00168940465252381</v>
+        <v>0.001689404652523809</v>
       </c>
       <c r="K2" t="n">
         <v>0.001649683112908661</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001771858391866566</v>
+        <v>0.001771858391866564</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001619773705800259</v>
+        <v>0.001619773705800256</v>
       </c>
       <c r="C3" t="n">
         <v>0.001571227668222211</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001645275907460456</v>
+        <v>0.001645275907460455</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001624334004374865</v>
+        <v>0.001624334004374866</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001624334004374865</v>
+        <v>0.001624334004374863</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001677230231492702</v>
+        <v>0.001677230231492699</v>
       </c>
       <c r="H3" t="n">
         <v>0.001981509007728101</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001662898228499144</v>
+        <v>0.001662898228499142</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001792744662470944</v>
+        <v>0.001792744662470943</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001744793239331615</v>
+        <v>0.001744793239331613</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001901447677753576</v>
+        <v>0.001901447677753575</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001132704048056163</v>
+        <v>0.000689899048335265</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001043956056694687</v>
+        <v>0.000670276884035017</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001145884263702764</v>
+        <v>0.0007030792639818644</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001178332689530516</v>
+        <v>0.0007161956948354449</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001178332689530516</v>
+        <v>0.0007161956948354449</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001160507302572656</v>
+        <v>0.0007192611502649907</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001319490324809753</v>
+        <v>0.0008766853250888531</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001142570436439512</v>
+        <v>0.0007098944815853273</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001174343682271297</v>
+        <v>0.0007315386825503994</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001141773215115067</v>
+        <v>0.0006989682153941662</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001278258018830144</v>
+        <v>0.000835453019109249</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002584988204363078</v>
+        <v>0.0009455010584602747</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002244676703244132</v>
+        <v>0.0008816037166826233</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003960935881076807</v>
+        <v>0.00119852834595505</v>
       </c>
       <c r="E5" t="n">
-        <v>0.004859526185459066</v>
+        <v>0.001364085746608262</v>
       </c>
       <c r="F5" t="n">
-        <v>0.004859526185459066</v>
+        <v>0.001364085746608262</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005696015389582114</v>
+        <v>0.001517510569253254</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02342347103561988</v>
+        <v>0.004766985909111452</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00485951762145398</v>
+        <v>0.001364077182603154</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00702455234573485</v>
+        <v>0.001761175401740791</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003573182029088119</v>
+        <v>0.001126896164334649</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01925533736464395</v>
+        <v>0.003999418966828196</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002557761104214538</v>
+        <v>0.0008244446217777463</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001869909333003735</v>
+        <v>0.0008156446598777195</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001906930132796568</v>
+        <v>0.0008370233362165729</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001824366813297066</v>
+        <v>0.0008298977000022521</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001910074355665989</v>
+        <v>0.0008449822273774445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002585564358731028</v>
+        <v>0.0009700711907898215</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002792045900787262</v>
+        <v>0.001135855105056554</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001907033926050479</v>
+        <v>0.000960704522110162</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002607677916280726</v>
+        <v>0.0009838055063691202</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001896298212723504</v>
+        <v>0.0008317646142536774</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002045317744241599</v>
+        <v>0.0009704555300501377</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001627266842092683</v>
+        <v>0.0007769420996140379</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001621601860441392</v>
+        <v>0.0007719425449435512</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001640399913691064</v>
+        <v>0.0007901140179081957</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001652095458806994</v>
+        <v>0.0007995779417762889</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001652095458806994</v>
+        <v>0.0007995779417762889</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001655070096609177</v>
+        <v>0.0008063042015437651</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001814053118846272</v>
+        <v>0.0009637283763676288</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001637133230476033</v>
+        <v>0.0007969375328641026</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001668906476307816</v>
+        <v>0.0008185817338291708</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001636336009151585</v>
+        <v>0.0007860112666729426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001772820812866666</v>
+        <v>0.0009224960703880214</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002049216345690087</v>
+        <v>0.0008512052118447769</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002816721151061198</v>
+        <v>0.000982283538952881</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002978386739186644</v>
+        <v>0.001025599697919416</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002623230683283251</v>
+        <v>0.000970497740357964</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002092088807640407</v>
+        <v>0.0008770167707513603</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002835693750671617</v>
+        <v>0.001014093963532826</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002994676772907886</v>
+        <v>0.00117151813835654</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002817756884538472</v>
+        <v>0.001004727294853162</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00284967923133581</v>
+        <v>0.001026397737588027</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002044192750921315</v>
+        <v>0.0008577940528354486</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003745943056165869</v>
+        <v>0.001269765583326968</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002511389487291568</v>
+        <v>0.0009325476843258802</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00296375634337</v>
+        <v>0.001008161732659006</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002982601654350112</v>
+        <v>0.001026341522984169</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003507855074287043</v>
+        <v>0.001126191632330987</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002979296009579545</v>
+        <v>0.001033165237446541</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002997224579537786</v>
+        <v>0.001042523389259222</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003156207601774877</v>
+        <v>0.001199947564083084</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002979287713404649</v>
+        <v>0.001033156720579558</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003011060959236419</v>
+        <v>0.001054800921544628</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002702338068851392</v>
+        <v>0.0009755226246295161</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003114975295795273</v>
+        <v>0.001158715258103478</v>
       </c>
     </row>
   </sheetData>
@@ -4085,7 +4085,7 @@
         <v>0.001477783540857383</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001496808983684855</v>
+        <v>0.001496808983684854</v>
       </c>
       <c r="E2" t="n">
         <v>0.001506375252574483</v>
@@ -4094,19 +4094,19 @@
         <v>0.001506375252574483</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001497465373609844</v>
+        <v>0.001497465373609843</v>
       </c>
       <c r="H2" t="n">
         <v>0.001500951123275851</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001515708575495113</v>
+        <v>0.001515708575495115</v>
       </c>
       <c r="J2" t="n">
         <v>0.001647760227405584</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001631464675337149</v>
+        <v>0.00163146467533715</v>
       </c>
       <c r="L2" t="n">
         <v>0.001492800494595543</v>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001582300161011088</v>
+        <v>0.001582300161011089</v>
       </c>
       <c r="C3" t="n">
         <v>0.001569946614311116</v>
@@ -4128,10 +4128,10 @@
         <v>0.001590276237473945</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001602707154329811</v>
+        <v>0.001602707154329809</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001602707154329811</v>
+        <v>0.001602707154329809</v>
       </c>
       <c r="G3" t="n">
         <v>0.001591031221858446</v>
@@ -4140,16 +4140,16 @@
         <v>0.001595263469293756</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001612572519047105</v>
+        <v>0.001612572519047104</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001745031828860808</v>
+        <v>0.001745031828860807</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001724595637330897</v>
+        <v>0.001724595637330896</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001585659706228188</v>
+        <v>0.001585659706228187</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001109415777337761</v>
+        <v>0.0006814487451174026</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001040025173384627</v>
+        <v>0.0006688168804272515</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001113538025651649</v>
+        <v>0.0006855709934312922</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001207585578835995</v>
+        <v>0.0007114651241014372</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001207585578835996</v>
+        <v>0.0007114651241014372</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001112244351566477</v>
+        <v>0.0006856648282952754</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001116009982643998</v>
+        <v>0.0006880429504236416</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001113930043617389</v>
+        <v>0.0006949782676048908</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001128594056559809</v>
+        <v>0.0007006270243394503</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001112207122140925</v>
+        <v>0.0006842400899205705</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001111168564359973</v>
+        <v>0.0006832015321396147</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.002114743431912563</v>
+        <v>0.0008583864113638122</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00220225942479682</v>
+        <v>0.0008733701075674047</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002595383062581561</v>
+        <v>0.0009463757185177593</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003653634383318412</v>
+        <v>0.001141969711357605</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003653634383318412</v>
+        <v>0.001141969711357605</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002677806672096373</v>
+        <v>0.0009612037952155005</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003070761832199338</v>
+        <v>0.001032079274081183</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003653630157120125</v>
+        <v>0.001141965485159323</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004138803765283795</v>
+        <v>0.001230423930204111</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002479445605538979</v>
+        <v>0.0009248740616947255</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002600239742986484</v>
+        <v>0.0009452780581577911</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002470246372371248</v>
+        <v>0.0008125698022338824</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001837316519363339</v>
+        <v>0.0008091401565591486</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00185593389058304</v>
+        <v>0.0008162318535318864</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001789920857836812</v>
+        <v>0.0008139561326502226</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001866480479504603</v>
+        <v>0.0008274306259907406</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001857250361947009</v>
+        <v>0.000816785885411755</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002513135699566005</v>
+        <v>0.0009339370752695117</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001858936053997916</v>
+        <v>0.000934484451032995</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001927040947704312</v>
+        <v>0.0009409786952007788</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001855370589098351</v>
+        <v>0.0008150368593963413</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001852316021638869</v>
+        <v>0.000813643483913888</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001567601107304196</v>
+        <v>0.0007620893627545359</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001566423117149567</v>
+        <v>0.0007614629180278686</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001571678578680586</v>
+        <v>0.0007662037303274687</v>
       </c>
       <c r="E7" t="n">
-        <v>0.00159146738970492</v>
+        <v>0.0007790283224482699</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00159146738970492</v>
+        <v>0.0007790283224482699</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001570429681532907</v>
+        <v>0.0007663054459324086</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001574195312610437</v>
+        <v>0.000768683568060775</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001572115373583824</v>
+        <v>0.0007756188852420241</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001586779386526245</v>
+        <v>0.0007812676419765837</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001570392452107365</v>
+        <v>0.0007648807075577036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001569353894326408</v>
+        <v>0.000763842149776748</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001955480185360486</v>
+        <v>0.0008303560801225328</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002676684096300095</v>
+        <v>0.0009568688492995338</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002809217720857356</v>
+        <v>0.0009840106181703684</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002487942245217889</v>
+        <v>0.000936807896163606</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001993873449679282</v>
+        <v>0.0008498517886199929</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002662007523851672</v>
+        <v>0.0009584231451395001</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002665773154929114</v>
+        <v>0.0009608012672678507</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002663693215902587</v>
+        <v>0.000967736584449115</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002678495525528687</v>
+        <v>0.0009734096813998714</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001945199964363343</v>
+        <v>0.0008308468293573113</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003396003937986783</v>
+        <v>0.001085332555718944</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002257121033373383</v>
+        <v>0.0008834448690851353</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002645650463802581</v>
+        <v>0.0009514069300095673</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002650950979917923</v>
+        <v>0.000956155671915966</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003101061297484608</v>
+        <v>0.001044716848777833</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002651346946306114</v>
+        <v>0.0009655671233992998</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002649657028185928</v>
+        <v>0.0009562494579141072</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002653422659263449</v>
+        <v>0.0009586275800424744</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00265134272023684</v>
+        <v>0.0009655628972237232</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002666006733179261</v>
+        <v>0.0009712116539582826</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002158908521757656</v>
+        <v>0.0009150842905502265</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002648581240979427</v>
+        <v>0.0009537861617584474</v>
       </c>
     </row>
   </sheetData>
@@ -4493,7 +4493,7 @@
         <v>0.00148488431376234</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001489071576468462</v>
+        <v>0.001489071576468461</v>
       </c>
       <c r="I2" t="n">
         <v>0.001492259569058398</v>
@@ -4502,10 +4502,10 @@
         <v>0.001584956496414474</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00162113665419026</v>
+        <v>0.001621136654190257</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001482515368807099</v>
+        <v>0.001482515368807097</v>
       </c>
     </row>
     <row r="3">
@@ -4515,7 +4515,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001578220420931969</v>
+        <v>0.001578220420931968</v>
       </c>
       <c r="C3" t="n">
         <v>0.001572298179331193</v>
@@ -4533,7 +4533,7 @@
         <v>0.001584707532131141</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00158973826202437</v>
+        <v>0.001589738262024369</v>
       </c>
       <c r="I3" t="n">
         <v>0.001593631485580444</v>
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001096296525668316</v>
+        <v>0.0006766207484117188</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001036376384680954</v>
+        <v>0.0006663411212872212</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001100133728627791</v>
+        <v>0.0006804579513711932</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001161518499650924</v>
+        <v>0.0006945573870817106</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001161518499650925</v>
+        <v>0.0006945573870817106</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001098060114887383</v>
+        <v>0.0006796937743836187</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001102147589879951</v>
+        <v>0.0006824718126233536</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001093852885575579</v>
+        <v>0.0006826436272777202</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001111497819937178</v>
+        <v>0.0006918220426805807</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001098276504934769</v>
+        <v>0.0006786007276781712</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001098253427185048</v>
+        <v>0.0006785776499284499</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001938966703030067</v>
+        <v>0.000824930698823754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002106839318611123</v>
+        <v>0.000854742596638057</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002399689257178679</v>
+        <v>0.0009091797231567972</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002775539250133812</v>
+        <v>0.0009786250376274397</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002775539250133812</v>
+        <v>0.0009786250376274397</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002393718465406187</v>
+        <v>0.0009077296428392859</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002802367573971604</v>
+        <v>0.0009817105282020286</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002775533653299721</v>
+        <v>0.0009786194407933962</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003575968086568824</v>
+        <v>0.001125568807257448</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002234394262726645</v>
+        <v>0.0008785574519660552</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002427154311468299</v>
+        <v>0.0009124642042949637</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.00245470432026432</v>
+        <v>0.000808517557311737</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001831687169594218</v>
+        <v>0.0008063158186734894</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001844445128237443</v>
+        <v>0.0008114567569926613</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001769178308231679</v>
+        <v>0.0008015055128124133</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001848832199240754</v>
+        <v>0.0008155245975540465</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002456467909483388</v>
+        <v>0.0009187735449370365</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002494946893410938</v>
+        <v>0.0009276044887165304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001843266576568281</v>
+        <v>0.0009217233978311385</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002474134025139011</v>
+        <v>0.0008331300117788128</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001848752978200998</v>
+        <v>0.0008106845862573176</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001843179795003396</v>
+        <v>0.000809684689954051</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001541429731811711</v>
+        <v>0.0007549641922684438</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001541068813950085</v>
+        <v>0.0007551669883572764</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001545221058200604</v>
+        <v>0.0007587933209515392</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001553825210077331</v>
+        <v>0.000763603367742625</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001553825210077331</v>
+        <v>0.000763603367742625</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001543193321030779</v>
+        <v>0.0007580372182403439</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001547280796023347</v>
+        <v>0.0007608152564800787</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001538986091718975</v>
+        <v>0.0007609870711344461</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001556631026080574</v>
+        <v>0.0007701654865373057</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001543409711078164</v>
+        <v>0.0007569441715348971</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001543386633328443</v>
+        <v>0.0007569210937851751</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001920805358785447</v>
+        <v>0.0008217343022540207</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002621186255901249</v>
+        <v>0.0009452676571106006</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002753337274393657</v>
+        <v>0.0009714217738493682</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002429861442093838</v>
+        <v>0.0009177857437420776</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001949000505373756</v>
+        <v>0.0008331542193379267</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002608940125685879</v>
+        <v>0.000945608654843266</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002613027600679281</v>
+        <v>0.0009483866930831481</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002604732896374075</v>
+        <v>0.0009485585077373682</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002622512722084937</v>
+        <v>0.0009577606640175701</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001910035641064632</v>
+        <v>0.000821470334862873</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003326105526264372</v>
+        <v>0.001070679617241766</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002125999029277481</v>
+        <v>0.0008578483880649295</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002481130696462659</v>
+        <v>0.0009206178787829753</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002485329080194157</v>
+        <v>0.0009242523319258475</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002889284699928585</v>
+        <v>0.0009986442366828508</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002479053559634947</v>
+        <v>0.0009264435563823982</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002483255203543351</v>
+        <v>0.0009234881086660435</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002487342678535917</v>
+        <v>0.0009262661469057779</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002479047974231544</v>
+        <v>0.0009264379615601443</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002496692908593145</v>
+        <v>0.0009356163769630049</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002269141280840466</v>
+        <v>0.0008846729271209492</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002483448515841011</v>
+        <v>0.0009223719842108743</v>
       </c>
     </row>
   </sheetData>
@@ -4871,7 +4871,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001853525320896991</v>
+        <v>0.001853525320896992</v>
       </c>
       <c r="C2" t="n">
         <v>0.001755699520896561</v>
@@ -4889,13 +4889,13 @@
         <v>0.001922034701607579</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002473945125575531</v>
+        <v>0.002473945125575532</v>
       </c>
       <c r="I2" t="n">
         <v>0.001616076413844758</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002223490261563302</v>
+        <v>0.002223490261563301</v>
       </c>
       <c r="K2" t="n">
         <v>0.001848648737916645</v>
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002005302273724727</v>
+        <v>0.002005302273724726</v>
       </c>
       <c r="C3" t="n">
         <v>0.001871656444381811</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00208293401810901</v>
+        <v>0.002082934018109011</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001909312954284284</v>
+        <v>0.001909312954284283</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001758982750049495</v>
+        <v>0.001758982750049494</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002084102253217362</v>
+        <v>0.002084102253217363</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002719133340530401</v>
+        <v>0.002719133340530405</v>
       </c>
       <c r="I3" t="n">
         <v>0.00173205484575565</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00239898538246587</v>
+        <v>0.002398985382465869</v>
       </c>
       <c r="K3" t="n">
         <v>0.001973026910130956</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003456896857123952</v>
+        <v>0.003456896857123951</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001436059260527743</v>
+        <v>0.0009224663764832407</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001209609665040096</v>
+        <v>0.0007663515836492992</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001476181409416701</v>
+        <v>0.0009625885253721971</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001227111925329785</v>
+        <v>0.0007694322283103003</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001227111925329785</v>
+        <v>0.0007694322283103003</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001474444922741178</v>
+        <v>0.0009627804142822715</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001804756422945974</v>
+        <v>0.001291163538901472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001279857927898563</v>
+        <v>0.0007786752118676564</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001529925937014398</v>
+        <v>0.001016333052969893</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001327626245471331</v>
+        <v>0.0008140333614268283</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002186067292503199</v>
+        <v>0.001672474408458694</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02231091902586651</v>
+        <v>0.004596441675275048</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008954212121804136</v>
+        <v>0.002129401608653941</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02674362973244003</v>
+        <v>0.005409659406127386</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00895421242139963</v>
+        <v>0.00212940190824946</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00895421242139963</v>
+        <v>0.00212940190824946</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02742427972354659</v>
+        <v>0.005529951314476326</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06612597245447707</v>
+        <v>0.01261169749910948</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008954163498044794</v>
+        <v>0.002129352984894604</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03397392933130065</v>
+        <v>0.006726477619423251</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0123832628886927</v>
+        <v>0.002759825400090312</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02982477048320248</v>
+        <v>0.006536886143663441</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.003051686653084575</v>
+        <v>0.001206816796032462</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002074575182383201</v>
+        <v>0.0009185855138767905</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002323053373594539</v>
+        <v>0.001111637990259855</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001990442897741089</v>
+        <v>0.0009037784787267204</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0021075396852421</v>
+        <v>0.0009243875132152264</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002307213383922513</v>
+        <v>0.00124713083383149</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002652890083357777</v>
+        <v>0.00158417084791722</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002895485320455395</v>
+        <v>0.001063025631416876</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00315815009126342</v>
+        <v>0.001302900502564928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002138175578243013</v>
+        <v>0.0009566900432216441</v>
       </c>
       <c r="L6" t="n">
-        <v>0.003048147470276372</v>
+        <v>0.001824200518924629</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001999558210446473</v>
+        <v>0.001021642191131543</v>
       </c>
       <c r="C7" t="n">
-        <v>0.00184340550157663</v>
+        <v>0.0008778996502752942</v>
       </c>
       <c r="D7" t="n">
-        <v>0.002039626166992057</v>
+        <v>0.001061754802168117</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001842556677347405</v>
+        <v>0.0008777505040784678</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001842556677347405</v>
+        <v>0.0008777505040784678</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002037943872659907</v>
+        <v>0.001061956228930573</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002368255372864705</v>
+        <v>0.001390339353549775</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001843356877817291</v>
+        <v>0.0008778510265159576</v>
       </c>
       <c r="J7" t="n">
-        <v>0.002093424886933126</v>
+        <v>0.001115508867618196</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00189112519539006</v>
+        <v>0.0009132091760751298</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002749566242421921</v>
+        <v>0.001771650223106996</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002485754227974108</v>
+        <v>0.001107212689752735</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003182148702223304</v>
+        <v>0.001113518452312385</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003555901617565279</v>
+        <v>0.001328619280022972</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002948874931948136</v>
+        <v>0.001072462515833129</v>
       </c>
       <c r="F8" t="n">
-        <v>0.00235617032812308</v>
+        <v>0.0009681465061251662</v>
       </c>
       <c r="G8" t="n">
-        <v>0.00337726423948366</v>
+        <v>0.001297676612214279</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003707575739688473</v>
+        <v>0.001626059736833484</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003182677244641049</v>
+        <v>0.001113571409799663</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003432912917004868</v>
+        <v>0.001351258759633387</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002361473990145004</v>
+        <v>0.0009959905635034399</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004980046329063267</v>
+        <v>0.002164214716228718</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003348066717763292</v>
+        <v>0.001258979687133264</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003801716202512102</v>
+        <v>0.001222562331772346</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00399799117123973</v>
+        <v>0.001406427041048065</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004505414253917202</v>
+        <v>0.001346413435015252</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003801715582069881</v>
+        <v>0.001222562469441224</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003996254573595387</v>
+        <v>0.001406618910427625</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004326566073800177</v>
+        <v>0.001735002035046828</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003801667578752771</v>
+        <v>0.001222513708013012</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004051735587868605</v>
+        <v>0.001460171549115249</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003496114157138785</v>
+        <v>0.001195687231812268</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004707876943357397</v>
+        <v>0.002116312904604051</v>
       </c>
     </row>
   </sheetData>
@@ -5273,7 +5273,7 @@
         <v>0.001767156118684155</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001907624774576561</v>
+        <v>0.00190762477457656</v>
       </c>
       <c r="E2" t="n">
         <v>0.001805304097632186</v>
@@ -5282,16 +5282,16 @@
         <v>0.001653643305873263</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00189103271970248</v>
+        <v>0.001891032719702479</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002306362500485442</v>
+        <v>0.002306362500485441</v>
       </c>
       <c r="I2" t="n">
         <v>0.001627502030467487</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002081747129094186</v>
+        <v>0.002081747129094185</v>
       </c>
       <c r="K2" t="n">
         <v>0.001842952741042702</v>
@@ -5307,13 +5307,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001905622184973181</v>
+        <v>0.001905622184973182</v>
       </c>
       <c r="C3" t="n">
         <v>0.001884637509123376</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002067327227559785</v>
+        <v>0.002067327227559781</v>
       </c>
       <c r="E3" t="n">
         <v>0.001922946644500402</v>
@@ -5322,7 +5322,7 @@
         <v>0.001771285852741479</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002048242927420779</v>
+        <v>0.002048242927420778</v>
       </c>
       <c r="H3" t="n">
         <v>0.002526167544441188</v>
@@ -5331,13 +5331,13 @@
         <v>0.0017450189473151</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002235578124278049</v>
+        <v>0.002235578124278048</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001966294540387278</v>
+        <v>0.001966294540387279</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003313858918824018</v>
+        <v>0.003313858918824019</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001363467643839506</v>
+        <v>0.0008674938961226247</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00121284805283662</v>
+        <v>0.0007726897089311887</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001447041107842052</v>
+        <v>0.0009510673601251693</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001228341988205342</v>
+        <v>0.0007754168415698208</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001228341988205342</v>
+        <v>0.0007754168415698208</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001435010910015814</v>
+        <v>0.0009408227078983256</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001683989116431825</v>
+        <v>0.001188015368714944</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001266603030518654</v>
+        <v>0.0007821152747771138</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001423804311980813</v>
+        <v>0.0009278305642639298</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001303140714642484</v>
+        <v>0.0008071669669256027</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002091085215343295</v>
+        <v>0.001595111467626416</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01668072180816647</v>
+        <v>0.003563330614436491</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00897579576248695</v>
+        <v>0.002138968498426324</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0240021052577801</v>
+        <v>0.004920758629004049</v>
       </c>
       <c r="E5" t="n">
-        <v>0.008975796005240009</v>
+        <v>0.002138968741179376</v>
       </c>
       <c r="F5" t="n">
-        <v>0.008975796005240009</v>
+        <v>0.002138968741179376</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02372846468256424</v>
+        <v>0.004864470550606143</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05172987781881071</v>
+        <v>0.009996091732606162</v>
       </c>
       <c r="I5" t="n">
-        <v>0.008975752910333054</v>
+        <v>0.002138925646272431</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02365816986702637</v>
+        <v>0.0048410788807476</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0108442125807447</v>
+        <v>0.002486395606260515</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09729611862985915</v>
+        <v>0.006813442862113471</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002156424302509531</v>
+        <v>0.001134529441999306</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002028977815304857</v>
+        <v>0.0009163285463472768</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002253769673715582</v>
+        <v>0.001093051586949546</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001948665667830345</v>
+        <v>0.0009021938084968669</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002055902753449729</v>
+        <v>0.0009210675354636095</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002227967568685837</v>
+        <v>0.001207858253775006</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00323953682185512</v>
+        <v>0.001461791763385957</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002059559689188677</v>
+        <v>0.001049150820653794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002277702376744099</v>
+        <v>0.001196316623948449</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002082391467382178</v>
+        <v>0.0009443150986646375</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002906051101080252</v>
+        <v>0.001738545462738908</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001879737885731231</v>
+        <v>0.0009583574582032159</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001782916124564271</v>
+        <v>0.0008730216890115959</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00196326066248701</v>
+        <v>0.001041922001250376</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001781943748619876</v>
+        <v>0.0008728507508748231</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001781943748619876</v>
+        <v>0.0008728507508748231</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001951281151907542</v>
+        <v>0.001031686269978917</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00220025935832355</v>
+        <v>0.001278878930795533</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001782873272410381</v>
+        <v>0.0008729788368577042</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001940074553872535</v>
+        <v>0.001018694126344519</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001819410956534211</v>
+        <v>0.0008980305290061929</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002607355457235025</v>
+        <v>0.001685975029707008</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002322536748609634</v>
+        <v>0.001036290057647528</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003006041116746331</v>
+        <v>0.001088291686469913</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003349104238251374</v>
+        <v>0.00128583046926326</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002792497354023798</v>
+        <v>0.001050708184462173</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002249923023112919</v>
+        <v>0.0009552151027392983</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003175120257999378</v>
+        <v>0.001247081951483935</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003424098464415476</v>
+        <v>0.001494274612300569</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003006712378502218</v>
+        <v>0.001088374518362723</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003164067156625127</v>
+        <v>0.001234116823261684</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002247701595918417</v>
+        <v>0.0009734096811293635</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004647056406770886</v>
+        <v>0.002044962394880105</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002963027039749612</v>
+        <v>0.001149016348277346</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003383286488039367</v>
+        <v>0.001154686871456981</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003563681889578554</v>
+        <v>0.001323596135692207</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003979986747452024</v>
+        <v>0.001259706316573064</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003383286015114402</v>
+        <v>0.0011546869882507</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00355165151538264</v>
+        <v>0.001313351452424302</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003800629721798654</v>
+        <v>0.001560544113240917</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00338324363588548</v>
+        <v>0.001154644019303088</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003540444917347636</v>
+        <v>0.001300359308789903</v>
       </c>
       <c r="K9" t="n">
-        <v>0.00276868373292356</v>
+        <v>0.001065102536745422</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004207725820710124</v>
+        <v>0.001967640212152389</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001722821036520983</v>
+        <v>0.00172282103652098</v>
       </c>
       <c r="C2" t="n">
         <v>0.00178411268821582</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001831885750174664</v>
+        <v>0.001831885750174665</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001810624026539682</v>
+        <v>0.001810624026539684</v>
       </c>
       <c r="F2" t="n">
         <v>0.001695229594640822</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00183152475620494</v>
+        <v>0.001831524756204937</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002065730738877219</v>
+        <v>0.002065730738877218</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001669055162323655</v>
+        <v>0.001669055162323656</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001877808047759238</v>
+        <v>0.001877808047759235</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001813802140432623</v>
+        <v>0.001813802140432622</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00284264763189285</v>
+        <v>0.002842647631892852</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001859048075501539</v>
+        <v>0.001859048075501533</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001912128616587981</v>
+        <v>0.001912128616587982</v>
       </c>
       <c r="D3" t="n">
         <v>0.001984495088890642</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001938794277909908</v>
+        <v>0.001938794277909907</v>
       </c>
       <c r="F3" t="n">
         <v>0.001823399846011044</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001984079871045776</v>
+        <v>0.001984079871045779</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002253667338510769</v>
+        <v>0.002253667338510767</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001797161220903893</v>
+        <v>0.001797161220903894</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002013869987918181</v>
+        <v>0.002013869987918179</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001937068975751548</v>
+        <v>0.001937068975751545</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003147028678481584</v>
+        <v>0.003147028678481581</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001340780762642756</v>
+        <v>0.0008422583529563619</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001251748008648372</v>
+        <v>0.0008003148293849525</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001405615113445929</v>
+        <v>0.0009070927037595327</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00126662347070122</v>
+        <v>0.0008029330791768787</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001266623470701221</v>
+        <v>0.0008029330791768787</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001403389221351876</v>
+        <v>0.0009065241199633443</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001544583020880825</v>
+        <v>0.001046060611194428</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001295905978994913</v>
+        <v>0.0008080626959221874</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001340127369951237</v>
+        <v>0.0008416049602648398</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001289489649413899</v>
+        <v>0.0007909672397275013</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002006262383469813</v>
+        <v>0.001507739973783415</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01407298859946149</v>
+        <v>0.003083126920094061</v>
       </c>
       <c r="C5" t="n">
-        <v>0.01109058972107236</v>
+        <v>0.002531950961388519</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01953960778881766</v>
+        <v>0.004098675397331028</v>
       </c>
       <c r="E5" t="n">
-        <v>0.01109058992554422</v>
+        <v>0.002531951165860378</v>
       </c>
       <c r="F5" t="n">
-        <v>0.01109058992554422</v>
+        <v>0.002531951165860378</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02018642374692499</v>
+        <v>0.004212338178551278</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03574541896874509</v>
+        <v>0.007065407705402079</v>
       </c>
       <c r="I5" t="n">
-        <v>0.01109056067228399</v>
+        <v>0.002531921912600142</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01542228815580559</v>
+        <v>0.003320065245145403</v>
       </c>
       <c r="K5" t="n">
-        <v>0.009118543607656092</v>
+        <v>0.002168880728911761</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08673308274179299</v>
+        <v>0.0164196602760465</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002135259927582075</v>
+        <v>0.0009820866852280064</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0020705891678638</v>
+        <v>0.0009444308726259597</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002919460877701107</v>
+        <v>0.001173529556824729</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001989733817963024</v>
+        <v>0.000930200499605346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002089615975058044</v>
+        <v>0.0009477797591588137</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002197868386291191</v>
+        <v>0.001046352452234989</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003087534344777197</v>
+        <v>0.001317620042728717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002803112537601632</v>
+        <v>0.001073331048799586</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002855206952118041</v>
+        <v>0.0009918378155266909</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002073719487431745</v>
+        <v>0.0009289916904707419</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002824589507668418</v>
+        <v>0.001651765546861949</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001847656823726762</v>
+        <v>0.00093146853922375</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001802811088867287</v>
+        <v>0.0008973019309779469</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001912440185145727</v>
+        <v>0.0009962939158953499</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001801854794177854</v>
+        <v>0.0008971337915983292</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001801854794177854</v>
+        <v>0.0008971337915983292</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001910265282435867</v>
+        <v>0.0009957343062307307</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002051459081964815</v>
+        <v>0.001135270797461815</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001802782040078908</v>
+        <v>0.0008972728821895768</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001847003431035231</v>
+        <v>0.0009308151465322282</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001796365710497895</v>
+        <v>0.0008801774259948894</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002513138444553802</v>
+        <v>0.001596950160050803</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0022776413705823</v>
+        <v>0.001007145819060261</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002997022821632421</v>
+        <v>0.001107483194805721</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003266016809838988</v>
+        <v>0.001234523400550493</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002787883647972016</v>
+        <v>0.001070674868925754</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002256502703676618</v>
+        <v>0.0009771518232365272</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003105178065029138</v>
+        <v>0.001206038954827587</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003246371864558224</v>
+        <v>0.001345575446058696</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002997694822672166</v>
+        <v>0.001107577530786432</v>
       </c>
       <c r="J8" t="n">
-        <v>0.003042066543821888</v>
+        <v>0.001141146253242978</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002212141322669703</v>
+        <v>0.0009533539333406129</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00450708273152231</v>
+        <v>0.001947884352655682</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002759806990066689</v>
+        <v>0.001092006967629684</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003181244097419658</v>
+        <v>0.001139906139168588</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003290924426411386</v>
+        <v>0.001238907141043482</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003719324393713068</v>
+        <v>0.001234608439287886</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003181243788879546</v>
+        <v>0.00113990625335034</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003288698290988248</v>
+        <v>0.001238338514421373</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003429892090517197</v>
+        <v>0.001377875005652457</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003181215048631289</v>
+        <v>0.001139877090380217</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003225436439587607</v>
+        <v>0.00117341935472287</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002904632711382408</v>
+        <v>0.001075232417093639</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003891571453106181</v>
+        <v>0.001839554368241445</v>
       </c>
     </row>
   </sheetData>
@@ -6074,16 +6074,16 @@
         <v>0.001559709950036548</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00162923782038999</v>
+        <v>0.001629237820389989</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001803541537222949</v>
+        <v>0.00180354153722295</v>
       </c>
       <c r="I2" t="n">
         <v>0.001530868482842993</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001963757706751244</v>
+        <v>0.001963757706751243</v>
       </c>
       <c r="K2" t="n">
         <v>0.001769959298314756</v>
@@ -6114,16 +6114,16 @@
         <v>0.001662537724452389</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001746820391037841</v>
+        <v>0.001746820391037842</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001947518506657496</v>
+        <v>0.001947518506657497</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001633673842282048</v>
+        <v>0.001633673842282047</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00210066069848051</v>
+        <v>0.002100660698480509</v>
       </c>
       <c r="K3" t="n">
         <v>0.001882088780652377</v>
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001201371655994598</v>
+        <v>0.0007298788083360055</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001120683510150489</v>
+        <v>0.0007104699910547818</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0012381516843327</v>
+        <v>0.0007666588366741067</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001137196335548301</v>
+        <v>0.0007133764867126173</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0011371963355483</v>
+        <v>0.0007133764867126174</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001251549603658685</v>
+        <v>0.0007816187959619914</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001357031373405387</v>
+        <v>0.0008855385257467933</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001182803416272004</v>
+        <v>0.000721386533546784</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001329907500266361</v>
+        <v>0.0008584146526077679</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00123186422035673</v>
+        <v>0.0007603713726981371</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001390697167752982</v>
+        <v>0.0009192043200943902</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005816515148111759</v>
+        <v>0.001542144058547283</v>
       </c>
       <c r="C5" t="n">
-        <v>0.005236117792746011</v>
+        <v>0.001434786420866809</v>
       </c>
       <c r="D5" t="n">
-        <v>0.008910215464683869</v>
+        <v>0.002116942054699263</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005236118082070722</v>
+        <v>0.001434786710191527</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005236118082070722</v>
+        <v>0.001434786710191527</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01072268318577887</v>
+        <v>0.00244853829738277</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02152791512872118</v>
+        <v>0.004435614047445926</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005236097694534694</v>
+        <v>0.001434766322655493</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01950301852938752</v>
+        <v>0.004056882176401861</v>
       </c>
       <c r="K5" t="n">
-        <v>0.008494953200406353</v>
+        <v>0.002038675026260251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01447028420723599</v>
+        <v>0.00547887565894496</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001993764429266721</v>
+        <v>0.000869339935676214</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001953590571147597</v>
+        <v>0.0008570616329959496</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002031943632720711</v>
+        <v>0.001026890062806341</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00187142723430081</v>
+        <v>0.0008426011241928419</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001970880900386265</v>
+        <v>0.0008601049693290354</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002714264422160696</v>
+        <v>0.0009210799233022005</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002864354106004456</v>
+        <v>0.001150827325246735</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002645518234774015</v>
+        <v>0.0008608476608869928</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00280794195272996</v>
+        <v>0.001118548714831797</v>
       </c>
       <c r="K6" t="n">
-        <v>0.00201718940555504</v>
+        <v>0.0008985886045440948</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002187946264140643</v>
+        <v>0.001059520160298303</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00169124237016984</v>
+        <v>0.0008160960535636706</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001672694228658561</v>
+        <v>0.0008076238769857648</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001727969002897041</v>
+        <v>0.0008528666842743045</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001671911256844991</v>
+        <v>0.0008074863123508913</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001671911256844991</v>
+        <v>0.0008074863123508913</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001741420317833927</v>
+        <v>0.0008678360411896575</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00184690208758063</v>
+        <v>0.0009717557709744605</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001672674130447247</v>
+        <v>0.0008076037787744495</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001819778214441604</v>
+        <v>0.0009446318978354339</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001721734934531973</v>
+        <v>0.0008465886179258022</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001880567881928225</v>
+        <v>0.001005421565322055</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002113011398502877</v>
+        <v>0.000890327402148055</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00284471445948555</v>
+        <v>0.001013899436492834</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003056258257372834</v>
+        <v>0.00108664559179529</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00263942481937498</v>
+        <v>0.0009777686984334768</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002117826915212141</v>
+        <v>0.0008859674677982518</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002913975729254135</v>
+        <v>0.001074205792481378</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003019457499000834</v>
+        <v>0.00117812552226618</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002845229541867453</v>
+        <v>0.001013973530066171</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002992481176797967</v>
+        <v>0.001151027618091778</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002129557720351977</v>
+        <v>0.000918365427841193</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003837382450128179</v>
+        <v>0.001349820927459084</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002711609074014284</v>
+        <v>0.0009956805924671954</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003185388379353704</v>
+        <v>0.001073858046065492</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003240716772411355</v>
+        <v>0.001119110290266155</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003753523903970987</v>
+        <v>0.001173850136259886</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003185388347780037</v>
+        <v>0.001073858278912095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00325411446852907</v>
+        <v>0.001134070210269385</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003359596238275775</v>
+        <v>0.001237989940054187</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003185368281142388</v>
+        <v>0.001073837947854177</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003332472365136743</v>
+        <v>0.00121086606691516</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002614500891653869</v>
+        <v>0.001062617667505202</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003393262032623371</v>
+        <v>0.001271655734401782</v>
       </c>
     </row>
   </sheetData>
@@ -6455,16 +6455,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001524218697862826</v>
+        <v>0.001524218697862827</v>
       </c>
       <c r="C2" t="n">
         <v>0.001699518926753932</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001542950788411306</v>
+        <v>0.001542950788411308</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001736289772667047</v>
+        <v>0.001736289772667046</v>
       </c>
       <c r="F2" t="n">
         <v>0.001588575969792313</v>
@@ -6476,13 +6476,13 @@
         <v>0.001509922520148557</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001559406575503538</v>
+        <v>0.00155940657550354</v>
       </c>
       <c r="J2" t="n">
-        <v>0.00187565645536965</v>
+        <v>0.001875656455369649</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001765204925970587</v>
+        <v>0.001765204925970586</v>
       </c>
       <c r="L2" t="n">
         <v>0.001483162624556006</v>
@@ -6495,34 +6495,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001626105250774127</v>
+        <v>0.001626105250774128</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001806574018415059</v>
+        <v>0.001806574018415058</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001647651035245746</v>
+        <v>0.001647651035245747</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001843484957188867</v>
+        <v>0.001843484957188869</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001695771154314134</v>
+        <v>0.001695771154314135</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001681971691362544</v>
+        <v>0.001681971691362546</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001609871937929928</v>
+        <v>0.001609871937929927</v>
       </c>
       <c r="I3" t="n">
         <v>0.001666628017922258</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001999142493918724</v>
+        <v>0.001999142493918723</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001876663965620489</v>
+        <v>0.001876663965620488</v>
       </c>
       <c r="L3" t="n">
         <v>0.001578881856898407</v>
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001171568477409399</v>
+        <v>0.0007164810135788035</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001138442736735617</v>
+        <v>0.0007279624127913857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001182703911494461</v>
+        <v>0.000727616447663867</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001152684978164592</v>
+        <v>0.0007304692329726684</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001152684978164592</v>
+        <v>0.0007304692329726684</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001198805796286103</v>
+        <v>0.0007450663490818186</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001163094522924005</v>
+        <v>0.0007080070590934115</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001182012406803594</v>
+        <v>0.0007356236510647708</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001257050287144536</v>
+        <v>0.0008019628233139402</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001209452411490228</v>
+        <v>0.0007543649476596339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001147198154341232</v>
+        <v>0.0006921106905106377</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004757218232123763</v>
+        <v>0.00134755536698899</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006413474993114994</v>
+        <v>0.001656368084883494</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005478534289053133</v>
+        <v>0.001483682590017367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.006413475218483158</v>
+        <v>0.001656368310251656</v>
       </c>
       <c r="F5" t="n">
-        <v>0.006413475218483157</v>
+        <v>0.001656368310251656</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007147413776855014</v>
+        <v>0.00179202134798891</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00424509825951255</v>
+        <v>0.001250439713793767</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006413466469307941</v>
+        <v>0.001656359561076434</v>
       </c>
       <c r="J5" t="n">
-        <v>0.012610034233672</v>
+        <v>0.002800087987075723</v>
       </c>
       <c r="K5" t="n">
-        <v>0.007781882157099157</v>
+        <v>0.001911112576618848</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005090248183201925</v>
+        <v>0.001386087491829733</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001927543949787182</v>
+        <v>0.0009563945512613736</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001926491422728279</v>
+        <v>0.0008666589807745537</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001936884412139145</v>
+        <v>0.0008603515399084106</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001847835963292297</v>
+        <v>0.0008528158056921964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001935674653733883</v>
+        <v>0.0008682754151261458</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001954781268663886</v>
+        <v>0.000878118031499354</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002555965176536311</v>
+        <v>0.0008402818424495257</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001937987879181378</v>
+        <v>0.0008686753334823062</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002067795807404422</v>
+        <v>0.001043436994186778</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001967252084421938</v>
+        <v>0.0008877376893729202</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001897625687478109</v>
+        <v>0.0008241859356270643</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001614678021208152</v>
+        <v>0.0007944682928648022</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001625130474409408</v>
+        <v>0.0008136194541578312</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001625763194717228</v>
+        <v>0.0008055948810885399</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001624451474230438</v>
+        <v>0.0008135001358303446</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001624451474230438</v>
+        <v>0.0008135001358303446</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001641915340084854</v>
+        <v>0.000823053628367817</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001606204066722757</v>
+        <v>0.0007859943383794093</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001625121950602344</v>
+        <v>0.000813610930350769</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001700159830943285</v>
+        <v>0.0008799501025999376</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001652561955288979</v>
+        <v>0.000832352226945632</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001590307698139985</v>
+        <v>0.0007700979697966354</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001991081783760195</v>
+        <v>0.0008607153547149948</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002678312485037573</v>
+        <v>0.0009989794870239952</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002819878465201786</v>
+        <v>0.001015759167555024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002493131591283114</v>
+        <v>0.0009663878356031774</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002022626483416841</v>
+        <v>0.0008835789370674227</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002695551749012837</v>
+        <v>0.001008493635334316</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002659840475650641</v>
+        <v>0.0009714343453458905</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002678758359530328</v>
+        <v>0.0009990509373172674</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002753929335406521</v>
+        <v>0.001065413534380515</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002016385773748986</v>
+        <v>0.0008963852186476235</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003351370235403372</v>
+        <v>0.001080044974675511</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002411783958891706</v>
+        <v>0.0009347589371369282</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002833351317082374</v>
+        <v>0.001026266321316024</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002834034633726745</v>
+        <v>0.001018250653201915</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003307769671234556</v>
+        <v>0.001109764136897733</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002833351496008649</v>
+        <v>0.001026266538510412</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002850136182757822</v>
+        <v>0.00103570049552601</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002814424909395732</v>
+        <v>0.0009986412055376019</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002833342793275318</v>
+        <v>0.001026257797508961</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002908380673616257</v>
+        <v>0.001092596969758131</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002612917201343958</v>
+        <v>0.001001374749335441</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002798528540812955</v>
+        <v>0.0009827448369548284</v>
       </c>
     </row>
   </sheetData>
@@ -6854,7 +6854,7 @@
         <v>0.001562105858736169</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001684596030564098</v>
+        <v>0.001684596030564099</v>
       </c>
       <c r="D2" t="n">
         <v>0.001515775520759957</v>
@@ -6869,13 +6869,13 @@
         <v>0.001559258172085421</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001502863091008993</v>
+        <v>0.001502863091008994</v>
       </c>
       <c r="I2" t="n">
         <v>0.001570190107477174</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001777302942387238</v>
+        <v>0.001777302942387239</v>
       </c>
       <c r="K2" t="n">
         <v>0.001746043833124482</v>
@@ -6894,7 +6894,7 @@
         <v>0.001674061893328177</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001797651993149217</v>
+        <v>0.001797651993149218</v>
       </c>
       <c r="D3" t="n">
         <v>0.001620772407354935</v>
@@ -6906,7 +6906,7 @@
         <v>0.001710866452793136</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001670786463783304</v>
+        <v>0.001670786463783305</v>
       </c>
       <c r="H3" t="n">
         <v>0.001606124156726379</v>
@@ -6915,7 +6915,7 @@
         <v>0.001683425906151581</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001898799802760083</v>
+        <v>0.001898799802760084</v>
       </c>
       <c r="K3" t="n">
         <v>0.001859087552193158</v>
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001196445823344638</v>
+        <v>0.0007395168270678609</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001153926753883036</v>
+        <v>0.000736070916930446</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001168904400600728</v>
+        <v>0.0007119754043239547</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001167740734838156</v>
+        <v>0.0007385023345927396</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001167740734838156</v>
+        <v>0.0007385023345927397</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001193103070293756</v>
+        <v>0.0007375336113976254</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001161251480732759</v>
+        <v>0.0007043224844559766</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001190677328462015</v>
+        <v>0.0007425346886564599</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001234204456480205</v>
+        <v>0.0007772754602034261</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001200750427585951</v>
+        <v>0.0007438214313091636</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001158991481797788</v>
+        <v>0.0007020624855210071</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.006731057116684886</v>
+        <v>0.001713608409417528</v>
       </c>
       <c r="C5" t="n">
-        <v>0.007078240737552506</v>
+        <v>0.001778750172406399</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004295671996048358</v>
+        <v>0.001262286498140818</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0070782409281197</v>
+        <v>0.001778750362973594</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0070782409281197</v>
+        <v>0.001778750362973594</v>
       </c>
       <c r="G5" t="n">
-        <v>0.006618990970190555</v>
+        <v>0.001692489876604941</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003983623052797211</v>
+        <v>0.001201059878447698</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007078235483468982</v>
+        <v>0.001778744918322874</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01052663801733704</v>
+        <v>0.002412743758052275</v>
       </c>
       <c r="K5" t="n">
-        <v>0.006786503772443691</v>
+        <v>0.001726914014677141</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005871121144086941</v>
+        <v>0.001178314381842102</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001958425738540528</v>
+        <v>0.000873625291415655</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001943606734302173</v>
+        <v>0.0008750545927311197</v>
       </c>
       <c r="D6" t="n">
-        <v>0.00254598475721247</v>
+        <v>0.0008446365458388205</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001864273727975275</v>
+        <v>0.0008610921407206068</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0019506317994378</v>
+        <v>0.0008762911612156533</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001955082985489619</v>
+        <v>0.0009794808904143007</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002560743511394337</v>
+        <v>0.0009506330805177562</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001952657243657898</v>
+        <v>0.0008766431530042552</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002049945444734001</v>
+        <v>0.001019985305022377</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001964772605002598</v>
+        <v>0.0008782893338058652</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001918920839753936</v>
+        <v>0.0008358100517965641</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001637754699173311</v>
+        <v>0.0008171871887928412</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001631991458374217</v>
+        <v>0.0008202103044649764</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001610162778566094</v>
+        <v>0.0007896368784250443</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001631302233076156</v>
+        <v>0.0008200891578405415</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001631302233076156</v>
+        <v>0.0008200891578405415</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001634411946122435</v>
+        <v>0.0008152039731226063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001602560356561433</v>
+        <v>0.0007819928461809576</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001631986204290682</v>
+        <v>0.0008202050503814407</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00167551333230888</v>
+        <v>0.0008549458219284065</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001642059303414591</v>
+        <v>0.0008214917930341443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001600300357626461</v>
+        <v>0.0007797328472459869</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002011072069020358</v>
+        <v>0.0008828910455298963</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002678691964962736</v>
+        <v>0.001004429592626965</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002797104482707733</v>
+        <v>0.0009985386172220109</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002494437505247545</v>
+        <v>0.0009720009649195557</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002026287789767091</v>
+        <v>0.0008896066154414578</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002681576540660238</v>
+        <v>0.0009995049407626111</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002649724951099142</v>
+        <v>0.0009662938138209417</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002679150798828517</v>
+        <v>0.001004506018021446</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002722810357053986</v>
+        <v>0.001039270097284766</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002002859615115076</v>
+        <v>0.0008849926475493435</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003351354724469294</v>
+        <v>0.001087918414140396</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002324985357410445</v>
+        <v>0.0009381397839871867</v>
       </c>
       <c r="C9" t="n">
-        <v>0.002699330524479033</v>
+        <v>0.00100806197908153</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002677552649819901</v>
+        <v>0.00097749749474777</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003137967985480901</v>
+        <v>0.001085262328826909</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002699330674705043</v>
+        <v>0.001008062162548675</v>
       </c>
       <c r="G9" t="n">
-        <v>0.002701751012227225</v>
+        <v>0.00100305564773916</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002669899422666219</v>
+        <v>0.0009698445207975118</v>
       </c>
       <c r="I9" t="n">
-        <v>0.002699325270395488</v>
+        <v>0.001008056724997995</v>
       </c>
       <c r="J9" t="n">
-        <v>0.002742852398413661</v>
+        <v>0.001042797496544961</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002489162194443937</v>
+        <v>0.0009690092931328488</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002667639423731246</v>
+        <v>0.0009675845218625416</v>
       </c>
     </row>
   </sheetData>
@@ -7262,13 +7262,13 @@
         <v>0.001618483087996896</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001863938724720284</v>
+        <v>0.001863938724720283</v>
       </c>
       <c r="H2" t="n">
         <v>0.002447965588717348</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001591733248870864</v>
+        <v>0.001591733248870865</v>
       </c>
       <c r="J2" t="n">
         <v>0.002038920829015086</v>
@@ -7277,7 +7277,7 @@
         <v>0.0018381173854532</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002891654405158424</v>
+        <v>0.002891654405158425</v>
       </c>
     </row>
     <row r="3">
@@ -7287,7 +7287,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001842514812646739</v>
+        <v>0.00184251481264674</v>
       </c>
       <c r="C3" t="n">
         <v>0.001842302409915243</v>
@@ -7305,19 +7305,19 @@
         <v>0.002017075622378655</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002689038704557585</v>
+        <v>0.002689038704557583</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001703873110938296</v>
+        <v>0.001703873110938297</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002187145191931245</v>
+        <v>0.002187145191931244</v>
       </c>
       <c r="K3" t="n">
         <v>0.001960757299104918</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003199107956795635</v>
+        <v>0.003199107956795634</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001339190964196354</v>
+        <v>0.0008364828031954314</v>
       </c>
       <c r="C4" t="n">
-        <v>0.001183943315470161</v>
+        <v>0.0007502161585543792</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001450136824095436</v>
+        <v>0.0009474286630945137</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001201258794846402</v>
+        <v>0.0007532639289870742</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001201258794846402</v>
+        <v>0.0007532639289870742</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001427141195588896</v>
+        <v>0.0009263014008381072</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001776464029852975</v>
+        <v>0.001273755868852052</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001253016307958508</v>
+        <v>0.0007623367827040541</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001409966854417607</v>
+        <v>0.0009072586934166823</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001308714210679805</v>
+        <v>0.0008060060496788823</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002040132113038258</v>
+        <v>0.001537423952037335</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.01454027821080243</v>
+        <v>0.003159874146008567</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00781670273931143</v>
+        <v>0.001917581810824945</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02466316829807692</v>
+        <v>0.005032922180377582</v>
       </c>
       <c r="E5" t="n">
-        <v>0.007816703037950973</v>
+        <v>0.001917582109464497</v>
       </c>
       <c r="F5" t="n">
-        <v>0.007816703037950972</v>
+        <v>0.001917582109464497</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0235909893055218</v>
+        <v>0.004827138647049206</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05954963928350488</v>
+        <v>0.01144183465839801</v>
       </c>
       <c r="I5" t="n">
-        <v>0.007816658780012432</v>
+        <v>0.001917537851525967</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02314610690149197</v>
+        <v>0.00473281932097257</v>
       </c>
       <c r="K5" t="n">
-        <v>0.01178469497347985</v>
+        <v>0.00264977865394102</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09690618481854633</v>
+        <v>0.01823384913773547</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.002160138646589105</v>
+        <v>0.0009809695945136392</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002038777334672988</v>
+        <v>0.0009006669451188423</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002287886118204134</v>
+        <v>0.001094872538058704</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001955474788861908</v>
+        <v>0.0008860059432145272</v>
       </c>
       <c r="F6" t="n">
-        <v>0.002069121342484441</v>
+        <v>0.0009060077365437109</v>
       </c>
       <c r="G6" t="n">
-        <v>0.003006634050798243</v>
+        <v>0.00120429214184863</v>
       </c>
       <c r="H6" t="n">
-        <v>0.003410776517632012</v>
+        <v>0.001561394865142561</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002073963990351259</v>
+        <v>0.001040327523714578</v>
       </c>
       <c r="J6" t="n">
-        <v>0.003007067432355389</v>
+        <v>0.001188348393610619</v>
       </c>
       <c r="K6" t="n">
-        <v>0.002111606721140193</v>
+        <v>0.0009473151307542127</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002886348960840875</v>
+        <v>0.001686358116443582</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001882694714699501</v>
+        <v>0.0009321394627656603</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001796564017760635</v>
+        <v>0.0008580374015732625</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001993586659110369</v>
+        <v>0.001043075833538868</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001795690581873174</v>
+        <v>0.0008578839229368923</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001795690581873174</v>
+        <v>0.0008578839229368923</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001970644946092043</v>
+        <v>0.001021958060408335</v>
       </c>
       <c r="H7" t="n">
-        <v>0.002319967780356125</v>
+        <v>0.001369412528422282</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001796520058461656</v>
+        <v>0.0008579934422742827</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001953470604920753</v>
+        <v>0.001002915352986911</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001852217961182952</v>
+        <v>0.0009016627092491106</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002583635863541403</v>
+        <v>0.001633080611607567</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002352547533816019</v>
+        <v>0.00101483355848208</v>
       </c>
       <c r="C8" t="n">
-        <v>0.003092100779526212</v>
+        <v>0.001086051870409323</v>
       </c>
       <c r="D8" t="n">
-        <v>0.003461120291149514</v>
+        <v>0.001301361751378208</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002866169028910888</v>
+        <v>0.001046288128594642</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002292120198297276</v>
+        <v>0.0009452555349541014</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003266787999740838</v>
+        <v>0.001250079236614425</v>
       </c>
       <c r="H8" t="n">
-        <v>0.003616110834005009</v>
+        <v>0.001597533704628385</v>
       </c>
       <c r="I8" t="n">
-        <v>0.003092663112110447</v>
+        <v>0.001086114618480372</v>
       </c>
       <c r="J8" t="n">
-        <v>0.00324977604815056</v>
+        <v>0.001231065109759104</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002306722014984642</v>
+        <v>0.0009816554222847591</v>
       </c>
       <c r="L8" t="n">
-        <v>0.004742908160309928</v>
+        <v>0.002013112533779583</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003166647239787262</v>
+        <v>0.001158115105956634</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003665305669338929</v>
+        <v>0.001186935930468871</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003862382270239415</v>
+        <v>0.00137198385931536</v>
       </c>
       <c r="E9" t="n">
-        <v>0.004340139145872788</v>
+        <v>0.001305706867774249</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003665305076476551</v>
+        <v>0.001186936072204084</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003839386597670334</v>
+        <v>0.001350856589303945</v>
       </c>
       <c r="H9" t="n">
-        <v>0.004188709431934413</v>
+        <v>0.001698311057317891</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003665261710039945</v>
+        <v>0.00118689197116989</v>
       </c>
       <c r="J9" t="n">
-        <v>0.003822212256499045</v>
+        <v>0.001331813881882519</v>
       </c>
       <c r="K9" t="n">
-        <v>0.003368383788462395</v>
+        <v>0.001170927317219968</v>
       </c>
       <c r="L9" t="n">
-        <v>0.004452377515119693</v>
+        <v>0.001961979140503172</v>
       </c>
     </row>
   </sheetData>
@@ -7646,13 +7646,13 @@
         <v>0.001503796599591133</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001687957089055229</v>
+        <v>0.001687957089055228</v>
       </c>
       <c r="D2" t="n">
         <v>0.001849214497043732</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001725283516738898</v>
+        <v>0.001725283516738897</v>
       </c>
       <c r="F2" t="n">
         <v>0.001575998944047144</v>
@@ -7664,7 +7664,7 @@
         <v>0.00159897563462809</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00154938828652916</v>
+        <v>0.001549388286529159</v>
       </c>
       <c r="J2" t="n">
         <v>0.001916253941868371</v>
@@ -7673,7 +7673,7 @@
         <v>0.001723136802838082</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002315283583925599</v>
+        <v>0.002315283583925598</v>
       </c>
     </row>
     <row r="3">
@@ -7683,7 +7683,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001602593434520191</v>
+        <v>0.00160259343452019</v>
       </c>
       <c r="C3" t="n">
         <v>0.001793471462406998</v>
@@ -7701,7 +7701,7 @@
         <v>0.001836654530003503</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001712285083149185</v>
+        <v>0.001712285083149184</v>
       </c>
       <c r="I3" t="n">
         <v>0.001654995272523717</v>
@@ -7713,7 +7713,7 @@
         <v>0.001828720879108024</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002535937777043931</v>
+        <v>0.002535937777043929</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001171817393495728</v>
+        <v>0.0007057118850428176</v>
       </c>
       <c r="C4" t="n">
-        <v>0.00113718621002525</v>
+        <v>0.0007220113386568844</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001377153696933392</v>
+        <v>0.0009110481884804837</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001151996478600361</v>
+        <v>0.000724618138183153</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001151996478600361</v>
+        <v>0.0007246181381831532</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001290853230209276</v>
+        <v>0.0008263406444391833</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001228432927514043</v>
+        <v>0.0007623274190611355</v>
       </c>
       <c r="I4" t="n">
-        <v>0.001186516126656399</v>
+        <v>0.0007306700845769881</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001292954029222667</v>
+        <v>0.0008268485207697575</v>
       </c>
       <c r="K4" t="n">
-        <v>0.001198678480961313</v>
+        <v>0.0007325729725084056</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00165409255839659</v>
+        <v>0.001187987049943681</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003310407918716749</v>
+        <v>0.001082103815442198</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00561602299250896</v>
+        <v>0.001510286608102666</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02020663526316295</v>
+        <v>0.004225036926179699</v>
       </c>
       <c r="E5" t="n">
-        <v>0.005616023225847759</v>
+        <v>0.001510286841441467</v>
       </c>
       <c r="F5" t="n">
-        <v>0.005616023225847759</v>
+        <v>0.001510286841441467</v>
       </c>
       <c r="G5" t="n">
-        <v>0.01385483398660417</v>
+        <v>0.003037601245582741</v>
       </c>
       <c r="H5" t="n">
-        <v>0.008795522760942101</v>
+        <v>0.002094135222527931</v>
       </c>
       <c r="I5" t="n">
-        <v>0.005615994692314898</v>
+        <v>0.001510258307908604</v>
       </c>
       <c r="J5" t="n">
-        <v>0.01511590090197708</v>
+        <v>0.003259687157191946</v>
       </c>
       <c r="K5" t="n">
-        <v>0.005528082051846019</v>
+        <v>0.001494547996855271</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05347810205694199</v>
+        <v>0.00214425291766725</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001936915622875095</v>
+        <v>0.0009562763119689828</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001929539758631455</v>
+        <v>0.0008614655624559291</v>
       </c>
       <c r="D6" t="n">
-        <v>0.002165385291419959</v>
+        <v>0.001049776948358391</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001850591276491228</v>
+        <v>0.0008475708219457138</v>
       </c>
       <c r="F6" t="n">
-        <v>0.001948526665329869</v>
+        <v>0.000864807450287916</v>
       </c>
       <c r="G6" t="n">
-        <v>0.002714514754549472</v>
+        <v>0.0009609979320802974</v>
       </c>
       <c r="H6" t="n">
-        <v>0.002684921533124146</v>
+        <v>0.001018669412259498</v>
       </c>
       <c r="I6" t="n">
-        <v>0.002610177650996594</v>
+        <v>0.0009812345115031524</v>
       </c>
       <c r="J6" t="n">
-        <v>0.002727312830075806</v>
+        <v>0.0009715454803612632</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001953323845806006</v>
+        <v>0.0008653905560013857</v>
       </c>
       <c r="L6" t="n">
-        <v>0.002429746252225249</v>
+        <v>0.001324502099317804</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001641950025278581</v>
+        <v>0.0007884552277882467</v>
       </c>
       <c r="C7" t="n">
-        <v>0.001656677058633314</v>
+        <v>0.0008134417275164787</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001847236067395635</v>
+        <v>0.000993782685233533</v>
       </c>
       <c r="E7" t="n">
-        <v>0.001655853702617029</v>
+        <v>0.0008132970091295716</v>
       </c>
       <c r="F7" t="n">
-        <v>0.001655853702617029</v>
+        <v>0.0008132970091295716</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001760985861992131</v>
+        <v>0.0009090839871846123</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001698565559296898</v>
+        <v>0.0008450707618065641</v>
       </c>
       <c r="I7" t="n">
-        <v>0.001656648758439252</v>
+        <v>0.0008134134273224167</v>
       </c>
       <c r="J7" t="n">
-        <v>0.00176308666100552</v>
+        <v>0.0009095918635151867</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001668811112744168</v>
+        <v>0.0008153163152538342</v>
       </c>
       <c r="L7" t="n">
-        <v>0.002124225190179444</v>
+        <v>0.001270730392689109</v>
       </c>
     </row>
     <row r="8">
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002047140045700125</v>
+        <v>0.0008597686709960191</v>
       </c>
       <c r="C8" t="n">
-        <v>0.002779991104165084</v>
+        <v>0.001011144998459469</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00312021354396849</v>
+        <v>0.001217826719896351</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002583480803695056</v>
+        <v>0.0009765593780346499</v>
       </c>
       <c r="F8" t="n">
-        <v>0.002084187929324047</v>
+        <v>0.0008886838326215147</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002884884221244958</v>
+        <v>0.001106890097341277</v>
       </c>
       <c r="H8" t="n">
-        <v>0.002822463918549647</v>
+        <v>0.001042876871963215</v>
       </c>
       <c r="I8" t="n">
-        <v>0.002780547117692081</v>
+        <v>0.001011219537479082</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002887126266939925</v>
+        <v>0.001107422833087674</v>
       </c>
       <c r="K8" t="n">
-        <v>0.002060650756794291</v>
+        <v>0.0008842800922329688</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003998874506664108</v>
+        <v>0.001600668670602606</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.002556123053855787</v>
+        <v>0.0009493496799460113</v>
       </c>
       <c r="C9" t="n">
-        <v>0.003024431814719322</v>
+        <v>0.001054166563283224</v>
       </c>
       <c r="D9" t="n">
-        <v>0.003215041553273323</v>
+        <v>0.001234516449443564</v>
       </c>
       <c r="E9" t="n">
-        <v>0.003547855973406208</v>
+        <v>0.001146289406984112</v>
       </c>
       <c r="F9" t="n">
-        <v>0.003024431892697244</v>
+        <v>0.001054166769278511</v>
       </c>
       <c r="G9" t="n">
-        <v>0.003128740618078143</v>
+        <v>0.001149808822951357</v>
       </c>
       <c r="H9" t="n">
-        <v>0.003066320315382907</v>
+        <v>0.00108579559757331</v>
       </c>
       <c r="I9" t="n">
-        <v>0.003024403514525262</v>
+        <v>0.001054138263089161</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00313084141709153</v>
+        <v>0.001150316699281932</v>
       </c>
       <c r="K9" t="n">
-        <v>0.002773759031596559</v>
+        <v>0.0009555204270144612</v>
       </c>
       <c r="L9" t="n">
-        <v>0.003491979946265454</v>
+        <v>0.001511455228455855</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication marine results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001965158088279958</v>
+        <v>0.0008449854937270019</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001882299464714898</v>
+        <v>0.0009572700886623306</v>
       </c>
       <c r="D2" t="n">
-        <v>0.002436254609911233</v>
+        <v>0.0008697783679873998</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001922527732824526</v>
+        <v>0.0009912872891636596</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001762876614088069</v>
+        <v>0.0008584787227424251</v>
       </c>
       <c r="G2" t="n">
-        <v>0.002088113982665379</v>
+        <v>0.0008514564182384302</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00261911895249744</v>
+        <v>0.0008793133894171389</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001731792481240241</v>
+        <v>0.0008327093103732859</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002266345628208429</v>
+        <v>0.001039236162549189</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001918662506463396</v>
+        <v>0.00098337391920448</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003190219778389428</v>
+        <v>0.0009101023584615698</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00213318913135174</v>
+        <v>0.0009467307397597003</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002015150632650059</v>
+        <v>0.001065657121219904</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002675047718578166</v>
+        <v>0.001123478687602477</v>
       </c>
       <c r="E3" t="n">
-        <v>0.002055520962909799</v>
+        <v>0.001121341292344692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001895869844173341</v>
+        <v>0.0009020642872900717</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00227461388013176</v>
+        <v>0.0009933018084791619</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002885614714441803</v>
+        <v>0.001194484658714626</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001864640897507633</v>
+        <v>0.0008595148563005965</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002445250775682498</v>
+        <v>0.001289014102877056</v>
       </c>
       <c r="K3" t="n">
-        <v>0.002052579455640571</v>
+        <v>0.001110047146185085</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003542208862400057</v>
+        <v>0.001411650583385579</v>
       </c>
     </row>
     <row r="4">
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.001004254226357975</v>
+        <v>0.00100425422635798</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008555620181352514</v>
+        <v>0.0008555620181352511</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001284301146414817</v>
+        <v>0.001284301146414818</v>
       </c>
       <c r="E4" t="n">
         <v>0.000858928141198734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008589281411987345</v>
+        <v>0.0008589281411987341</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001076964041059431</v>
+        <v>0.001076964041059433</v>
       </c>
       <c r="H4" t="n">
         <v>0.001392896082033641</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008630906681908021</v>
+        <v>0.0008630906681908024</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001047289423544866</v>
+        <v>0.001047289423544867</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008692447852773497</v>
+        <v>0.0008692447852773502</v>
       </c>
       <c r="L4" t="n">
         <v>0.00173228437313958</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005961968337054251</v>
+        <v>0.005961968337054292</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003404757856228678</v>
+        <v>0.003404757856228683</v>
       </c>
       <c r="D5" t="n">
-        <v>0.01148262214147353</v>
+        <v>0.01148262214147355</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003404758000335059</v>
+        <v>0.003404758000335063</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003404758000335059</v>
+        <v>0.003404758000335063</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007663966928771969</v>
+        <v>0.007663966928771967</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01513702578167123</v>
+        <v>0.01513702578167122</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003404702508019527</v>
+        <v>0.003404702508019526</v>
       </c>
       <c r="J5" t="n">
-        <v>0.007265012361292491</v>
+        <v>0.007265012361292506</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003514783701008337</v>
+        <v>0.003514783701008349</v>
       </c>
       <c r="L5" t="n">
-        <v>0.007260504885285009</v>
+        <v>0.02314868193608524</v>
       </c>
     </row>
     <row r="6">
@@ -675,16 +675,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001169292996374263</v>
+        <v>0.001169292996374265</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001021513965528589</v>
+        <v>0.001021513965528586</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001459943265224399</v>
+        <v>0.001459944293162347</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001005053013823727</v>
+        <v>0.001005053013823728</v>
       </c>
       <c r="F6" t="n">
         <v>0.001027897893320295</v>
@@ -693,16 +693,16 @@
         <v>0.001403621027752399</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001729587308305658</v>
+        <v>0.001729587308305656</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001028129438207088</v>
+        <v>0.001189747654883771</v>
       </c>
       <c r="J6" t="n">
-        <v>0.00122494763878557</v>
+        <v>0.001375077619662449</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001029723518286959</v>
+        <v>0.001029723518286958</v>
       </c>
       <c r="L6" t="n">
         <v>0.001903171116776317</v>
@@ -718,13 +718,13 @@
         <v>0.001120938739134154</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009798305291761284</v>
+        <v>0.0009798305291761286</v>
       </c>
       <c r="D7" t="n">
         <v>0.001400975097486688</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0009796763854850816</v>
+        <v>0.0009796763854850814</v>
       </c>
       <c r="F7" t="n">
         <v>0.0009796763854850816</v>
@@ -733,13 +733,13 @@
         <v>0.001193648553835607</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001509580594809819</v>
+        <v>0.001509580594809818</v>
       </c>
       <c r="I7" t="n">
         <v>0.0009797751809669771</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001163973936321043</v>
+        <v>0.001163973936321042</v>
       </c>
       <c r="K7" t="n">
         <v>0.0009859292980535241</v>
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001221888211292269</v>
+        <v>0.001221888211292272</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001256383923955319</v>
+        <v>0.001256383923956309</v>
       </c>
       <c r="D8" t="n">
         <v>0.00171407220705916</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001208338562895889</v>
+        <v>0.00120833856289589</v>
       </c>
       <c r="F8" t="n">
         <v>0.001086263943659646</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001470301783071913</v>
+        <v>0.001470301783071911</v>
       </c>
       <c r="H8" t="n">
         <v>0.001786233824046124</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001256428410203281</v>
+        <v>0.001256428410203282</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001440661696353934</v>
+        <v>0.001440661696353933</v>
       </c>
       <c r="K8" t="n">
-        <v>0.001083614982719522</v>
+        <v>0.001083614982719519</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002309159381505374</v>
+        <v>0.002309159381505367</v>
       </c>
     </row>
     <row r="9">
@@ -795,16 +795,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001498714937756751</v>
+        <v>0.001498714937756749</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00151064020052889</v>
+        <v>0.001510640200528889</v>
       </c>
       <c r="D9" t="n">
         <v>0.001931795379681757</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001687237537175906</v>
+        <v>0.001687237537175905</v>
       </c>
       <c r="F9" t="n">
         <v>0.001510640156974167</v>
@@ -813,19 +813,19 @@
         <v>0.001724458225188367</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002040390266162578</v>
+        <v>0.002040390266162576</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00151058485231974</v>
+        <v>0.001510584852319739</v>
       </c>
       <c r="J9" t="n">
         <v>0.001694783607673802</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001428070794965016</v>
+        <v>0.001324042498125414</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002379778557268513</v>
+        <v>0.002379778557268512</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001490192711251397</v>
+        <v>0.0007689484808071735</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001672855341773082</v>
+        <v>0.0008671795162691195</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001539795388426546</v>
+        <v>0.0007715589711880498</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001698542885147366</v>
+        <v>0.0008887852168955772</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001585588259067473</v>
+        <v>0.0007948456512819418</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001575585733242004</v>
+        <v>0.0007734425459503373</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001532844571463772</v>
+        <v>0.000770915078967209</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001558633146106919</v>
+        <v>0.0007725584377720862</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001765781149476128</v>
+        <v>0.000902190443756618</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001712442107942768</v>
+        <v>0.0009174699156924765</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00150250850291529</v>
+        <v>0.0007694685772615342</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001590721646794565</v>
+        <v>0.000740301014516262</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001783547186966441</v>
+        <v>0.0009223497537510784</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001647775000709608</v>
+        <v>0.00075882101293708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00180937510416077</v>
+        <v>0.0009578442943993563</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001696420478080876</v>
+        <v>0.0008027275179346715</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001688941311194977</v>
+        <v>0.0007722569481131663</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001639983902729756</v>
+        <v>0.0007561525666825489</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001669496060238633</v>
+        <v>0.0007659242595312166</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001884832036276117</v>
+        <v>0.0009958805975753987</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001819996938865391</v>
+        <v>0.0009988200488595641</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001604886342061262</v>
+        <v>0.0007449491547404674</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006966513093931535</v>
+        <v>0.0006966513093931541</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007288347455321233</v>
+        <v>0.0007288347455321238</v>
       </c>
       <c r="D4" t="n">
         <v>0.0007261379991300533</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007312858129851609</v>
+        <v>0.0007312858129851614</v>
       </c>
       <c r="F4" t="n">
         <v>0.0007312858129851611</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007471143372480536</v>
+        <v>0.000747114337248054</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007220258917304416</v>
+        <v>0.0007220258917304421</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000735483520340774</v>
+        <v>0.0007354835203407746</v>
       </c>
       <c r="J4" t="n">
         <v>0.0007699535138905687</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007244568906054769</v>
+        <v>0.000724456890605477</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007040041084484814</v>
+        <v>0.0007040041084484815</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001013886609608379</v>
+        <v>0.001013886609608378</v>
       </c>
       <c r="C5" t="n">
-        <v>0.00165997260977666</v>
+        <v>0.001659972609776661</v>
       </c>
       <c r="D5" t="n">
         <v>0.001477779979005644</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001659972801619339</v>
+        <v>0.00165997280161934</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001659972801619339</v>
+        <v>0.00165997280161934</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00185003117423862</v>
+        <v>0.001850031174238609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001513689301603488</v>
+        <v>0.00151368930160349</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001659963557621235</v>
+        <v>0.001659963557621236</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002328701978039853</v>
+        <v>0.002328701978039858</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001428794027620178</v>
+        <v>0.001428794027620177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001212919401791342</v>
+        <v>0.001212919401791343</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009376123658623435</v>
+        <v>0.0008302115416042471</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008674758936843676</v>
+        <v>0.000867475893684366</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000969017081393014</v>
+        <v>0.0009690170813930138</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008535240895618781</v>
+        <v>0.0008535240895618769</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008689749496148797</v>
+        <v>0.0008689749496148801</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008806745694591476</v>
+        <v>0.0009880753937172434</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009692052935010425</v>
+        <v>0.0009692052935010427</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008690437525518674</v>
+        <v>0.0008690437525518675</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001013152673144083</v>
+        <v>0.0009132983577968541</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008580517143916922</v>
+        <v>0.0008580517143917012</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008375696602074936</v>
+        <v>0.0008375696602074938</v>
       </c>
     </row>
     <row r="7">
@@ -1111,31 +1111,31 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007752871244924751</v>
+        <v>0.0007752871244924755</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008141283875955185</v>
+        <v>0.0008141283875955188</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008047649263518174</v>
+        <v>0.0008047649263518175</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008140064599480379</v>
+        <v>0.0008140064599480381</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008140064599480379</v>
+        <v>0.0008140064599480381</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008257501523473755</v>
+        <v>0.0008257501523473758</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008006617068297635</v>
+        <v>0.0008006617068297639</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008141193354400958</v>
+        <v>0.0008141193354400965</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008485893289898903</v>
+        <v>0.0008485893289898907</v>
       </c>
       <c r="K7" t="n">
         <v>0.0008030927057047988</v>
@@ -1151,34 +1151,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008419523164151991</v>
+        <v>0.0008419523164151998</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001000756680776125</v>
+        <v>0.001000756680776755</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001016376411488891</v>
+        <v>0.00101637641148889</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009679320513043164</v>
+        <v>0.000967932051304317</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008845314720357356</v>
+        <v>0.0008845314720357363</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001012460586590718</v>
+        <v>0.001012460586590719</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009873721410731014</v>
+        <v>0.0009873721410731025</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001000829769683439</v>
+        <v>0.00100082976968344</v>
       </c>
       <c r="J8" t="n">
         <v>0.001035323355548235</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008675279956211984</v>
+        <v>0.0008675279956211986</v>
       </c>
       <c r="L8" t="n">
         <v>0.001094747651401418</v>
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008978616203881675</v>
+        <v>0.0008978616203881679</v>
       </c>
       <c r="C9" t="n">
         <v>0.001004414947536662</v>
@@ -1200,13 +1200,13 @@
         <v>0.0009950604307272812</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001082553462168171</v>
+        <v>0.001082553462168172</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001004415127764574</v>
+        <v>0.001004415127764575</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001016036712288519</v>
+        <v>0.001016036712288518</v>
       </c>
       <c r="H9" t="n">
         <v>0.0009909482667709072</v>
@@ -1215,13 +1215,13 @@
         <v>0.001004405895381239</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001038875888931034</v>
+        <v>0.001038875888931033</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009541466535999027</v>
+        <v>0.0009541466535999032</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009729264834889468</v>
+        <v>0.0009729264834889467</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001617191545522628</v>
+        <v>0.0008162643829117077</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001624422352944587</v>
+        <v>0.000779861743084333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001800215756712903</v>
+        <v>0.0008258965836312897</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001595929616741028</v>
+        <v>0.0007762039579994248</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001595929616741028</v>
+        <v>0.0007762840608603351</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001761579788935728</v>
+        <v>0.0008238632493843896</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00203895412367625</v>
+        <v>0.0008383285814772392</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001645605080487307</v>
+        <v>0.0008177669792647081</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002061416820095612</v>
+        <v>0.0009041797697259697</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001732291575321202</v>
+        <v>0.0008961261929123771</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001876142676648459</v>
+        <v>0.0008298768463585903</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001721987442610255</v>
+        <v>0.0008463591664873166</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001737176115118068</v>
+        <v>0.0008021772755220224</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001932503198830202</v>
+        <v>0.0009149501712099669</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001705014117908087</v>
+        <v>0.000788533371476109</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001705014117908087</v>
+        <v>0.0007886134743370192</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001888063832469838</v>
+        <v>0.0009006052535841562</v>
       </c>
       <c r="H3" t="n">
-        <v>0.00220733528968763</v>
+        <v>0.001005561251957441</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001754709338920543</v>
+        <v>0.0008570756528692436</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002220506366659265</v>
+        <v>0.001096004726483324</v>
       </c>
       <c r="K3" t="n">
-        <v>0.00184015886730494</v>
+        <v>0.0009840732518662252</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002019826436917582</v>
+        <v>0.0009444315969220547</v>
       </c>
     </row>
     <row r="4">
@@ -1393,31 +1393,31 @@
         <v>0.0007609564817462417</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008516085541111023</v>
+        <v>0.0008516085541111027</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007544642571965637</v>
+        <v>0.0007544642571965635</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007544642571965637</v>
+        <v>0.0007544642571965636</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008282598733038883</v>
+        <v>0.0008282598733038891</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009934751825057175</v>
+        <v>0.0009934751825057177</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007572926141965779</v>
+        <v>0.0007572926141965778</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009576801722601027</v>
+        <v>0.0009576801722601029</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007549637236541304</v>
+        <v>0.0007549637236541305</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008967386337909161</v>
+        <v>0.0008967386337909163</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001752674738452496</v>
+        <v>0.001752674738452498</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002364157893986158</v>
+        <v>0.002364157893986159</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003693707721550134</v>
+        <v>0.003693707721550132</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002062022521416695</v>
+        <v>0.002062022521416693</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002062022521416695</v>
+        <v>0.002062022521416693</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0033571551452966</v>
+        <v>0.003357155145296583</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006936767293945805</v>
+        <v>0.006936767293945803</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002061999651857643</v>
+        <v>0.002061999651857636</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005839895392467594</v>
+        <v>0.005839895392467588</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001969967769906914</v>
+        <v>0.001969967769906913</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005070683104814434</v>
+        <v>0.005070683104814427</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008832788790938815</v>
+        <v>0.001005430836864267</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009114967566058753</v>
+        <v>0.000911496756605876</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009937890808401006</v>
+        <v>0.000993789849391207</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008803037291570069</v>
+        <v>0.0008803037291570067</v>
       </c>
       <c r="F6" t="n">
         <v>0.0008976192074593928</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001090882294215973</v>
+        <v>0.0009687303364455872</v>
       </c>
       <c r="H6" t="n">
         <v>0.001265602745068647</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001019915035108662</v>
+        <v>0.000897763077338276</v>
       </c>
       <c r="J6" t="n">
         <v>0.001221925047054791</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008927893717145603</v>
+        <v>0.0008927893717145606</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001037778018250316</v>
+        <v>0.001037778018250317</v>
       </c>
     </row>
     <row r="7">
@@ -1507,19 +1507,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008343819420351964</v>
+        <v>0.0008343819420351967</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008662268983602556</v>
+        <v>0.0008662268983602555</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009431734347636725</v>
+        <v>0.0009431734347636729</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008491299861300391</v>
+        <v>0.0008491299861300385</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008491299861300391</v>
+        <v>0.0008491299861300385</v>
       </c>
       <c r="G7" t="n">
         <v>0.0009198333993869029</v>
@@ -1528,16 +1528,16 @@
         <v>0.001085048708588731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008488661402795912</v>
+        <v>0.0008488661402795913</v>
       </c>
       <c r="J7" t="n">
         <v>0.001049253698343117</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000846537249737144</v>
+        <v>0.0008465372497371443</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009883121598739302</v>
+        <v>0.0009883121598739304</v>
       </c>
     </row>
     <row r="8">
@@ -1547,22 +1547,22 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0009130623530590341</v>
+        <v>0.0009130623530590353</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001084693285792964</v>
+        <v>0.001084693285792965</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001190310134595332</v>
+        <v>0.001190310134595333</v>
       </c>
       <c r="E8" t="n">
         <v>0.001029168223954927</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009321408290439609</v>
+        <v>0.0009321408290439613</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001138031543052472</v>
+        <v>0.001138031543052475</v>
       </c>
       <c r="H8" t="n">
         <v>0.001303246852254464</v>
@@ -1574,7 +1574,7 @@
         <v>0.001267479261217618</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009226260472503432</v>
+        <v>0.0009226260472503441</v>
       </c>
       <c r="L8" t="n">
         <v>0.001352248241546477</v>
@@ -1617,7 +1617,7 @@
         <v>0.001076122864805661</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001271077256717776</v>
+        <v>0.001271077256717777</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001559417185777966</v>
+        <v>0.0008034242888443013</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001575610611200636</v>
+        <v>0.0007709002585494961</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001711839185112802</v>
+        <v>0.00081144595593482</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001546923216764795</v>
+        <v>0.000768804916531312</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001546923216764795</v>
+        <v>0.000768885155955684</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001662604271263257</v>
+        <v>0.000808854820207333</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001783750233240226</v>
+        <v>0.000815032253891839</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001590201785409731</v>
+        <v>0.0008050522811759177</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001911276859462251</v>
+        <v>0.0008949070679053655</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001670012306872454</v>
+        <v>0.0008887204059936061</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00163069448533306</v>
+        <v>0.0008070680352744942</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001657810667741961</v>
+        <v>0.0008164647262343844</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001682663089327617</v>
+        <v>0.0007799837049975878</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001833127541099064</v>
+        <v>0.0008736131748819454</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001649963199128392</v>
+        <v>0.0007683250167478369</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001649963199128392</v>
+        <v>0.0007684052561722081</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001776497191190409</v>
+        <v>0.000855245823439022</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001916065071934505</v>
+        <v>0.0009010439795337517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001693462970021778</v>
+        <v>0.0008280933209979948</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002048466392587468</v>
+        <v>0.001042169501005002</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001769707993700483</v>
+        <v>0.0009597806610724263</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001739791940525136</v>
+        <v>0.0008434666933363907</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007071109476301037</v>
+        <v>0.0007071109476301048</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007303527325139781</v>
+        <v>0.0007303527325139783</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007977193675666789</v>
+        <v>0.0007977193675666794</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00073277088567054</v>
+        <v>0.0007327708856705403</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007327708856705402</v>
+        <v>0.0007327708856705404</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007681119049705942</v>
+        <v>0.0007681119049705948</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008404501480123987</v>
+        <v>0.0008404501480123989</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000723286249388649</v>
+        <v>0.0007232862493886493</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008606496345902495</v>
+        <v>0.0008606496345902501</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007122645346316782</v>
+        <v>0.0007122645346316788</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007495071552764042</v>
+        <v>0.0007495071552764044</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001189045679814624</v>
+        <v>0.001189045679814625</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001819723288601799</v>
+        <v>0.001819723288601803</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002738440809024565</v>
+        <v>0.002738440809024567</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001517027075410957</v>
+        <v>0.001517027075410958</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001517027075410957</v>
+        <v>0.001517027075410958</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002285595097157355</v>
+        <v>0.002285595097157371</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003819659144679897</v>
+        <v>0.003819659144679898</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001517010386064166</v>
+        <v>0.001517010386064167</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00396669326127665</v>
+        <v>0.003966693261276649</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001288438910680704</v>
+        <v>0.001288438910680702</v>
       </c>
       <c r="L5" t="n">
-        <v>0.002106544064004801</v>
+        <v>0.0021065440640048</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009542364694772312</v>
+        <v>0.0009542364694772308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008733377523454794</v>
+        <v>0.0008733377523454759</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001046211041978334</v>
+        <v>0.001046211041978336</v>
       </c>
       <c r="E6" t="n">
         <v>0.0008432858960051085</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008584715285862863</v>
+        <v>0.0008584715285862858</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009024651478401882</v>
+        <v>0.001015237426817721</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001095705710312202</v>
+        <v>0.001095705710312203</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008576394922582419</v>
+        <v>0.000857639492258242</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001005422496414116</v>
+        <v>0.001005422496414117</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008451927122104595</v>
+        <v>0.0008451927122104572</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008834530275291332</v>
+        <v>0.0008834530275291343</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007918975840391573</v>
+        <v>0.0007918975840391579</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008265452711700011</v>
+        <v>0.0008265452711700014</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008824978858495135</v>
+        <v>0.0008824978858495141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008096394361615895</v>
+        <v>0.0008096394361615896</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008096394361615895</v>
+        <v>0.0008096394361615897</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008528985413796474</v>
+        <v>0.0008528985413796483</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009252367844214523</v>
+        <v>0.0009252367844214519</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008080728857977019</v>
+        <v>0.0008080728857977022</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009454362709993015</v>
+        <v>0.0009454362709993035</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007970511710407313</v>
+        <v>0.0007970511710407318</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008342937916854577</v>
+        <v>0.0008342937916854572</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008642620648972405</v>
+        <v>0.0008642620648972402</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001029897722526583</v>
+        <v>0.001029897722525612</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001111188710055022</v>
+        <v>0.001111188710055023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000975870744538003</v>
+        <v>0.0009758707445380025</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008854875119511623</v>
+        <v>0.0008854875119511626</v>
       </c>
       <c r="G8" t="n">
         <v>0.001054734494300654</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001127072737342776</v>
+        <v>0.001127072737342778</v>
       </c>
       <c r="I8" t="n">
         <v>0.001009908838718707</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001147297668740074</v>
+        <v>0.001147297668740073</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008670106528372088</v>
+        <v>0.0008670106528372102</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001171373523373868</v>
+        <v>0.001171373523373867</v>
       </c>
     </row>
     <row r="9">
@@ -1983,7 +1983,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.000934882430483521</v>
+        <v>0.0009348824304835213</v>
       </c>
       <c r="C9" t="n">
         <v>0.001045413407572</v>
@@ -1992,28 +1992,28 @@
         <v>0.001101374189820571</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001114525419888104</v>
+        <v>0.001114525419888105</v>
       </c>
       <c r="F9" t="n">
         <v>0.001026957676362869</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001071766677781645</v>
+        <v>0.001071766677781647</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001144104920823452</v>
+        <v>0.001144104920823451</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0010269410221997</v>
+        <v>0.001026941022199701</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001164304407401299</v>
+        <v>0.001164304407401301</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009719522520202023</v>
+        <v>0.0009719522520202035</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001053161928087454</v>
+        <v>0.001053161928087456</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001509386368156186</v>
+        <v>0.0007776985986412642</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001540398679815981</v>
+        <v>0.0007582078551472506</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001615941892640543</v>
+        <v>0.0007833064042585579</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001487841289153779</v>
+        <v>0.0007536536113134562</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001487841289153779</v>
+        <v>0.0007537341502352622</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001575531489253625</v>
+        <v>0.0007811796849898309</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001621334475864535</v>
+        <v>0.0007833677783631631</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001516941847401348</v>
+        <v>0.000778104279592975</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001691086542761538</v>
+        <v>0.0008337296227810828</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001632132760658254</v>
+        <v>0.0008749103621136205</v>
       </c>
       <c r="L2" t="n">
-        <v>0.00153173523337203</v>
+        <v>0.0007787712032178004</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001611231086021553</v>
+        <v>0.0007781771252442454</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001650778993604956</v>
+        <v>0.000762930728239505</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001733792012088964</v>
+        <v>0.0008181509703740828</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001590843872856487</v>
+        <v>0.0007408128554943722</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001590843872856487</v>
+        <v>0.0007408933944161727</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001687311677204165</v>
+        <v>0.0008030544542391915</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001740212981015543</v>
+        <v>0.000820286878724498</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001620212465867151</v>
+        <v>0.0007811074958157845</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001811272366923898</v>
+        <v>0.0009060055054349054</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001734932686343599</v>
+        <v>0.000940511388439155</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001636934025146603</v>
+        <v>0.0007866360925168007</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006836141607568969</v>
+        <v>0.0006836141607568965</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007076534405288514</v>
+        <v>0.000707653440528851</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007469569049222659</v>
+        <v>0.0007469569049222654</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006950674375885695</v>
+        <v>0.0006950674375885692</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006950674375885695</v>
+        <v>0.0006950674375885692</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007226210896749653</v>
+        <v>0.0007226210896749655</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007501623131855148</v>
+        <v>0.0007501623131855139</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006861563371098329</v>
+        <v>0.0006861563371098323</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007562006558755382</v>
+        <v>0.0007562006558755372</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006873944773113688</v>
+        <v>0.0006873944773113685</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006969243414627317</v>
+        <v>0.0006969243414627313</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008805884294876514</v>
+        <v>0.0008805884294876505</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001503598470040024</v>
+        <v>0.001503598470040023</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001975338560933318</v>
+        <v>0.001975338560933314</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009777499844685032</v>
+        <v>0.0009777499844685006</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009777499844685032</v>
+        <v>0.0009777499844685006</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00159263829886193</v>
+        <v>0.001592638298861918</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002204585638490659</v>
+        <v>0.002204585638490657</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009777353872009319</v>
+        <v>0.0009777353872009306</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002207214282391385</v>
+        <v>0.002207214282391382</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009641867241636928</v>
+        <v>0.0009641867241636896</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001196157191159903</v>
+        <v>0.0011961571911599</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008167373051211132</v>
+        <v>0.0008167373051211127</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008488640325405371</v>
+        <v>0.0008488640325405368</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008805000939663293</v>
+        <v>0.0008804992700611192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000804921878702918</v>
+        <v>0.0008049218787029166</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008199958848388995</v>
+        <v>0.0008199958848388987</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009655923798022985</v>
+        <v>0.0009655923798022969</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001000292797415246</v>
+        <v>0.001000292797415245</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000929127627237165</v>
+        <v>0.000929127627237164</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001000153363680227</v>
+        <v>0.001000153363680225</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008199373710197941</v>
+        <v>0.0008199373710198018</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008293370921409259</v>
+        <v>0.0008293370921409224</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007652075858473108</v>
+        <v>0.0007652075858473103</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007993746200301969</v>
+        <v>0.0007993746200301964</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008285421523101442</v>
+        <v>0.0008285421523101436</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000769602390379381</v>
+        <v>0.0007696023903793804</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000769602390379381</v>
+        <v>0.0007696023903793804</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008042145147653806</v>
+        <v>0.0008042145147653791</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008317557382759289</v>
+        <v>0.0008317557382759281</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007677497622002469</v>
+        <v>0.0007677497622002461</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008377940809659523</v>
+        <v>0.000837794080965952</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000768987902401783</v>
+        <v>0.0007689879024017822</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007785177665531463</v>
+        <v>0.0007785177665531454</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008350068038844876</v>
+        <v>0.0008350068038844877</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009962184881157324</v>
+        <v>0.000996218488116724</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00104957456216977</v>
+        <v>0.001049574562169771</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009301611305666694</v>
+        <v>0.0009301611305666675</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008426352569753665</v>
+        <v>0.0008426352569753659</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009992667233810232</v>
+        <v>0.0009992667233810224</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001026807946891889</v>
+        <v>0.001026807946891888</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009628019708158913</v>
+        <v>0.0009628019708158912</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001032870905346307</v>
+        <v>0.001032870905346304</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008364604818368892</v>
+        <v>0.0008364604818368877</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00110440719727956</v>
+        <v>0.001104407197279556</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008775578720399273</v>
+        <v>0.0008775578720399254</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009780093808993313</v>
+        <v>0.000978009380899329</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001007185139828639</v>
+        <v>0.001007185139828636</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001022890017057246</v>
+        <v>0.001022890017057245</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009463990996603076</v>
+        <v>0.0009463990996603056</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009828492756345142</v>
+        <v>0.0009828492756345111</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001010390499145064</v>
+        <v>0.001010390499145062</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009463845230693821</v>
+        <v>0.0009463845230693799</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001016428841835087</v>
+        <v>0.001016428841835086</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008641586652304996</v>
+        <v>0.0009076590387226993</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009571525274222809</v>
+        <v>0.0009571525274222779</v>
       </c>
     </row>
   </sheetData>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001541534369961888</v>
+        <v>0.0008032721076161871</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001485299617695341</v>
+        <v>0.0007645590420444175</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001663796036425617</v>
+        <v>0.0008097064962909455</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001535596792780807</v>
+        <v>0.0007678804453315182</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001535596792780807</v>
+        <v>0.0007679604625667586</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001666526974569658</v>
+        <v>0.0008098502201413864</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001918939474355035</v>
+        <v>0.0008230106667080461</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001580309815146055</v>
+        <v>0.0008053206860672195</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002034000655356312</v>
+        <v>0.000898860924146045</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00169458047199991</v>
+        <v>0.0008910691752779734</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001845204354413269</v>
+        <v>0.0008193016137717265</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00163575512700634</v>
+        <v>0.00081135057025941</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001577751547273725</v>
+        <v>0.0007446658270455662</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001776381369867538</v>
+        <v>0.0008572062925590257</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001635664457336112</v>
+        <v>0.0007642458304357647</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001635664457336112</v>
+        <v>0.0007643258476710042</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001779522514445316</v>
+        <v>0.0008583180712891005</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002070080399641978</v>
+        <v>0.0009537028229947631</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00168068775554706</v>
+        <v>0.0008259843740703114</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002188772091817945</v>
+        <v>0.001085671381003477</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001796428471512686</v>
+        <v>0.0009709335297072199</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001985025254231036</v>
+        <v>0.0009262115767902446</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000696484552240747</v>
+        <v>0.0006964845522407471</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006750301571116856</v>
+        <v>0.0006750301571116857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007691639322871624</v>
+        <v>0.0007691639322871622</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000721927215042647</v>
+        <v>0.0007219272150426468</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000721927215042647</v>
+        <v>0.0007219272150426469</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007704269471376858</v>
+        <v>0.000770426947137686</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009207883037521312</v>
+        <v>0.0009207883037521313</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007172680954166978</v>
+        <v>0.0007172680954166977</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000936119039101901</v>
+        <v>0.0009361190391019008</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000726670015932566</v>
+        <v>0.0007266700159325661</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008769799597267685</v>
+        <v>0.0008769799597267688</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001004626728103001</v>
+        <v>0.001004626728103</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009120945975726986</v>
+        <v>0.0009120945975726985</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002321152366164199</v>
+        <v>0.002321152366164197</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001440196811255598</v>
+        <v>0.001440196811255592</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001440196811255598</v>
+        <v>0.001440196811255592</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002398076412065068</v>
+        <v>0.002398076412065072</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005588137808200288</v>
+        <v>0.005588137808200289</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001440178201251254</v>
+        <v>0.00144017820125125</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005542595741103659</v>
+        <v>0.005542595741103662</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001564580403539144</v>
+        <v>0.001564580403539147</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004783357071912022</v>
+        <v>0.004783357071912021</v>
       </c>
     </row>
     <row r="6">
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008338502805622346</v>
+        <v>0.000833850280562235</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008223491772367044</v>
+        <v>0.0008223491772367027</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009070025938865399</v>
+        <v>0.0009070017965816472</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008387095873080888</v>
+        <v>0.0008387095873080867</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008550082269515057</v>
+        <v>0.0008550082269515051</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009077926754591744</v>
+        <v>0.0009077926754591738</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001185517404891857</v>
+        <v>0.001185517404891858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008546338237381862</v>
+        <v>0.0009729923800471203</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001193704103893081</v>
+        <v>0.0010843647006495</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008620866912793891</v>
+        <v>0.0008620866912793892</v>
       </c>
       <c r="L6" t="n">
         <v>0.001015024655546426</v>
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007864465415958402</v>
+        <v>0.0007864465415958409</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007798264383017364</v>
+        <v>0.000779826438301737</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000859117530501107</v>
+        <v>0.0008591175305011077</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008095360281298879</v>
+        <v>0.0008095360281298881</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008095360281298879</v>
+        <v>0.0008095360281298881</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008603889364927794</v>
+        <v>0.0008603889364927795</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001010750293107224</v>
+        <v>0.001010750293107225</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008072300847717916</v>
+        <v>0.0008072300847717918</v>
       </c>
       <c r="J7" t="n">
         <v>0.001026081028456995</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000816632005287659</v>
+        <v>0.0008166320052876598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009669419490818617</v>
+        <v>0.0009669419490818625</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008628782161146728</v>
+        <v>0.000862878216114673</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009955713781625928</v>
+        <v>0.0009955713781635528</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001101074593535892</v>
+        <v>0.001101074593535893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009852642302879823</v>
+        <v>0.0009852642302879827</v>
       </c>
       <c r="F8" t="n">
         <v>0.0008893954346677174</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001073911019191717</v>
+        <v>0.001073911019191718</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001224272375806092</v>
+        <v>0.001224272375806093</v>
       </c>
       <c r="I8" t="n">
         <v>0.00102075216747073</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001239630053312123</v>
+        <v>0.001239630053312124</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008905171550953569</v>
+        <v>0.0008905171550953576</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001323666426404479</v>
+        <v>0.00132366642640448</v>
       </c>
     </row>
     <row r="9">
@@ -2775,7 +2775,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00095770928082627</v>
+        <v>0.0009577092808262696</v>
       </c>
       <c r="C9" t="n">
         <v>0.001036984240051356</v>
@@ -2787,13 +2787,13 @@
         <v>0.001163527542639766</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001064406441463069</v>
+        <v>0.001064406441463068</v>
       </c>
       <c r="G9" t="n">
         <v>0.001117546738242399</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001267908094856843</v>
+        <v>0.001267908094856844</v>
       </c>
       <c r="I9" t="n">
         <v>0.001064387886521411</v>
@@ -2802,7 +2802,7 @@
         <v>0.001283238830206614</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009656325813448261</v>
+        <v>0.001024021886327044</v>
       </c>
       <c r="L9" t="n">
         <v>0.001224099750831483</v>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001511859679359501</v>
+        <v>0.0007849064117542194</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00147667477660951</v>
+        <v>0.0007554591343105815</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001522279071660818</v>
+        <v>0.0007854547636764588</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001508429143775071</v>
+        <v>0.000758299099092796</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001508429143775071</v>
+        <v>0.0007583792514622408</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001531649396243409</v>
+        <v>0.0007859479052482762</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001539832324635501</v>
+        <v>0.0007861468924884548</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001542026654739009</v>
+        <v>0.0007865029099869117</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001747715425104546</v>
+        <v>0.0008767584381567565</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001629637972012708</v>
+        <v>0.0008787347528041047</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001550877685155771</v>
+        <v>0.0007869123402140799</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001604286065553182</v>
+        <v>0.0007856422161695144</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001568943973507749</v>
+        <v>0.0007372525650494437</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00161627052507031</v>
+        <v>0.0007895834707826484</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001605412142141986</v>
+        <v>0.0007505663789977277</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001605412142141986</v>
+        <v>0.0007506465313671723</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001627048339397181</v>
+        <v>0.0007931178206643688</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001636684796873869</v>
+        <v>0.0007960571910790863</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001639454257161999</v>
+        <v>0.0007970581808370152</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001860266051910873</v>
+        <v>0.0009760268559914991</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001722874727525549</v>
+        <v>0.0009421144984479434</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001649158113887738</v>
+        <v>0.0008004340905720332</v>
       </c>
     </row>
     <row r="4">
@@ -2971,13 +2971,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006803359845698502</v>
+        <v>0.0006803359845698505</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006683488434830096</v>
+        <v>0.0006683488434830097</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006865298717858792</v>
+        <v>0.0006865298717858791</v>
       </c>
       <c r="E4" t="n">
         <v>0.0007107744551970254</v>
@@ -2986,22 +2986,22 @@
         <v>0.0007107744551970254</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006917974174834343</v>
+        <v>0.0006917974174834342</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0006969730304543958</v>
+        <v>0.000696973030454396</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000696398538662093</v>
+        <v>0.0006963985386620926</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007599793860824258</v>
+        <v>0.000759979386082426</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006835430903832594</v>
+        <v>0.0006835430903832593</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007035387743785638</v>
+        <v>0.0007035387743785641</v>
       </c>
     </row>
     <row r="5">
@@ -3011,34 +3011,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008402151960252735</v>
+        <v>0.0008402151960252739</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008625292417746179</v>
+        <v>0.0008625292417746174</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009640878389632488</v>
+        <v>0.0009640878389632487</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001168429978530846</v>
+        <v>0.001168429978530845</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001168429978530846</v>
+        <v>0.001168429978530845</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001069960578954451</v>
+        <v>0.001069960578954449</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001204560585321703</v>
+        <v>0.001204560585321701</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00116842480510813</v>
+        <v>0.001168424805108132</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002291393464968044</v>
+        <v>0.002291393464968045</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009143976482436264</v>
+        <v>0.0009143976482436257</v>
       </c>
       <c r="L5" t="n">
         <v>0.001343566987765076</v>
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008115718919619306</v>
+        <v>0.0008115718919619312</v>
       </c>
       <c r="C6" t="n">
         <v>0.0008084697037160128</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000817282303102742</v>
+        <v>0.0009266985396286188</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008151353967313108</v>
+        <v>0.0008151353967313104</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008288426191024943</v>
+        <v>0.0008288426191024945</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009310902348593727</v>
+        <v>0.0008230333248755149</v>
       </c>
       <c r="H6" t="n">
         <v>0.0009428525608795766</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009356913560380311</v>
+        <v>0.0009356913560380316</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009009636791209655</v>
+        <v>0.001000051142231937</v>
       </c>
       <c r="K6" t="n">
         <v>0.0008142955324059952</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008342303464087111</v>
+        <v>0.0008342303464087112</v>
       </c>
     </row>
     <row r="7">
@@ -3091,13 +3091,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007612016437626699</v>
+        <v>0.0007612016437626697</v>
       </c>
       <c r="C7" t="n">
         <v>0.0007609825048294308</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007673875774834581</v>
+        <v>0.000767387577483458</v>
       </c>
       <c r="E7" t="n">
         <v>0.0007800835459772982</v>
@@ -3106,22 +3106,22 @@
         <v>0.0007800835459772982</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007726630766762538</v>
+        <v>0.000772663076676254</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007778386896472154</v>
+        <v>0.0007778386896472151</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007772641978549123</v>
+        <v>0.0007772641978549122</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008408450452752453</v>
+        <v>0.0008408450452752451</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007644087495760787</v>
+        <v>0.0007644087495760785</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007844044335713835</v>
+        <v>0.0007844044335713837</v>
       </c>
     </row>
     <row r="8">
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008298985830997663</v>
+        <v>0.0008298985830997662</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009565041832823949</v>
+        <v>0.000956504183281452</v>
       </c>
       <c r="D8" t="n">
         <v>0.0009859268853198465</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009385610804116493</v>
+        <v>0.0009385610804116483</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008515836641040984</v>
+        <v>0.0008515836641040979</v>
       </c>
       <c r="G8" t="n">
         <v>0.0009654612348503639</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009706368478213853</v>
+        <v>0.0009706368478213849</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009700623560290221</v>
+        <v>0.0009700623560290223</v>
       </c>
       <c r="J8" t="n">
         <v>0.001033667592850847</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008308004450634012</v>
+        <v>0.0008308004450634008</v>
       </c>
       <c r="L8" t="n">
         <v>0.001106836691955783</v>
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008839953344092975</v>
+        <v>0.0008839953344092974</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009527523740721544</v>
+        <v>0.0009527523740721536</v>
       </c>
       <c r="D9" t="n">
         <v>0.0009591654497906629</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001048636329654921</v>
+        <v>0.00104863632965492</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009690392379251258</v>
+        <v>0.0009690392379251257</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009644329459189778</v>
+        <v>0.0009644329459189777</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009696085588899396</v>
+        <v>0.0009696085588899389</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009690340670976362</v>
+        <v>0.0009690340670976358</v>
       </c>
       <c r="J9" t="n">
         <v>0.001032614914517969</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008693252849148683</v>
+        <v>0.0009162135708986334</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009761743028141071</v>
+        <v>0.0009761743028141068</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001486515247377808</v>
+        <v>0.0007600835140207434</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001473051125717154</v>
+        <v>0.0007472794554028429</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00149543373430603</v>
+        <v>0.0007605528762742339</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001485492217682602</v>
+        <v>0.0007473746515701823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001485492217682602</v>
+        <v>0.0007474551477949689</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001494105437576195</v>
+        <v>0.0007604829706555529</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001498774794504713</v>
+        <v>0.0007605008314015023</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001501426580920427</v>
+        <v>0.0007608770205969617</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001584984271364612</v>
+        <v>0.000820515382289043</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00161543952832343</v>
+        <v>0.0008676759125080157</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001491145823430079</v>
+        <v>0.0007602663034642927</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001586430900068636</v>
+        <v>0.0007540720566896588</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001573091770586</v>
+        <v>0.0007336787055430838</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001596689007495092</v>
+        <v>0.0007574524666967067</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001587672640637933</v>
+        <v>0.0007375447942416368</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001587672640637933</v>
+        <v>0.0007376252904664243</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001595161191099943</v>
+        <v>0.0007569685163168242</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001600747414766595</v>
+        <v>0.000758558155741798</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001603974337559425</v>
+        <v>0.0007597674298211181</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001689047544056106</v>
+        <v>0.0008618599019064542</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001715301288313656</v>
+        <v>0.0009316087218730823</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001591751168205358</v>
+        <v>0.0007558589927347042</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006755108416758825</v>
+        <v>0.000675510841675885</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000666145704620068</v>
+        <v>0.0006661457046200681</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006808125042463619</v>
+        <v>0.0006808125042463632</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006933507670463458</v>
+        <v>0.0006933507670463465</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006933507670463461</v>
+        <v>0.0006933507670463465</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006797358940924385</v>
+        <v>0.0006797358940924521</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000682807650052023</v>
+        <v>0.0006828076500520214</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006826117741108868</v>
+        <v>0.0006826117741108855</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0006919254021749803</v>
+        <v>0.0006919254021749817</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006752975567090009</v>
+        <v>0.0006752975567090011</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006782760602575471</v>
+        <v>0.0006782760602575458</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008100450432008508</v>
+        <v>0.0008100450432008541</v>
       </c>
       <c r="C5" t="n">
         <v>0.0008518559774307533</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009196445280266965</v>
+        <v>0.000919644528026697</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009833374241179004</v>
+        <v>0.0009833374241179091</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009833374241179004</v>
+        <v>0.0009833374241179091</v>
       </c>
       <c r="G5" t="n">
         <v>0.0009131494371280025</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009931413054634689</v>
+        <v>0.0009931413054634706</v>
       </c>
       <c r="I5" t="n">
-        <v>0.000983331950597716</v>
+        <v>0.0009833319505977254</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001132076983863157</v>
+        <v>0.001132076983863156</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0008266442122680926</v>
+        <v>0.0008266442122680923</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009116807779232941</v>
+        <v>0.0009116807779232954</v>
       </c>
     </row>
     <row r="6">
@@ -3447,34 +3447,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009139080739916388</v>
+        <v>0.0009139080739916384</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008055762269515686</v>
+        <v>0.0008055762269515682</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008115013214217213</v>
+        <v>0.0008115013214217192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008009986321076048</v>
+        <v>0.0008009986321076061</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008150568635152157</v>
+        <v>0.0008150568635152163</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009181331264081917</v>
+        <v>0.0009181331264081901</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009273010959075849</v>
+        <v>0.0008137682128243909</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008141414037889245</v>
+        <v>0.0009210090064266448</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009309664082870722</v>
+        <v>0.0008328688056170946</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008068814693804371</v>
+        <v>0.0008068814693804229</v>
       </c>
       <c r="L6" t="n">
         <v>0.0008090287017837678</v>
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007539686064334285</v>
+        <v>0.0007539686064334283</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007548576665568513</v>
+        <v>0.0007548576665568515</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007592621538587815</v>
+        <v>0.0007592621538587807</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007633371323835026</v>
+        <v>0.000763337132383503</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007633371323835026</v>
+        <v>0.000763337132383503</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007581936588499812</v>
+        <v>0.0007581936588499823</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007612654148095686</v>
+        <v>0.000761265414809568</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007610695388684339</v>
+        <v>0.000761069538868434</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007703831669325261</v>
+        <v>0.0007703831669325259</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007537553214665466</v>
+        <v>0.0007537553214665445</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007567338250150925</v>
+        <v>0.0007567338250150916</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008210875734168048</v>
+        <v>0.0008210875734168045</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009451389819151877</v>
+        <v>0.000945138981916143</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009724386319922266</v>
+        <v>0.0009724386319922256</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009180388737066104</v>
+        <v>0.0009180388737066105</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008333827283506406</v>
+        <v>0.0008333827283506407</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009462788808429022</v>
+        <v>0.0009462788808429026</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009493506368026675</v>
+        <v>0.0009493506368026678</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009491547608613553</v>
+        <v>0.0009491547608613555</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009584921622204776</v>
+        <v>0.0009584921622204763</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008186272781622991</v>
+        <v>0.0008186272781622976</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001071178415362754</v>
+        <v>0.001071178415362753</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008569020770090084</v>
+        <v>0.0008569020770090086</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009203467666075086</v>
+        <v>0.0009203467666075093</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009247594151673335</v>
+        <v>0.0009247594151673311</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009987520206385819</v>
+        <v>0.0009987520206385823</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009265641096339204</v>
+        <v>0.0009265641096339205</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009236827589006387</v>
+        <v>0.0009236827589006386</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009267545148602264</v>
+        <v>0.0009267545148602275</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009265586389190915</v>
+        <v>0.0009265586389190924</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009358722669831835</v>
+        <v>0.0009358722669831834</v>
       </c>
       <c r="K9" t="n">
-        <v>0.000881528957918231</v>
+        <v>0.0008829994635194184</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00092222292506575</v>
+        <v>0.0009222229250657502</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001526955170351366</v>
+        <v>0.000792196854071122</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001479775951347989</v>
+        <v>0.0007589903763613065</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001549127004071958</v>
+        <v>0.0007933637136430412</v>
       </c>
       <c r="E2" t="n">
-        <v>0.00152591420448741</v>
+        <v>0.0007621565511366872</v>
       </c>
       <c r="F2" t="n">
-        <v>0.00152591420448741</v>
+        <v>0.0007622365204153273</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001576908368541464</v>
+        <v>0.0007948257916768368</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001841253243392557</v>
+        <v>0.0008086439385082116</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001564082618346277</v>
+        <v>0.0007941593666653668</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001689404652523809</v>
+        <v>0.0008727967387203812</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001649683112908661</v>
+        <v>0.0008824559517703033</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001771858391866564</v>
+        <v>0.0008051608752930932</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001619773705800256</v>
+        <v>0.0007974017273270617</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001571227668222211</v>
+        <v>0.0007405223636899553</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001645275907460455</v>
+        <v>0.0008057436405866105</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001624334004374866</v>
+        <v>0.0007586596471920865</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001624334004374863</v>
+        <v>0.0007587396164707232</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001677230231492699</v>
+        <v>0.0008162002306849789</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001981509007728101</v>
+        <v>0.0009159623495837504</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001662898228499142</v>
+        <v>0.0008114229918600963</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001792744662470943</v>
+        <v>0.0009507455072664845</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001744793239331613</v>
+        <v>0.0009508188581781893</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001901447677753575</v>
+        <v>0.0008900770672942056</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000689899048335265</v>
+        <v>0.0006898990483352614</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000670276884035017</v>
+        <v>0.0006702768840350169</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007030792639818644</v>
+        <v>0.0007030792639818625</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007161956948354449</v>
+        <v>0.0007161956948354447</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007161956948354449</v>
+        <v>0.0007161956948354447</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007192611502649907</v>
+        <v>0.0007192611502649889</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008766853250888531</v>
+        <v>0.0008766853250888505</v>
       </c>
       <c r="I4" t="n">
         <v>0.0007098944815853273</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007315386825503994</v>
+        <v>0.000731538682550397</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006989682153941662</v>
+        <v>0.0006989682153941663</v>
       </c>
       <c r="L4" t="n">
-        <v>0.000835453019109249</v>
+        <v>0.0008354530191092485</v>
       </c>
     </row>
     <row r="5">
@@ -3803,34 +3803,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009455010584602747</v>
+        <v>0.0009455010584602751</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008816037166826233</v>
+        <v>0.0008816037166826228</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00119852834595505</v>
+        <v>0.001198528345955046</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001364085746608262</v>
+        <v>0.00136408574660821</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001364085746608262</v>
+        <v>0.00136408574660821</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001517510569253254</v>
+        <v>0.001517510569253237</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004766985909111452</v>
+        <v>0.00476698590911145</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001364077182603154</v>
+        <v>0.001364077182603116</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001761175401740791</v>
+        <v>0.001761175401740788</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001126896164334649</v>
+        <v>0.001126896164334653</v>
       </c>
       <c r="L5" t="n">
         <v>0.003999418966828196</v>
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008244446217777463</v>
+        <v>0.0008244446217777428</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008156446598777195</v>
+        <v>0.0008156446598777188</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008370233362165729</v>
+        <v>0.0008370233362165731</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008298977000022521</v>
+        <v>0.0008298977000022512</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008449822273774445</v>
+        <v>0.0008449822273774442</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009700711907898215</v>
+        <v>0.0008538067237074705</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001135855105056554</v>
+        <v>0.001135855105056556</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000960704522110162</v>
+        <v>0.0008444400550278076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009838055063691202</v>
+        <v>0.0008756329741489338</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008317646142536774</v>
+        <v>0.0008317646142536714</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009704555300501377</v>
+        <v>0.0009704555300501384</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007769420996140379</v>
+        <v>0.0007769420996140387</v>
       </c>
       <c r="C7" t="n">
         <v>0.0007719425449435512</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007901140179081957</v>
+        <v>0.0007901140179081973</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007995779417762889</v>
+        <v>0.0007995779417762892</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007995779417762889</v>
+        <v>0.0007995779417762892</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008063042015437651</v>
+        <v>0.0008063042015437635</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009637283763676288</v>
+        <v>0.0009637283763676271</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007969375328641026</v>
+        <v>0.0007969375328641024</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008185817338291708</v>
+        <v>0.0008185817338291704</v>
       </c>
       <c r="K7" t="n">
         <v>0.0007860112666729426</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009224960703880214</v>
+        <v>0.0009224960703880217</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008512052118447769</v>
+        <v>0.0008512052118447788</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000982283538952881</v>
+        <v>0.0009822835389519239</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001025599697919416</v>
+        <v>0.001025599697919415</v>
       </c>
       <c r="E8" t="n">
         <v>0.000970497740357964</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008770167707513603</v>
+        <v>0.0008770167707513598</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001014093963532826</v>
+        <v>0.001014093963532825</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00117151813835654</v>
+        <v>0.001171518138356541</v>
       </c>
       <c r="I8" t="n">
         <v>0.001004727294853162</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001026397737588027</v>
+        <v>0.001026397737588022</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008577940528354486</v>
+        <v>0.0008577940528354509</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001269765583326968</v>
+        <v>0.001269765583326964</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009325476843258802</v>
+        <v>0.0009325476843258771</v>
       </c>
       <c r="C9" t="n">
         <v>0.001008161732659006</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001026341522984169</v>
+        <v>0.001026341522984165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001126191632330987</v>
+        <v>0.001126191632330986</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001033165237446541</v>
+        <v>0.00103316523744654</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001042523389259222</v>
+        <v>0.001042523389259219</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001199947564083084</v>
+        <v>0.00119994756408308</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001033156720579558</v>
+        <v>0.001033156720579557</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001054800921544628</v>
+        <v>0.001054800921544626</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009755226246295161</v>
+        <v>0.0009755226246295134</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001158715258103478</v>
+        <v>0.001158715258103477</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001489874514126755</v>
+        <v>0.0007636040907642135</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001477783540857383</v>
+        <v>0.0007539310462914284</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001496808983684854</v>
+        <v>0.0007639690381240902</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001506375252574483</v>
+        <v>0.0007569637105399237</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001506375252574483</v>
+        <v>0.0007570438539092515</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001497465373609843</v>
+        <v>0.0007640035826221472</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001500951123275851</v>
+        <v>0.0007639554027768126</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001515708575495115</v>
+        <v>0.0007649727235907292</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001647760227405584</v>
+        <v>0.0008698674675199501</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00163146467533715</v>
+        <v>0.0008777980519725301</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001492800494595543</v>
+        <v>0.000763694303115533</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001582300161011089</v>
+        <v>0.0007537105224266037</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001569946614311116</v>
+        <v>0.0007377523629657141</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001590276237473945</v>
+        <v>0.000756344270323637</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001602707154329809</v>
+        <v>0.0007503448138126703</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001602707154329809</v>
+        <v>0.0007504249571819969</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001591031221858446</v>
+        <v>0.0007566066841063093</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001595263469293756</v>
+        <v>0.0007577547117254377</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001612572519047104</v>
+        <v>0.0007635018431324406</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001745031828860807</v>
+        <v>0.0009384962107623929</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001724595637330896</v>
+        <v>0.0009435973892772255</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001585659706228187</v>
+        <v>0.0007548609094583018</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006814487451174026</v>
+        <v>0.0006814487451174023</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006688168804272515</v>
+        <v>0.0006688168804272514</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006855709934312922</v>
+        <v>0.0006855709934312918</v>
       </c>
       <c r="E4" t="n">
         <v>0.0007114651241014372</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007114651241014372</v>
+        <v>0.0007114651241014371</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006856648282952754</v>
+        <v>0.0006856648282952735</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0006880429504236416</v>
+        <v>0.0006880429504236414</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006949782676048908</v>
+        <v>0.0006949782676048907</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007006270243394503</v>
+        <v>0.0007006270243394498</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006842400899205705</v>
+        <v>0.00068424008992057</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006832015321396147</v>
+        <v>0.0006832015321396145</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008583864113638122</v>
+        <v>0.0008583864113638105</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008733701075674047</v>
+        <v>0.000873370107567404</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009463757185177593</v>
+        <v>0.0009463757185177574</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001141969711357605</v>
+        <v>0.001141969711357604</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001141969711357605</v>
+        <v>0.001141969711357604</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009612037952155005</v>
+        <v>0.000961203795215471</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001032079274081183</v>
+        <v>0.001032079274081181</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001141965485159323</v>
+        <v>0.001141965485159324</v>
       </c>
       <c r="J5" t="n">
         <v>0.001230423930204111</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009248740616947255</v>
+        <v>0.0009248740616947245</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009452780581577911</v>
+        <v>0.0009452780581577914</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008125698022338824</v>
+        <v>0.0009209549285455071</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008091401565591486</v>
+        <v>0.0008091401565591482</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008162318535318864</v>
+        <v>0.0008162326649512103</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008139561326502226</v>
+        <v>0.0008139561326502221</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008274306259907406</v>
+        <v>0.0008274306259907402</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000816785885411755</v>
+        <v>0.0008167858854117539</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009339370752695117</v>
+        <v>0.0009339370752695108</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000934484451032995</v>
+        <v>0.0009344844510329949</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009409786952007788</v>
+        <v>0.0008411536764194235</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008150368593963413</v>
+        <v>0.0008150368593963377</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000813643483913888</v>
+        <v>0.0008136434839138875</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007620893627545359</v>
+        <v>0.0007620893627545352</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007614629180278686</v>
+        <v>0.0007614629180278684</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007662037303274687</v>
+        <v>0.000766203730327468</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007790283224482699</v>
+        <v>0.0007790283224482691</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007790283224482699</v>
+        <v>0.0007790283224482692</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007663054459324086</v>
+        <v>0.0007663054459324066</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000768683568060775</v>
+        <v>0.0007686835680607742</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007756188852420241</v>
+        <v>0.0007756188852420235</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007812676419765837</v>
+        <v>0.0007812676419765829</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007648807075577036</v>
+        <v>0.0007648807075577029</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000763842149776748</v>
+        <v>0.0007638421497767472</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008303560801225328</v>
+        <v>0.0008303560801225318</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009568688492995338</v>
+        <v>0.0009568688492995328</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009840106181703684</v>
+        <v>0.0009840106181703665</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000936807896163606</v>
+        <v>0.0009368078961636049</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008498517886199929</v>
+        <v>0.0008498517886199923</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009584231451395001</v>
+        <v>0.0009584231451394982</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009608012672678507</v>
+        <v>0.0009608012672678489</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000967736584449115</v>
+        <v>0.000967736584449114</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009734096813998714</v>
+        <v>0.0009734096813998695</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008308468293573113</v>
+        <v>0.0008308468293573105</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001085332555718944</v>
+        <v>0.001085332555718943</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008834448690851353</v>
+        <v>0.0008834448690851344</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009514069300095673</v>
+        <v>0.000951406930009567</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000956155671915966</v>
+        <v>0.0009561556719159636</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001044716848777833</v>
+        <v>0.00104471684877783</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009655671233992998</v>
+        <v>0.0009655671233992965</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009562494579141072</v>
+        <v>0.0009562494579141043</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009586275800424744</v>
+        <v>0.000958627580042472</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009655628972237232</v>
+        <v>0.0009655628972237209</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009712116539582826</v>
+        <v>0.0009712116539582803</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009150842905502265</v>
+        <v>0.0008684595352549005</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009537861617584474</v>
+        <v>0.0009537861617584455</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001479244363425837</v>
+        <v>0.00074745051010869</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001473371460063359</v>
+        <v>0.0007418703781937421</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0014856993280676</v>
+        <v>0.0007477902220771938</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001485511385192965</v>
+        <v>0.0007422870928939157</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001485511385192965</v>
+        <v>0.0007423675913011186</v>
       </c>
       <c r="G2" t="n">
-        <v>0.00148488431376234</v>
+        <v>0.0007477473294930571</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001489071576468461</v>
+        <v>0.0007477399323952425</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001492259569058398</v>
+        <v>0.0007481443161478068</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001584956496414474</v>
+        <v>0.0008155027449351102</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001621136654190257</v>
+        <v>0.0008629602111570324</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001482515368807097</v>
+        <v>0.0007475617832223138</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001578220420931968</v>
+        <v>0.0007426296523659599</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001572298179331193</v>
+        <v>0.0007338247562478932</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001585644967411893</v>
+        <v>0.0007450858049250078</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001586467654752555</v>
+        <v>0.0007380108923384956</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001586467654752555</v>
+        <v>0.0007380913907456989</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001584707532131141</v>
+        <v>0.0007447939553029499</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001589738262024369</v>
+        <v>0.000746200914889793</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001593631485580444</v>
+        <v>0.000747613982244564</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00168777360663408</v>
+        <v>0.0008624071318646683</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001720613011512941</v>
+        <v>0.0009342971709505428</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001581976750809349</v>
+        <v>0.0007439062719419397</v>
       </c>
     </row>
     <row r="4">
@@ -4561,31 +4561,31 @@
         <v>0.0006663411212872212</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006804579513711932</v>
+        <v>0.0006804579513711935</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006945573870817106</v>
+        <v>0.0006945573870817102</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006945573870817106</v>
+        <v>0.0006945573870817103</v>
       </c>
       <c r="G4" t="n">
         <v>0.0006796937743836187</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0006824718126233536</v>
+        <v>0.0006824718126233535</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006826436272777202</v>
+        <v>0.0006826436272777201</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0006918220426805807</v>
+        <v>0.0006918220426805809</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006786007276781712</v>
+        <v>0.0006786007276781716</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006785776499284499</v>
+        <v>0.0006785776499284503</v>
       </c>
     </row>
     <row r="5">
@@ -4595,34 +4595,34 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.000824930698823754</v>
+        <v>0.0008249306988237544</v>
       </c>
       <c r="C5" t="n">
         <v>0.000854742596638057</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009091797231567972</v>
+        <v>0.0009091797231567968</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009786250376274397</v>
+        <v>0.0009786250376274412</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009786250376274397</v>
+        <v>0.0009786250376274412</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009077296428392859</v>
+        <v>0.000907729642839287</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009817105282020286</v>
+        <v>0.0009817105282020283</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009786194407933962</v>
+        <v>0.0009786194407933946</v>
       </c>
       <c r="J5" t="n">
         <v>0.001125568807257448</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0008785574519660552</v>
+        <v>0.0008785574519660554</v>
       </c>
       <c r="L5" t="n">
         <v>0.0009124642042949637</v>
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000808517557311737</v>
+        <v>0.0009157005189651378</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008063158186734894</v>
+        <v>0.0008063158186734896</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008114567569926613</v>
+        <v>0.0008114559177671598</v>
       </c>
       <c r="E6" t="n">
         <v>0.0008015055128124133</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008155245975540465</v>
+        <v>0.0008155245975540467</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009187735449370365</v>
+        <v>0.000811590583283638</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009276044887165304</v>
+        <v>0.0009276044887165306</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009217233978311385</v>
+        <v>0.0008145404361777388</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008331300117788128</v>
+        <v>0.0009316460134965928</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008106845862573176</v>
+        <v>0.0008106845862573184</v>
       </c>
       <c r="L6" t="n">
-        <v>0.000809684689954051</v>
+        <v>0.0008096846899540617</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007549641922684438</v>
+        <v>0.0007549641922684447</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007551669883572764</v>
+        <v>0.0007551669883572761</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007587933209515392</v>
+        <v>0.0007587933209515399</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000763603367742625</v>
+        <v>0.0007636033677426248</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000763603367742625</v>
+        <v>0.0007636033677426248</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007580372182403439</v>
+        <v>0.0007580372182403444</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007608152564800787</v>
+        <v>0.0007608152564800794</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007609870711344461</v>
+        <v>0.0007609870711344459</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007701654865373057</v>
+        <v>0.0007701654865373063</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007569441715348971</v>
+        <v>0.0007569441715348976</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007569210937851751</v>
+        <v>0.0007569210937851756</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008217343022540207</v>
+        <v>0.0008217343022540211</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009452676571106006</v>
+        <v>0.0009452676571096396</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009714217738493682</v>
+        <v>0.0009714217738493677</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009177857437420776</v>
+        <v>0.0009177857437420772</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008331542193379267</v>
+        <v>0.0008331542193379268</v>
       </c>
       <c r="G8" t="n">
-        <v>0.000945608654843266</v>
+        <v>0.0009456086548432662</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009483866930831481</v>
+        <v>0.0009483866930831487</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009485585077373682</v>
+        <v>0.0009485585077373677</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009577606640175701</v>
+        <v>0.0009577606640175711</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000821470334862873</v>
+        <v>0.0008214703348628743</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001070679617241766</v>
+        <v>0.001070679617241767</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008578483880649295</v>
+        <v>0.0008578483880649303</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009206178787829753</v>
+        <v>0.0009206178787829754</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009242523319258475</v>
+        <v>0.0009242523319258473</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009986442366828508</v>
+        <v>0.000998644236682851</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009264435563823982</v>
+        <v>0.0009264435563823973</v>
       </c>
       <c r="G9" t="n">
         <v>0.0009234881086660435</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009262661469057779</v>
+        <v>0.0009262661469057778</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009264379615601443</v>
+        <v>0.0009264379615601444</v>
       </c>
       <c r="J9" t="n">
         <v>0.0009356163769630049</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008846729271209492</v>
+        <v>0.0008846729271209506</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009223719842108743</v>
+        <v>0.0009223719842108744</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001853525320896992</v>
+        <v>0.0008189702122502112</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001755699520896561</v>
+        <v>0.0009220846881111005</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001921019027944808</v>
+        <v>0.0008225222719988376</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001793186912382998</v>
+        <v>0.0009537131105051964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001642856708148209</v>
+        <v>0.0008286632392175996</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001922034701607579</v>
+        <v>0.0008225757248864197</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002473945125575532</v>
+        <v>0.000851591763618782</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001616076413844758</v>
+        <v>0.0008064792180369409</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002223490261563301</v>
+        <v>0.001003794174675506</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001848648737916645</v>
+        <v>0.0009571411087426632</v>
       </c>
       <c r="L2" t="n">
-        <v>0.003115606595450202</v>
+        <v>0.0008861341994380921</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.002005302273724726</v>
+        <v>0.000893358582142787</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001871656444381811</v>
+        <v>0.0009958553665298626</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002082934018109011</v>
+        <v>0.0009188079697645677</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001909312954284283</v>
+        <v>0.001047677570620918</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001758982750049494</v>
+        <v>0.0008412075493055741</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002084102253217363</v>
+        <v>0.0009193859724446193</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002719133340530405</v>
+        <v>0.001128177813546975</v>
       </c>
       <c r="I3" t="n">
-        <v>0.00173205484575565</v>
+        <v>0.000804575381894674</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002398985382465869</v>
+        <v>0.001244675456427499</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001973026910130956</v>
+        <v>0.001069151584754229</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003456896857123951</v>
+        <v>0.001372075935252812</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009224663764832407</v>
+        <v>0.0009224663764832424</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007663515836492992</v>
+        <v>0.0007663515836492989</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009625885253721971</v>
+        <v>0.0009625885253721976</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007694322283103003</v>
+        <v>0.0007694322283103002</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007694322283103003</v>
+        <v>0.0007694322283103002</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009627804142822715</v>
+        <v>0.0009627804142822729</v>
       </c>
       <c r="H4" t="n">
         <v>0.001291163538901472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007786752118676564</v>
+        <v>0.0007786752118676561</v>
       </c>
       <c r="J4" t="n">
-        <v>0.001016333052969893</v>
+        <v>0.001016333052969894</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008140333614268283</v>
+        <v>0.0008140333614268284</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001672474408458694</v>
+        <v>0.001672474408458695</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.004596441675275048</v>
+        <v>0.00459644167527508</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002129401608653941</v>
+        <v>0.002129401608653938</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005409659406127386</v>
+        <v>0.005409659406127385</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00212940190824946</v>
+        <v>0.002129401908249456</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00212940190824946</v>
+        <v>0.002129401908249456</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005529951314476326</v>
+        <v>0.005529951314476333</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01261169749910948</v>
+        <v>0.01261169749910946</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002129352984894604</v>
+        <v>0.002129352984894602</v>
       </c>
       <c r="J5" t="n">
-        <v>0.006726477619423251</v>
+        <v>0.006726477619423252</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002759825400090312</v>
+        <v>0.002759825400090329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006536886143663441</v>
+        <v>0.006536886143663435</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001206816796032462</v>
+        <v>0.001069033624856967</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009185855138767905</v>
+        <v>0.0009185855138767896</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001111637990259855</v>
+        <v>0.001111638614804956</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009037784787267204</v>
+        <v>0.00090377847872672</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009243875132152264</v>
+        <v>0.000924387513215226</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00124713083383149</v>
+        <v>0.001109347662655996</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00158417084791722</v>
+        <v>0.001584170847917221</v>
       </c>
       <c r="I6" t="n">
         <v>0.001063025631416876</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001302900502564928</v>
+        <v>0.001174467296074853</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009566900432216441</v>
+        <v>0.0009566900432216414</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001824200518924629</v>
+        <v>0.00182420051892463</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001021642191131543</v>
+        <v>0.001021642191131544</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008778996502752942</v>
+        <v>0.0008778996502752941</v>
       </c>
       <c r="D7" t="n">
         <v>0.001061754802168117</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008777505040784678</v>
+        <v>0.0008777505040784674</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008777505040784678</v>
+        <v>0.0008777505040784674</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001061956228930573</v>
+        <v>0.001061956228930574</v>
       </c>
       <c r="H7" t="n">
         <v>0.001390339353549775</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008778510265159576</v>
+        <v>0.000877851026515958</v>
       </c>
       <c r="J7" t="n">
         <v>0.001115508867618196</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009132091760751298</v>
+        <v>0.0009132091760751305</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001771650223106996</v>
+        <v>0.001771650223106995</v>
       </c>
     </row>
     <row r="8">
@@ -5111,10 +5111,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001107212689752735</v>
+        <v>0.001107212689752737</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001113518452312385</v>
+        <v>0.001113518452313253</v>
       </c>
       <c r="D8" t="n">
         <v>0.001328619280022972</v>
@@ -5123,7 +5123,7 @@
         <v>0.001072462515833129</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009681465061251662</v>
+        <v>0.0009681465061251657</v>
       </c>
       <c r="G8" t="n">
         <v>0.001297676612214279</v>
@@ -5135,13 +5135,13 @@
         <v>0.001113571409799663</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001351258759633387</v>
+        <v>0.001351258759633388</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009959905635034399</v>
+        <v>0.0009959905635034412</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002164214716228718</v>
+        <v>0.002164214716228716</v>
       </c>
     </row>
     <row r="9">
@@ -5151,37 +5151,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001258979687133264</v>
+        <v>0.001258979687133266</v>
       </c>
       <c r="C9" t="n">
         <v>0.001222562331772346</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001406427041048065</v>
+        <v>0.001406427041048066</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001346413435015252</v>
+        <v>0.001346413435015253</v>
       </c>
       <c r="F9" t="n">
         <v>0.001222562469441224</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001406618910427625</v>
+        <v>0.001406618910427626</v>
       </c>
       <c r="H9" t="n">
         <v>0.001735002035046828</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001222513708013012</v>
+        <v>0.001222513708013011</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001460171549115249</v>
+        <v>0.00146017154911525</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001195687231812268</v>
+        <v>0.001195687231812269</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002116312904604051</v>
+        <v>0.002116312904604052</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001767037018123875</v>
+        <v>0.0008118622111206691</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001767156118684155</v>
+        <v>0.0009201713354569388</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00190762477457656</v>
+        <v>0.0008192610655129993</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001805304097632186</v>
+        <v>0.0009523284555193418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001653643305873263</v>
+        <v>0.0008261711522222978</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001891032719702479</v>
+        <v>0.0008183878586194525</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002306362500485441</v>
+        <v>0.0008401461350272102</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001627502030467487</v>
+        <v>0.0008045245544326208</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002081747129094185</v>
+        <v>0.0009946745664093125</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001842952741042702</v>
+        <v>0.000954182100584842</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002991418820763652</v>
+        <v>0.0008769783442692357</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001905622184973182</v>
+        <v>0.0008597597708565018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001884637509123376</v>
+        <v>0.0009987968525911601</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002067327227559781</v>
+        <v>0.0009123328401993659</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001922946644500402</v>
+        <v>0.001051518893477591</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001771285852741479</v>
+        <v>0.0008432207823422734</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002048242927420778</v>
+        <v>0.0009063294645801733</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002526167544441188</v>
+        <v>0.001063663333129732</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0017450189473151</v>
+        <v>0.0008074754546423271</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002235578124278048</v>
+        <v>0.001191237792244451</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001966294540387279</v>
+        <v>0.001065363941664081</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003313858918824019</v>
+        <v>0.001323907659104364</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008674938961226247</v>
+        <v>0.0008674938961226255</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007726897089311887</v>
+        <v>0.0007726897089311892</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009510673601251693</v>
+        <v>0.0009510673601251701</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007754168415698208</v>
+        <v>0.000775416841569821</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007754168415698208</v>
+        <v>0.000775416841569821</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009408227078983256</v>
+        <v>0.0009408227078983272</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001188015368714944</v>
+        <v>0.001188015368714943</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007821152747771138</v>
+        <v>0.000782115274777114</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009278305642639298</v>
+        <v>0.0009278305642639297</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008071669669256027</v>
+        <v>0.0008071669669256028</v>
       </c>
       <c r="L4" t="n">
         <v>0.001595111467626416</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003563330614436491</v>
+        <v>0.003563330614436495</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002138968498426324</v>
+        <v>0.002138968498426323</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004920758629004049</v>
+        <v>0.004920758629004072</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002138968741179376</v>
+        <v>0.002138968741179375</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002138968741179376</v>
+        <v>0.002138968741179375</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004864470550606143</v>
+        <v>0.004864470550606161</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009996091732606162</v>
+        <v>0.009996091732606141</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002138925646272431</v>
+        <v>0.00213892564627243</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0048410788807476</v>
+        <v>0.004841078880747599</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002486395606260515</v>
+        <v>0.002486395606260521</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006813442862113471</v>
+        <v>0.006813442862113476</v>
       </c>
     </row>
     <row r="6">
@@ -5427,22 +5427,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001134529441999306</v>
+        <v>0.001007054267292327</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009163285463472768</v>
+        <v>0.0009163285463472761</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001093051586949546</v>
+        <v>0.001093051586949555</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009021938084968669</v>
+        <v>0.0009021938084968671</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009210675354636095</v>
+        <v>0.0009210675354636097</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001207858253775006</v>
+        <v>0.001080383079068028</v>
       </c>
       <c r="H6" t="n">
         <v>0.001461791763385957</v>
@@ -5451,13 +5451,13 @@
         <v>0.001049150820653794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001196316623948449</v>
+        <v>0.001078116622847922</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009443150986646375</v>
+        <v>0.0009443150986646379</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001738545462738908</v>
+        <v>0.001738545462738909</v>
       </c>
     </row>
     <row r="7">
@@ -5467,34 +5467,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009583574582032159</v>
+        <v>0.0009583574582032158</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008730216890115959</v>
+        <v>0.0008730216890115962</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001041922001250376</v>
+        <v>0.001041922001250378</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008728507508748231</v>
+        <v>0.0008728507508748235</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008728507508748231</v>
+        <v>0.0008728507508748235</v>
       </c>
       <c r="G7" t="n">
         <v>0.001031686269978917</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001278878930795533</v>
+        <v>0.001278878930795532</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008729788368577042</v>
+        <v>0.0008729788368577044</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001018694126344519</v>
+        <v>0.00101869412634452</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008980305290061929</v>
+        <v>0.0008980305290061936</v>
       </c>
       <c r="L7" t="n">
         <v>0.001685975029707008</v>
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001036290057647528</v>
+        <v>0.001036290057647529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001088291686469913</v>
+        <v>0.001088291686469915</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00128583046926326</v>
+        <v>0.001285830469263262</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001050708184462173</v>
+        <v>0.001050708184462174</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009552151027392983</v>
+        <v>0.0009552151027392989</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001247081951483935</v>
+        <v>0.001247081951483936</v>
       </c>
       <c r="H8" t="n">
         <v>0.001494274612300569</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001088374518362723</v>
+        <v>0.001088374518362724</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001234116823261684</v>
+        <v>0.001234116823261685</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009734096811293635</v>
+        <v>0.0009734096811293641</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002044962394880105</v>
+        <v>0.002044962394880106</v>
       </c>
     </row>
     <row r="9">
@@ -5547,16 +5547,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001149016348277346</v>
+        <v>0.001149016348277347</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001154686871456981</v>
+        <v>0.001154686871456982</v>
       </c>
       <c r="D9" t="n">
         <v>0.001323596135692207</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001259706316573064</v>
+        <v>0.001259706316573065</v>
       </c>
       <c r="F9" t="n">
         <v>0.0011546869882507</v>
@@ -5568,13 +5568,13 @@
         <v>0.001560544113240917</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001154644019303088</v>
+        <v>0.001154644019303089</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001300359308789903</v>
+        <v>0.001300359308789904</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001065102536745422</v>
+        <v>0.001126966321298275</v>
       </c>
       <c r="L9" t="n">
         <v>0.001967640212152389</v>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00172282103652098</v>
+        <v>0.0008049108562669006</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00178411268821582</v>
+        <v>0.0008972774148949569</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001831885750174665</v>
+        <v>0.0008106507155265244</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001810624026539684</v>
+        <v>0.0009197171740228668</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001695229594640822</v>
+        <v>0.0008237469354063073</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001831524756204937</v>
+        <v>0.0008106317171308903</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002065730738877218</v>
+        <v>0.0008227696826700789</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001669055162323656</v>
+        <v>0.0008020880030829855</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001877808047759235</v>
+        <v>0.0009347743587399863</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001813802140432622</v>
+        <v>0.0009479185600269702</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002842647631892852</v>
+        <v>0.0008644710465590122</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001859048075501533</v>
+        <v>0.0008408790835488014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001912128616587982</v>
+        <v>0.0009782636529157573</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001984495088890642</v>
+        <v>0.0008815916619467955</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001938794277909907</v>
+        <v>0.001014996044551077</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001823399846011044</v>
+        <v>0.0008565271749681288</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001984079871045779</v>
+        <v>0.000881683407614436</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002253667338510767</v>
+        <v>0.0009701965995840243</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001797161220903894</v>
+        <v>0.0008207612841660563</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002013869987918179</v>
+        <v>0.001055404717724103</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001937068975751545</v>
+        <v>0.001052012991811006</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003147028678481581</v>
+        <v>0.001265031391473118</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008422583529563619</v>
+        <v>0.0008422583529563626</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008003148293849525</v>
+        <v>0.0008003148293849535</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009070927037595327</v>
+        <v>0.0009070927037595337</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0008029330791768787</v>
+        <v>0.00080293307917688</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008029330791768787</v>
+        <v>0.0008029330791768801</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009065241199633443</v>
+        <v>0.0009065241199633432</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001046060611194428</v>
+        <v>0.001046060611194429</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008080626959221874</v>
+        <v>0.0008080626959221873</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008416049602648398</v>
+        <v>0.0008416049602648408</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007909672397275013</v>
+        <v>0.0007909672397275019</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001507739973783415</v>
+        <v>0.001507739973783417</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003083126920094061</v>
+        <v>0.00308312692009406</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002531950961388519</v>
+        <v>0.002531950961388523</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004098675397331028</v>
+        <v>0.004098675397331034</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002531951165860378</v>
+        <v>0.002531951165860385</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002531951165860378</v>
+        <v>0.002531951165860385</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004212338178551278</v>
+        <v>0.004212338178551274</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007065407705402079</v>
+        <v>0.007065407705402081</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002531921912600142</v>
+        <v>0.002531921912600154</v>
       </c>
       <c r="J5" t="n">
         <v>0.003320065245145403</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002168880728911761</v>
+        <v>0.002168880728911757</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0164196602760465</v>
+        <v>0.004956211323771136</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009820866852280064</v>
+        <v>0.0009820866852280074</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009444308726259597</v>
+        <v>0.0009444308726259618</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001173529556824729</v>
+        <v>0.001048042507127328</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000930200499605346</v>
+        <v>0.000930200499605345</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009477797591588137</v>
+        <v>0.0009477797591588134</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001046352452234989</v>
+        <v>0.001171792472840739</v>
       </c>
       <c r="H6" t="n">
         <v>0.001317620042728717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001073331048799586</v>
+        <v>0.000947891028193833</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009918378155266909</v>
+        <v>0.001108258965281306</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009289916904707419</v>
+        <v>0.0009289916904707424</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001651765546861949</v>
+        <v>0.00165176554686195</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.00093146853922375</v>
+        <v>0.0009314685392237507</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008973019309779469</v>
+        <v>0.0008973019309779464</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009962939158953499</v>
+        <v>0.0009962939158953492</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008971337915983292</v>
+        <v>0.0008971337915983301</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008971337915983292</v>
+        <v>0.00089713379159833</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009957343062307307</v>
+        <v>0.0009957343062307301</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001135270797461815</v>
+        <v>0.001135270797461816</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008972728821895768</v>
+        <v>0.0008972728821895769</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009308151465322282</v>
+        <v>0.0009308151465322286</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008801774259948894</v>
+        <v>0.0008801774259948896</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001596950160050803</v>
+        <v>0.001596950160050802</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001007145819060261</v>
+        <v>0.001007145819060263</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001107483194805721</v>
+        <v>0.001107483194805722</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001234523400550493</v>
+        <v>0.001234523400550495</v>
       </c>
       <c r="E8" t="n">
         <v>0.001070674868925754</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009771518232365272</v>
+        <v>0.0009771518232365274</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001206038954827587</v>
+        <v>0.001206038954827589</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001345575446058696</v>
+        <v>0.001345575446058697</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001107577530786432</v>
+        <v>0.001107577530786433</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001141146253242978</v>
+        <v>0.001141146253242979</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009533539333406129</v>
+        <v>0.0009533539333406134</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001947884352655682</v>
+        <v>0.001947884352655684</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001092006967629684</v>
+        <v>0.001092006967629683</v>
       </c>
       <c r="C9" t="n">
         <v>0.001139906139168588</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001238907141043482</v>
+        <v>0.001238907141043484</v>
       </c>
       <c r="E9" t="n">
         <v>0.001234608439287886</v>
       </c>
       <c r="F9" t="n">
-        <v>0.00113990625335034</v>
+        <v>0.001139906253350341</v>
       </c>
       <c r="G9" t="n">
         <v>0.001238338514421373</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001377875005652457</v>
+        <v>0.00137787500565246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001139877090380217</v>
+        <v>0.001139877090380218</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00117341935472287</v>
+        <v>0.001173419354722872</v>
       </c>
       <c r="K9" t="n">
         <v>0.001075232417093639</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001839554368241445</v>
+        <v>0.001839554368241448</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001541639268509725</v>
+        <v>0.0007761842492108784</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001670136820266194</v>
+        <v>0.0008910747504161828</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001603510841359241</v>
+        <v>0.0007794404272031075</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0017063131639861</v>
+        <v>0.0009214419917416661</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001559709950036548</v>
+        <v>0.0007994941768644828</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001629237820389989</v>
+        <v>0.0007807943870115982</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00180354153722295</v>
+        <v>0.0007898002923994885</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001530868482842993</v>
+        <v>0.0007756247554492449</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001963757706751243</v>
+        <v>0.0009589441456548791</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001769959298314756</v>
+        <v>0.0009262342168979159</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001860184035615788</v>
+        <v>0.0007930346006130711</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001646063910390184</v>
+        <v>0.0007617838548868913</v>
       </c>
       <c r="C3" t="n">
-        <v>0.00177281379173176</v>
+        <v>0.0009486692969833048</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001717229035824831</v>
+        <v>0.0007848064490363425</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001809140938401941</v>
+        <v>0.0009985803625043028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001662537724452389</v>
+        <v>0.000797230968050472</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001746820391037842</v>
+        <v>0.0007945466130629718</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001947518506657497</v>
+        <v>0.0008598835264881492</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001633673842282047</v>
+        <v>0.0007578164105158168</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002100660698480509</v>
+        <v>0.001126045970516743</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001882088780652377</v>
+        <v>0.001024135591017872</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002012440196522797</v>
+        <v>0.0008821404317392124</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007298788083360055</v>
+        <v>0.000729878808336006</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007104699910547818</v>
+        <v>0.0007104699910547817</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007666588366741067</v>
+        <v>0.0007666588366741065</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007133764867126173</v>
+        <v>0.0007133764867126172</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007133764867126174</v>
+        <v>0.000713376486712617</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007816187959619914</v>
+        <v>0.0007816187959619916</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008855385257467933</v>
+        <v>0.0008855385257467936</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000721386533546784</v>
+        <v>0.0007213865335467837</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008584146526077679</v>
+        <v>0.0008584146526077681</v>
       </c>
       <c r="K4" t="n">
         <v>0.0007603713726981371</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009192043200943902</v>
+        <v>0.0009192043200943904</v>
       </c>
     </row>
     <row r="5">
@@ -6179,13 +6179,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001542144058547283</v>
+        <v>0.001542144058547292</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001434786420866809</v>
+        <v>0.001434786420866808</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002116942054699263</v>
+        <v>0.002116942054699265</v>
       </c>
       <c r="E5" t="n">
         <v>0.001434786710191527</v>
@@ -6197,19 +6197,19 @@
         <v>0.00244853829738277</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004435614047445926</v>
+        <v>0.004435614047445923</v>
       </c>
       <c r="I5" t="n">
         <v>0.001434766322655493</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004056882176401861</v>
+        <v>0.004056882176401864</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002038675026260251</v>
+        <v>0.002038675026260256</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00547887565894496</v>
+        <v>0.005478875658944961</v>
       </c>
     </row>
     <row r="6">
@@ -6219,28 +6219,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000869339935676214</v>
+        <v>0.0009873166149974063</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008570616329959496</v>
+        <v>0.0008570616329959493</v>
       </c>
       <c r="D6" t="n">
         <v>0.001026890062806341</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008426011241928419</v>
+        <v>0.000842601124192842</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008601049693290354</v>
+        <v>0.0008601049693290353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009210799233022005</v>
+        <v>0.001039056602623392</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001150827325246735</v>
+        <v>0.001025453953195413</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008608476608869928</v>
+        <v>0.0009788243402081842</v>
       </c>
       <c r="J6" t="n">
         <v>0.001118548714831797</v>
@@ -6249,7 +6249,7 @@
         <v>0.0008985886045440948</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001059520160298303</v>
+        <v>0.001059520160298302</v>
       </c>
     </row>
     <row r="7">
@@ -6259,34 +6259,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008160960535636706</v>
+        <v>0.0008160960535636708</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008076238769857648</v>
+        <v>0.0008076238769857641</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008528666842743045</v>
+        <v>0.0008528666842743046</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008074863123508913</v>
+        <v>0.0008074863123508909</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008074863123508913</v>
+        <v>0.000807486312350891</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008678360411896575</v>
+        <v>0.0008678360411896576</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009717557709744605</v>
+        <v>0.00097175577097446</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008076037787744495</v>
+        <v>0.0008076037787744492</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009446318978354339</v>
+        <v>0.0009446318978354335</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008465886179258022</v>
+        <v>0.000846588617925802</v>
       </c>
       <c r="L7" t="n">
         <v>0.001005421565322055</v>
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000890327402148055</v>
+        <v>0.0008903274021480555</v>
       </c>
       <c r="C8" t="n">
         <v>0.001013899436492834</v>
@@ -6308,10 +6308,10 @@
         <v>0.00108664559179529</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009777686984334768</v>
+        <v>0.0009777686984334766</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008859674677982518</v>
+        <v>0.0008859674677982514</v>
       </c>
       <c r="G8" t="n">
         <v>0.001074205792481378</v>
@@ -6323,10 +6323,10 @@
         <v>0.001013973530066171</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001151027618091778</v>
+        <v>0.001151027618091777</v>
       </c>
       <c r="K8" t="n">
-        <v>0.000918365427841193</v>
+        <v>0.0009183654278411937</v>
       </c>
       <c r="L8" t="n">
         <v>0.001349820927459084</v>
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009956805924671954</v>
+        <v>0.0009956805924671956</v>
       </c>
       <c r="C9" t="n">
         <v>0.001073858046065492</v>
@@ -6354,7 +6354,7 @@
         <v>0.001073858278912095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001134070210269385</v>
+        <v>0.001134070210269384</v>
       </c>
       <c r="H9" t="n">
         <v>0.001237989940054187</v>
@@ -6363,7 +6363,7 @@
         <v>0.001073837947854177</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00121086606691516</v>
+        <v>0.001210866066915161</v>
       </c>
       <c r="K9" t="n">
         <v>0.001062617667505202</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001524218697862827</v>
+        <v>0.0007710133796579636</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001699518926753932</v>
+        <v>0.0008890473727665362</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001542950788411308</v>
+        <v>0.000771999212378602</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001736289772667046</v>
+        <v>0.000919875386640291</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001588575969792313</v>
+        <v>0.0007970032386190632</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0015727894623714</v>
+        <v>0.0007735695625247413</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001509922520148557</v>
+        <v>0.0007699721906623126</v>
       </c>
       <c r="I2" t="n">
-        <v>0.00155940657550354</v>
+        <v>0.0007728733626150386</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001875656455369649</v>
+        <v>0.0009514141886859524</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001765204925970586</v>
+        <v>0.0009219111515385043</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001483162624556006</v>
+        <v>0.0007687115005760672</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001626105250774128</v>
+        <v>0.0007528382139408724</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001806574018415058</v>
+        <v>0.0009579960074230395</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001647651035245747</v>
+        <v>0.0007597567864754885</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001843484957188869</v>
+        <v>0.001008715455421559</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001695771154314135</v>
+        <v>0.000805840223173519</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001681971691362546</v>
+        <v>0.0007709546200619675</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001609871937929927</v>
+        <v>0.0007472947651477517</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001666628017922258</v>
+        <v>0.0007659954607696906</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001999142493918723</v>
+        <v>0.0010920279812489</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001876663965620488</v>
+        <v>0.001020117905003368</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001578881856898407</v>
+        <v>0.0007374409431196976</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007164810135788035</v>
+        <v>0.0007164810135788041</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007279624127913857</v>
+        <v>0.0007279624127913858</v>
       </c>
       <c r="D4" t="n">
-        <v>0.000727616447663867</v>
+        <v>0.0007276164476638673</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007304692329726684</v>
+        <v>0.0007304692329726685</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007304692329726684</v>
+        <v>0.0007304692329726685</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007450663490818186</v>
+        <v>0.00074506634908182</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007080070590934115</v>
+        <v>0.0007080070590934116</v>
       </c>
       <c r="I4" t="n">
         <v>0.0007356236510647708</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008019628233139402</v>
+        <v>0.0008019628233139403</v>
       </c>
       <c r="K4" t="n">
         <v>0.0007543649476596339</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006921106905106377</v>
+        <v>0.0006921106905106379</v>
       </c>
     </row>
     <row r="5">
@@ -6578,31 +6578,31 @@
         <v>0.00134755536698899</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001656368084883494</v>
+        <v>0.001656368084883495</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001483682590017367</v>
+        <v>0.001483682590017369</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001656368310251656</v>
+        <v>0.001656368310251658</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001656368310251656</v>
+        <v>0.001656368310251658</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00179202134798891</v>
+        <v>0.001792021347988922</v>
       </c>
       <c r="H5" t="n">
         <v>0.001250439713793767</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001656359561076434</v>
+        <v>0.001656359561076433</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002800087987075723</v>
+        <v>0.002800087987075722</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001911112576618848</v>
+        <v>0.001911112576618846</v>
       </c>
       <c r="L5" t="n">
         <v>0.001386087491829733</v>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009563945512613736</v>
+        <v>0.0009563945512613733</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008666589807745537</v>
+        <v>0.0008666589807745534</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008603515399084106</v>
+        <v>0.0008603522150580887</v>
       </c>
       <c r="E6" t="n">
         <v>0.0008528158056921964</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008682754151261458</v>
+        <v>0.000868275415126146</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000878118031499354</v>
+        <v>0.0009849798867643876</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008402818424495257</v>
+        <v>0.0009531522928008321</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008686753334823062</v>
+        <v>0.0009755371887473402</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001043436994186778</v>
+        <v>0.0009446540341064929</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008877376893729202</v>
+        <v>0.0008877376893729203</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008241859356270643</v>
+        <v>0.0008241859356270649</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007944682928648022</v>
+        <v>0.0007944682928648023</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008136194541578312</v>
+        <v>0.0008136194541578315</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008055948810885399</v>
+        <v>0.00080559488108854</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008135001358303446</v>
+        <v>0.0008135001358303451</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008135001358303446</v>
+        <v>0.0008135001358303451</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000823053628367817</v>
+        <v>0.0008230536283678184</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007859943383794093</v>
+        <v>0.0007859943383794095</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000813610930350769</v>
+        <v>0.0008136109303507687</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008799501025999376</v>
+        <v>0.0008799501025999381</v>
       </c>
       <c r="K7" t="n">
         <v>0.000832352226945632</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007700979697966354</v>
+        <v>0.0007700979697966358</v>
       </c>
     </row>
     <row r="8">
@@ -6695,16 +6695,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008607153547149948</v>
+        <v>0.0008607153547149951</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009989794870239952</v>
+        <v>0.000998979487023995</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001015759167555024</v>
+        <v>0.001015759167555025</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009663878356031774</v>
+        <v>0.0009663878356031781</v>
       </c>
       <c r="F8" t="n">
         <v>0.0008835789370674227</v>
@@ -6716,13 +6716,13 @@
         <v>0.0009714343453458905</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009990509373172674</v>
+        <v>0.0009990509373172677</v>
       </c>
       <c r="J8" t="n">
         <v>0.001065413534380515</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008963852186476235</v>
+        <v>0.0008963852186476234</v>
       </c>
       <c r="L8" t="n">
         <v>0.001080044974675511</v>
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009347589371369282</v>
+        <v>0.0009347589371369291</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001026266321316024</v>
+        <v>0.001026266321316025</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001018250653201915</v>
+        <v>0.001018250653201916</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001109764136897733</v>
+        <v>0.001109764136897734</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001026266538510412</v>
+        <v>0.001026266538510413</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00103570049552601</v>
+        <v>0.001035700495526011</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009986412055376019</v>
+        <v>0.0009986412055376028</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001026257797508961</v>
+        <v>0.001026257797508962</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001092596969758131</v>
+        <v>0.001092596969758132</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001001374749335441</v>
+        <v>0.001003075639253606</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009827448369548284</v>
+        <v>0.0009827448369548295</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001562105858736169</v>
+        <v>0.0007717301520037091</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001684596030564099</v>
+        <v>0.0008669456563126382</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001515775520759957</v>
+        <v>0.0007692918783354842</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001710112212135429</v>
+        <v>0.0008883967074404416</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001597672288587049</v>
+        <v>0.0007948855531401528</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001559258172085421</v>
+        <v>0.0007715802839112415</v>
       </c>
       <c r="H2" t="n">
-        <v>0.001502863091008994</v>
+        <v>0.0007683316120356576</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001570190107477174</v>
+        <v>0.0007721639549400951</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001777302942387239</v>
+        <v>0.0009013261827591769</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001746043833124482</v>
+        <v>0.0009191882196292881</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001499052867842946</v>
+        <v>0.0007682960033553144</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.001674061893328177</v>
+        <v>0.0007664626472659432</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001797651993149218</v>
+        <v>0.0009261958459465796</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001620772407354935</v>
+        <v>0.0007491296361926624</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001823306376341517</v>
+        <v>0.0009614507148512476</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001710866452793136</v>
+        <v>0.0008070411170810138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001670786463783305</v>
+        <v>0.0007654106149605221</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001606124156726379</v>
+        <v>0.000744154427127074</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001683425906151581</v>
+        <v>0.0007695208102491498</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001898799802760084</v>
+        <v>0.0009987849512452947</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001859087552193158</v>
+        <v>0.001011838753183106</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001601535917649972</v>
+        <v>0.0007429241567370121</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007395168270678609</v>
+        <v>0.0007395168270678603</v>
       </c>
       <c r="C4" t="n">
         <v>0.000736070916930446</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007119754043239547</v>
+        <v>0.0007119754043239546</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007385023345927396</v>
+        <v>0.0007385023345927398</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007385023345927397</v>
+        <v>0.0007385023345927398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007375336113976254</v>
+        <v>0.000737533611397625</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007043224844559766</v>
+        <v>0.0007043224844559767</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007425346886564599</v>
+        <v>0.00074253468865646</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007772754602034261</v>
+        <v>0.0007772754602034258</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007438214313091636</v>
+        <v>0.0007438214313091635</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007020624855210071</v>
+        <v>0.0007020624855210065</v>
       </c>
     </row>
     <row r="5">
@@ -6974,19 +6974,19 @@
         <v>0.001713608409417528</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001778750172406399</v>
+        <v>0.001778750172406407</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001262286498140818</v>
+        <v>0.001262286498140819</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001778750362973594</v>
+        <v>0.001778750362973598</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001778750362973594</v>
+        <v>0.001778750362973598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001692489876604941</v>
+        <v>0.001692489876604936</v>
       </c>
       <c r="H5" t="n">
         <v>0.001201059878447698</v>
@@ -6995,13 +6995,13 @@
         <v>0.001778744918322874</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002412743758052275</v>
+        <v>0.002412743758052274</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001726914014677141</v>
+        <v>0.001726914014677138</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001178314381842102</v>
+        <v>0.001531397301590063</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000873625291415655</v>
+        <v>0.0008736252914156551</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008750545927311197</v>
+        <v>0.0008750545927311171</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008446365458388205</v>
+        <v>0.0008446365458388201</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008610921407206068</v>
+        <v>0.0008610921407206071</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008762911612156533</v>
+        <v>0.0008762911612156539</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009794808904143007</v>
+        <v>0.0008716420757454201</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009506330805177562</v>
+        <v>0.0009506330805177565</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008766431530042552</v>
+        <v>0.0008766431530042549</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001019985305022377</v>
+        <v>0.0009208458733581433</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008782893338058652</v>
+        <v>0.0008782893338058654</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008358100517965641</v>
+        <v>0.0008358100517965644</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008171871887928412</v>
+        <v>0.0008171871887928409</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008202103044649764</v>
+        <v>0.0008202103044649757</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007896368784250443</v>
+        <v>0.0007896368784250439</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008200891578405415</v>
+        <v>0.0008200891578405414</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008200891578405415</v>
+        <v>0.0008200891578405414</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008152039731226063</v>
+        <v>0.000815203973122606</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007819928461809576</v>
+        <v>0.0007819928461809574</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008202050503814407</v>
+        <v>0.0008202050503814408</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008549458219284065</v>
+        <v>0.0008549458219284063</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008214917930341443</v>
+        <v>0.0008214917930341438</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007797328472459869</v>
+        <v>0.000779732847245987</v>
       </c>
     </row>
     <row r="8">
@@ -7091,25 +7091,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008828910455298963</v>
+        <v>0.0008828910455298966</v>
       </c>
       <c r="C8" t="n">
         <v>0.001004429592626965</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009985386172220109</v>
+        <v>0.0009985386172220116</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009720009649195557</v>
+        <v>0.0009720009649195559</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008896066154414578</v>
+        <v>0.0008896066154414577</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009995049407626111</v>
+        <v>0.0009995049407626104</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009662938138209417</v>
+        <v>0.0009662938138209416</v>
       </c>
       <c r="I8" t="n">
         <v>0.001004506018021446</v>
@@ -7118,10 +7118,10 @@
         <v>0.001039270097284766</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008849926475493435</v>
+        <v>0.0008849926475493433</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001087918414140396</v>
+        <v>0.001087918414140395</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009381397839871867</v>
+        <v>0.0009381397839871859</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00100806197908153</v>
+        <v>0.001008061979081529</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00097749749474777</v>
+        <v>0.0009774974947477687</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001085262328826909</v>
+        <v>0.001085262328826908</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001008062162548675</v>
+        <v>0.001008062162548674</v>
       </c>
       <c r="G9" t="n">
-        <v>0.00100305564773916</v>
+        <v>0.001003055647739159</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009698445207975118</v>
+        <v>0.0009698445207975109</v>
       </c>
       <c r="I9" t="n">
         <v>0.001008056724997995</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001042797496544961</v>
+        <v>0.00104279749654496</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009690092931328488</v>
+        <v>0.0009690092931328477</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009675845218625416</v>
+        <v>0.0009675845218625402</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001712174053611584</v>
+        <v>0.0008055104239159719</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001730201472472947</v>
+        <v>0.0009138556707151808</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001898807810116531</v>
+        <v>0.0008153325878363297</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001767039899972995</v>
+        <v>0.0009449062255669975</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001618483087996896</v>
+        <v>0.0008213324346602316</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001863938724720283</v>
+        <v>0.0008134974971275065</v>
       </c>
       <c r="H2" t="n">
-        <v>0.002447965588717348</v>
+        <v>0.0008442399454558416</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001591733248870865</v>
+        <v>0.0007991775663557954</v>
       </c>
       <c r="J2" t="n">
-        <v>0.002038920829015086</v>
+        <v>0.0009846487548265661</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0018381173854532</v>
+        <v>0.0009503177247281129</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002891654405158425</v>
+        <v>0.0008682154652122363</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00184251481264674</v>
+        <v>0.0008371409591139935</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001842302409915243</v>
+        <v>0.0009818605183154793</v>
       </c>
       <c r="D3" t="n">
-        <v>0.002057182293693618</v>
+        <v>0.0009068381963821116</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001879305865526311</v>
+        <v>0.001032763456796494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.001730749053550212</v>
+        <v>0.0008287300005795778</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002017075622378655</v>
+        <v>0.0008940764782934031</v>
       </c>
       <c r="H3" t="n">
-        <v>0.002689038704557583</v>
+        <v>0.001113474953060914</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001703873110938297</v>
+        <v>0.0007921458748424082</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002187145191931244</v>
+        <v>0.001167640478365753</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001960757299104918</v>
+        <v>0.001061487876237522</v>
       </c>
       <c r="L3" t="n">
-        <v>0.003199107956795634</v>
+        <v>0.001283955025156622</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008364828031954314</v>
+        <v>0.000836482803195431</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007502161585543792</v>
+        <v>0.0007502161585543789</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009474286630945137</v>
+        <v>0.0009474286630945132</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007532639289870742</v>
+        <v>0.0007532639289870737</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007532639289870742</v>
+        <v>0.0007532639289870737</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009263014008381072</v>
+        <v>0.0009263014008381061</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001273755868852052</v>
+        <v>0.00127375586885205</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007623367827040541</v>
+        <v>0.0007623367827040534</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009072586934166823</v>
+        <v>0.0009072586934166819</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008060060496788823</v>
+        <v>0.0008060060496788816</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001537423952037335</v>
+        <v>0.001537423952037334</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003159874146008567</v>
+        <v>0.003159874146008562</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001917581810824945</v>
+        <v>0.001917581810824942</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005032922180377582</v>
+        <v>0.00503292218037758</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001917582109464497</v>
+        <v>0.001917582109464496</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001917582109464497</v>
+        <v>0.001917582109464496</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004827138647049206</v>
+        <v>0.004827138647049191</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01144183465839801</v>
+        <v>0.011441834658398</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001917537851525967</v>
+        <v>0.001917537851525965</v>
       </c>
       <c r="J5" t="n">
-        <v>0.00473281932097257</v>
+        <v>0.004732819320972569</v>
       </c>
       <c r="K5" t="n">
-        <v>0.00264977865394102</v>
+        <v>0.002649778653941016</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01823384913773547</v>
+        <v>0.005042197372738456</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009809695945136392</v>
+        <v>0.0009809695945136386</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009006669451188423</v>
+        <v>0.0009006669451188429</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001094872538058704</v>
+        <v>0.001094872538058705</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008860059432145272</v>
+        <v>0.0008860059432145254</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009060077365437109</v>
+        <v>0.0009060077365437104</v>
       </c>
       <c r="G6" t="n">
-        <v>0.00120429214184863</v>
+        <v>0.001204292141848629</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001561394865142561</v>
+        <v>0.00156139486514256</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001040327523714578</v>
+        <v>0.001040327523714576</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001188348393610619</v>
+        <v>0.001188348393610618</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009473151307542127</v>
+        <v>0.0009473151307542099</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001686358116443582</v>
+        <v>0.001686358116443581</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009321394627656603</v>
+        <v>0.0009321394627656589</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008580374015732625</v>
+        <v>0.0008580374015732616</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001043075833538868</v>
+        <v>0.001043075833538867</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008578839229368923</v>
+        <v>0.0008578839229368916</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008578839229368923</v>
+        <v>0.0008578839229368916</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001021958060408335</v>
+        <v>0.001021958060408334</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001369412528422282</v>
+        <v>0.00136941252842228</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008579934422742827</v>
+        <v>0.0008579934422742818</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001002915352986911</v>
+        <v>0.001002915352986909</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009016627092491106</v>
+        <v>0.00090166270924911</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001633080611607567</v>
+        <v>0.001633080611607565</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00101483355848208</v>
+        <v>0.001014833558482079</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001086051870409323</v>
+        <v>0.001086051870408482</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001301361751378208</v>
+        <v>0.001301361751378207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001046288128594642</v>
+        <v>0.00104628812859464</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009452555349541014</v>
+        <v>0.0009452555349541006</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001250079236614425</v>
+        <v>0.001250079236614423</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001597533704628385</v>
+        <v>0.001597533704628382</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001086114618480372</v>
+        <v>0.001086114618480371</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001231065109759104</v>
+        <v>0.001231065109759102</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009816554222847591</v>
+        <v>0.0009816554222847576</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002013112533779583</v>
+        <v>0.002013112533779579</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001158115105956634</v>
+        <v>0.001158115105956633</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001186935930468871</v>
+        <v>0.001186935930468869</v>
       </c>
       <c r="D9" t="n">
-        <v>0.00137198385931536</v>
+        <v>0.001371983859315358</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001305706867774249</v>
+        <v>0.001305706867774248</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001186936072204084</v>
+        <v>0.001186936072204083</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001350856589303945</v>
+        <v>0.001350856589303943</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001698311057317891</v>
+        <v>0.001698311057317889</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00118689197116989</v>
+        <v>0.001186891971169889</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001331813881882519</v>
+        <v>0.001331813881882516</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001170927317219968</v>
+        <v>0.001170927317219966</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001961979140503172</v>
+        <v>0.00196197914050317</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.001503796599591133</v>
+        <v>0.0007803510834247427</v>
       </c>
       <c r="C2" t="n">
-        <v>0.001687957089055228</v>
+        <v>0.0008975941439555896</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001849214497043732</v>
+        <v>0.0007985297413124692</v>
       </c>
       <c r="E2" t="n">
-        <v>0.001725283516738897</v>
+        <v>0.0009289592380447034</v>
       </c>
       <c r="F2" t="n">
-        <v>0.001575998944047144</v>
+        <v>0.0008047797144919469</v>
       </c>
       <c r="G2" t="n">
-        <v>0.001707291331483824</v>
+        <v>0.0007910606069911626</v>
       </c>
       <c r="H2" t="n">
-        <v>0.00159897563462809</v>
+        <v>0.0007850072361080226</v>
       </c>
       <c r="I2" t="n">
-        <v>0.001549388286529159</v>
+        <v>0.0007827571895355289</v>
       </c>
       <c r="J2" t="n">
-        <v>0.001916253941868371</v>
+        <v>0.0009647748131973147</v>
       </c>
       <c r="K2" t="n">
-        <v>0.001723136802838082</v>
+        <v>0.0009276898732656048</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002315283583925598</v>
+        <v>0.0008234074179032068</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00160259343452019</v>
+        <v>0.000751469237628819</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001793471462406998</v>
+        <v>0.0009584279420991814</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001999895569692574</v>
+        <v>0.0008802680469604512</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001830947689301023</v>
+        <v>0.001009944070861502</v>
       </c>
       <c r="F3" t="n">
-        <v>0.00168166311660927</v>
+        <v>0.000804910720446333</v>
       </c>
       <c r="G3" t="n">
-        <v>0.001836654530003503</v>
+        <v>0.00082754916440325</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001712285083149184</v>
+        <v>0.0007869063773122055</v>
       </c>
       <c r="I3" t="n">
-        <v>0.001654995272523717</v>
+        <v>0.0007685446462941628</v>
       </c>
       <c r="J3" t="n">
-        <v>0.002045659499655535</v>
+        <v>0.001114799862369511</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001828720879108024</v>
+        <v>0.001007604827370836</v>
       </c>
       <c r="L3" t="n">
-        <v>0.002535937777043929</v>
+        <v>0.001057900461152102</v>
       </c>
     </row>
     <row r="4">
@@ -7723,34 +7723,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007057118850428176</v>
+        <v>0.0007057118850428177</v>
       </c>
       <c r="C4" t="n">
         <v>0.0007220113386568844</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009110481884804837</v>
+        <v>0.0009110481884804841</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000724618138183153</v>
+        <v>0.0007246181381831534</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007246181381831532</v>
+        <v>0.0007246181381831533</v>
       </c>
       <c r="G4" t="n">
         <v>0.0008263406444391833</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007623274190611355</v>
+        <v>0.0007623274190611353</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007306700845769881</v>
+        <v>0.0007306700845769884</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008268485207697575</v>
+        <v>0.0008268485207697573</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007325729725084056</v>
+        <v>0.0007325729725084055</v>
       </c>
       <c r="L4" t="n">
         <v>0.001187987049943681</v>
@@ -7778,10 +7778,10 @@
         <v>0.001510286841441467</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003037601245582741</v>
+        <v>0.003037601245582744</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002094135222527931</v>
+        <v>0.002094135222527935</v>
       </c>
       <c r="I5" t="n">
         <v>0.001510258307908604</v>
@@ -7790,10 +7790,10 @@
         <v>0.003259687157191946</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001494547996855271</v>
+        <v>0.001494547996855272</v>
       </c>
       <c r="L5" t="n">
-        <v>0.00214425291766725</v>
+        <v>0.01030901267226446</v>
       </c>
     </row>
     <row r="6">
@@ -7803,34 +7803,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009562763119689828</v>
+        <v>0.0009562763119689827</v>
       </c>
       <c r="C6" t="n">
         <v>0.0008614655624559291</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001049776948358391</v>
+        <v>0.001049777621127212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008475708219457138</v>
+        <v>0.0008475708219457137</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000864807450287916</v>
+        <v>0.0008648074502879161</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009609979320802974</v>
+        <v>0.001076905071365349</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001018669412259498</v>
+        <v>0.001018669412259497</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009812345115031524</v>
+        <v>0.0009812345115031531</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009715454803612632</v>
+        <v>0.000971545480361263</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008653905560013857</v>
+        <v>0.0008653905560013855</v>
       </c>
       <c r="L6" t="n">
         <v>0.001324502099317804</v>
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007884552277882467</v>
+        <v>0.0007884552277882468</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008134417275164787</v>
+        <v>0.0008134417275164788</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000993782685233533</v>
+        <v>0.0009937826852335328</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008132970091295716</v>
+        <v>0.0008132970091295709</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008132970091295716</v>
+        <v>0.0008132970091295709</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009090839871846123</v>
+        <v>0.0009090839871846121</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008450707618065641</v>
+        <v>0.000845070761806564</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008134134273224167</v>
+        <v>0.000813413427322417</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009095918635151867</v>
+        <v>0.0009095918635151866</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008153163152538342</v>
+        <v>0.0008153163152538345</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001270730392689109</v>
+        <v>0.00127073039268911</v>
       </c>
     </row>
     <row r="8">
@@ -7883,19 +7883,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008597686709960191</v>
+        <v>0.000859768670996019</v>
       </c>
       <c r="C8" t="n">
         <v>0.001011144998459469</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001217826719896351</v>
+        <v>0.00121782671989635</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009765593780346499</v>
+        <v>0.0009765593780346492</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008886838326215147</v>
+        <v>0.0008886838326215151</v>
       </c>
       <c r="G8" t="n">
         <v>0.001106890097341277</v>
@@ -7904,13 +7904,13 @@
         <v>0.001042876871963215</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001011219537479082</v>
+        <v>0.001011219537479081</v>
       </c>
       <c r="J8" t="n">
         <v>0.001107422833087674</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008842800922329688</v>
+        <v>0.0008842800922329685</v>
       </c>
       <c r="L8" t="n">
         <v>0.001600668670602606</v>
@@ -7926,10 +7926,10 @@
         <v>0.0009493496799460113</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001054166563283224</v>
+        <v>0.001054166563283225</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001234516449443564</v>
+        <v>0.001234516449443565</v>
       </c>
       <c r="E9" t="n">
         <v>0.001146289406984112</v>
@@ -7944,13 +7944,13 @@
         <v>0.00108579559757331</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001054138263089161</v>
+        <v>0.001054138263089162</v>
       </c>
       <c r="J9" t="n">
         <v>0.001150316699281932</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009555204270144612</v>
+        <v>0.001009787147918096</v>
       </c>
       <c r="L9" t="n">
         <v>0.001511455228455855</v>

--- a/Results/Ammonia/ammonia eutrophication marine results.xlsx
+++ b/Results/Ammonia/ammonia eutrophication marine results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008449854937270019</v>
+        <v>0.0008449854937270022</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009572700886623306</v>
+        <v>0.0009572700886623275</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008697783679873998</v>
+        <v>0.0008697783679873999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009912872891636596</v>
+        <v>0.0009912872891636594</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008584787227424251</v>
+        <v>0.0008584787227424253</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008514564182384302</v>
+        <v>0.0008514564182384305</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008793133894171389</v>
+        <v>0.0008793133894171392</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008327093103732859</v>
+        <v>0.0008327093103732862</v>
       </c>
       <c r="J2" t="n">
         <v>0.001039236162549189</v>
       </c>
       <c r="K2" t="n">
-        <v>0.00098337391920448</v>
+        <v>0.0009833739192044804</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0009101023584615698</v>
+        <v>0.00091010235846157</v>
       </c>
     </row>
     <row r="3">
@@ -555,10 +555,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0009467307397597003</v>
+        <v>0.0009467307397597006</v>
       </c>
       <c r="C3" t="n">
-        <v>0.001065657121219904</v>
+        <v>0.001065657121219902</v>
       </c>
       <c r="D3" t="n">
         <v>0.001123478687602477</v>
@@ -567,16 +567,16 @@
         <v>0.001121341292344692</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0009020642872900717</v>
+        <v>0.0009020642872900718</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009933018084791619</v>
+        <v>0.0009933018084791623</v>
       </c>
       <c r="H3" t="n">
         <v>0.001194484658714626</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008595148563005965</v>
+        <v>0.0008595148563005966</v>
       </c>
       <c r="J3" t="n">
         <v>0.001289014102877056</v>
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.00100425422635798</v>
+        <v>0.001004254226357979</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008555620181352511</v>
+        <v>0.0008555620181352508</v>
       </c>
       <c r="D4" t="n">
         <v>0.001284301146414818</v>
@@ -607,25 +607,25 @@
         <v>0.000858928141198734</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008589281411987341</v>
+        <v>0.000858928141198734</v>
       </c>
       <c r="G4" t="n">
-        <v>0.001076964041059433</v>
+        <v>0.001076964041059432</v>
       </c>
       <c r="H4" t="n">
         <v>0.001392896082033641</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0008630906681908024</v>
+        <v>0.0008630906681908023</v>
       </c>
       <c r="J4" t="n">
         <v>0.001047289423544867</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008692447852773502</v>
+        <v>0.0008692447852773496</v>
       </c>
       <c r="L4" t="n">
-        <v>0.00173228437313958</v>
+        <v>0.001732284373139579</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.005961968337054292</v>
+        <v>0.005961968337054296</v>
       </c>
       <c r="C5" t="n">
-        <v>0.003404757856228683</v>
+        <v>0.003404757856228689</v>
       </c>
       <c r="D5" t="n">
         <v>0.01148262214147355</v>
       </c>
       <c r="E5" t="n">
-        <v>0.003404758000335063</v>
+        <v>0.003404758000335065</v>
       </c>
       <c r="F5" t="n">
-        <v>0.003404758000335063</v>
+        <v>0.003404758000335065</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007663966928771967</v>
+        <v>0.007663966928771942</v>
       </c>
       <c r="H5" t="n">
-        <v>0.01513702578167122</v>
+        <v>0.01513702578167121</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003404702508019526</v>
+        <v>0.003404702508019534</v>
       </c>
       <c r="J5" t="n">
         <v>0.007265012361292506</v>
       </c>
       <c r="K5" t="n">
-        <v>0.003514783701008349</v>
+        <v>0.003514783701008354</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02314868193608524</v>
+        <v>0.02314868193608529</v>
       </c>
     </row>
     <row r="6">
@@ -678,13 +678,13 @@
         <v>0.001169292996374265</v>
       </c>
       <c r="C6" t="n">
-        <v>0.001021513965528586</v>
+        <v>0.001021513965528587</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001459944293162347</v>
+        <v>0.001459944293162348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001005053013823728</v>
+        <v>0.001005053013823726</v>
       </c>
       <c r="F6" t="n">
         <v>0.001027897893320295</v>
@@ -696,16 +696,16 @@
         <v>0.001729587308305656</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001189747654883771</v>
+        <v>0.00118974765488377</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001375077619662449</v>
+        <v>0.001375077619662448</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001029723518286958</v>
+        <v>0.00102972351828696</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001903171116776317</v>
+        <v>0.001903171116776316</v>
       </c>
     </row>
     <row r="7">
@@ -718,7 +718,7 @@
         <v>0.001120938739134154</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0009798305291761286</v>
+        <v>0.0009798305291761282</v>
       </c>
       <c r="D7" t="n">
         <v>0.001400975097486688</v>
@@ -727,7 +727,7 @@
         <v>0.0009796763854850814</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0009796763854850816</v>
+        <v>0.0009796763854850814</v>
       </c>
       <c r="G7" t="n">
         <v>0.001193648553835607</v>
@@ -736,13 +736,13 @@
         <v>0.001509580594809818</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0009797751809669771</v>
+        <v>0.0009797751809669767</v>
       </c>
       <c r="J7" t="n">
         <v>0.001163973936321042</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009859292980535241</v>
+        <v>0.0009859292980535239</v>
       </c>
       <c r="L7" t="n">
         <v>0.001848968885915756</v>
@@ -758,7 +758,7 @@
         <v>0.001221888211292272</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001256383923956309</v>
+        <v>0.00125638392395631</v>
       </c>
       <c r="D8" t="n">
         <v>0.00171407220705916</v>
@@ -770,10 +770,10 @@
         <v>0.001086263943659646</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001470301783071911</v>
+        <v>0.001470301783071912</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001786233824046124</v>
+        <v>0.001786233824046125</v>
       </c>
       <c r="I8" t="n">
         <v>0.001256428410203282</v>
@@ -785,7 +785,7 @@
         <v>0.001083614982719519</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002309159381505367</v>
+        <v>0.002309159381505368</v>
       </c>
     </row>
     <row r="9">
@@ -798,13 +798,13 @@
         <v>0.001498714937756749</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001510640200528889</v>
+        <v>0.00151064020052889</v>
       </c>
       <c r="D9" t="n">
         <v>0.001931795379681757</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001687237537175905</v>
+        <v>0.001687237537175906</v>
       </c>
       <c r="F9" t="n">
         <v>0.001510640156974167</v>
@@ -813,13 +813,13 @@
         <v>0.001724458225188367</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002040390266162576</v>
+        <v>0.002040390266162577</v>
       </c>
       <c r="I9" t="n">
         <v>0.001510584852319739</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001694783607673802</v>
+        <v>0.001694783607673801</v>
       </c>
       <c r="K9" t="n">
         <v>0.001324042498125414</v>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007689484808071735</v>
+        <v>0.00076894848080717</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008671795162691195</v>
+        <v>0.0008671795162691201</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007715589711880498</v>
+        <v>0.0007715589711880448</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008887852168955772</v>
+        <v>0.0008887852168955735</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007948456512819418</v>
+        <v>0.0007948456512819392</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007734425459503373</v>
+        <v>0.0007734425459503402</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000770915078967209</v>
+        <v>0.0007709150789672089</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007725584377720862</v>
+        <v>0.0007725584377720811</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000902190443756618</v>
+        <v>0.0009021904437566167</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009174699156924765</v>
+        <v>0.0009174699156924724</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007694685772615342</v>
+        <v>0.0007694685772615317</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000740301014516262</v>
+        <v>0.0007403010145162618</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009223497537510784</v>
+        <v>0.0009223497537510787</v>
       </c>
       <c r="D3" t="n">
-        <v>0.00075882101293708</v>
+        <v>0.0007588210129370799</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009578442943993563</v>
+        <v>0.0009578442943993547</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008027275179346715</v>
+        <v>0.0008027275179346705</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007722569481131663</v>
+        <v>0.0007722569481131641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007561525666825489</v>
+        <v>0.0007561525666825494</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007659242595312166</v>
+        <v>0.0007659242595312173</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009958805975753987</v>
+        <v>0.0009958805975753965</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009988200488595641</v>
+        <v>0.0009988200488595638</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007449491547404674</v>
+        <v>0.0007449491547404663</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006966513093931541</v>
+        <v>0.0006966513093931533</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007288347455321238</v>
+        <v>0.0007288347455321235</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007261379991300533</v>
+        <v>0.0007261379991300531</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007312858129851614</v>
+        <v>0.0007312858129851608</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007312858129851611</v>
+        <v>0.0007312858129851608</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000747114337248054</v>
+        <v>0.0007471143372480533</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007220258917304421</v>
+        <v>0.0007220258917304416</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007354835203407746</v>
+        <v>0.0007354835203407744</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007699535138905687</v>
+        <v>0.000769953513890568</v>
       </c>
       <c r="K4" t="n">
-        <v>0.000724456890605477</v>
+        <v>0.0007244568906054766</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007040041084484815</v>
+        <v>0.0007040041084484813</v>
       </c>
     </row>
     <row r="5">
@@ -1034,34 +1034,34 @@
         <v>0.001013886609608378</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001659972609776661</v>
+        <v>0.00165997260977666</v>
       </c>
       <c r="D5" t="n">
         <v>0.001477779979005644</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00165997280161934</v>
+        <v>0.001659972801619339</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00165997280161934</v>
+        <v>0.001659972801619339</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001850031174238609</v>
+        <v>0.001850031174238611</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00151368930160349</v>
+        <v>0.001513689301603489</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001659963557621236</v>
+        <v>0.001659963557621239</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002328701978039858</v>
+        <v>0.002328701978039849</v>
       </c>
       <c r="K5" t="n">
         <v>0.001428794027620177</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001212919401791343</v>
+        <v>0.001212919401791342</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008302115416042471</v>
+        <v>0.0008302115416042461</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000867475893684366</v>
+        <v>0.0008674758936843658</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009690170813930138</v>
+        <v>0.0009690170813930136</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008535240895618769</v>
+        <v>0.0008535240895618772</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008689749496148801</v>
+        <v>0.0008689749496148792</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009880753937172434</v>
+        <v>0.0009880753937172415</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009692052935010427</v>
+        <v>0.0009692052935010425</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008690437525518675</v>
+        <v>0.0008690437525518665</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009132983577968541</v>
+        <v>0.0009132983577968536</v>
       </c>
       <c r="K6" t="n">
         <v>0.0008580517143917012</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008375696602074938</v>
+        <v>0.0008375696602074929</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007752871244924755</v>
+        <v>0.000775287124492475</v>
       </c>
       <c r="C7" t="n">
         <v>0.0008141283875955188</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008047649263518175</v>
+        <v>0.0008047649263518172</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008140064599480381</v>
+        <v>0.0008140064599480376</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008140064599480381</v>
+        <v>0.0008140064599480376</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008257501523473758</v>
+        <v>0.0008257501523473757</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008006617068297639</v>
+        <v>0.0008006617068297636</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008141193354400965</v>
+        <v>0.0008141193354400951</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008485893289898907</v>
+        <v>0.0008485893289898901</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008030927057047988</v>
+        <v>0.0008030927057047986</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000782639923547803</v>
+        <v>0.0007826399235478027</v>
       </c>
     </row>
     <row r="8">
@@ -1151,19 +1151,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008419523164151998</v>
+        <v>0.0008419523164151993</v>
       </c>
       <c r="C8" t="n">
         <v>0.001000756680776755</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00101637641148889</v>
+        <v>0.001016376411488891</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000967932051304317</v>
+        <v>0.0009679320513043169</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008845314720357363</v>
+        <v>0.0008845314720357352</v>
       </c>
       <c r="G8" t="n">
         <v>0.001012460586590719</v>
@@ -1175,10 +1175,10 @@
         <v>0.00100082976968344</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001035323355548235</v>
+        <v>0.001035323355548234</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008675279956211986</v>
+        <v>0.0008675279956211988</v>
       </c>
       <c r="L8" t="n">
         <v>0.001094747651401418</v>
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008978616203881679</v>
+        <v>0.0008978616203881671</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001004414947536662</v>
+        <v>0.001004414947536661</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009950604307272812</v>
+        <v>0.0009950604307272808</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001082553462168172</v>
+        <v>0.001082553462168171</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001004415127764575</v>
+        <v>0.001004415127764574</v>
       </c>
       <c r="G9" t="n">
         <v>0.001016036712288518</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009909482667709072</v>
+        <v>0.0009909482667709061</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001004405895381239</v>
+        <v>0.00100440589538124</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001038875888931033</v>
+        <v>0.001038875888931034</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009541466535999032</v>
+        <v>0.0009541466535999025</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009729264834889467</v>
+        <v>0.0009729264834889462</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008162643829117077</v>
+        <v>0.000816264382911708</v>
       </c>
       <c r="C2" t="n">
-        <v>0.000779861743084333</v>
+        <v>0.0007798617430843333</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008258965836312897</v>
+        <v>0.00082589658363129</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007762039579994248</v>
+        <v>0.0007762039579994256</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007762840608603351</v>
+        <v>0.0007762840608603357</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008238632493843896</v>
+        <v>0.0008238632493843899</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008383285814772392</v>
+        <v>0.0008383285814772394</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008177669792647081</v>
+        <v>0.0008177669792647079</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009041797697259697</v>
+        <v>0.0009041797697259698</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008961261929123771</v>
+        <v>0.0008961261929123764</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008298768463585903</v>
+        <v>0.0008298768463585901</v>
       </c>
     </row>
     <row r="3">
@@ -1347,19 +1347,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008463591664873166</v>
+        <v>0.0008463591664873174</v>
       </c>
       <c r="C3" t="n">
         <v>0.0008021772755220224</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009149501712099669</v>
+        <v>0.0009149501712099664</v>
       </c>
       <c r="E3" t="n">
-        <v>0.000788533371476109</v>
+        <v>0.0007885333714761094</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007886134743370192</v>
+        <v>0.0007886134743370181</v>
       </c>
       <c r="G3" t="n">
         <v>0.0009006052535841562</v>
@@ -1368,16 +1368,16 @@
         <v>0.001005561251957441</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008570756528692436</v>
+        <v>0.0008570756528692432</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001096004726483324</v>
+        <v>0.001096004726483325</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009840732518662252</v>
+        <v>0.0009840732518662247</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009444315969220547</v>
+        <v>0.0009444315969220545</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007428084159521828</v>
+        <v>0.0007428084159521826</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007609564817462417</v>
+        <v>0.0007609564817462422</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0008516085541111027</v>
+        <v>0.0008516085541111024</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007544642571965635</v>
+        <v>0.0007544642571965637</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007544642571965636</v>
+        <v>0.0007544642571965637</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0008282598733038891</v>
+        <v>0.000828259873303889</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009934751825057177</v>
+        <v>0.0009934751825057173</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007572926141965778</v>
+        <v>0.0007572926141965777</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009576801722601029</v>
+        <v>0.0009576801722601031</v>
       </c>
       <c r="K4" t="n">
         <v>0.0007549637236541305</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008967386337909163</v>
+        <v>0.0008967386337909159</v>
       </c>
     </row>
     <row r="5">
@@ -1430,34 +1430,34 @@
         <v>0.001752674738452498</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002364157893986159</v>
+        <v>0.002364157893986167</v>
       </c>
       <c r="D5" t="n">
-        <v>0.003693707721550132</v>
+        <v>0.003693707721550131</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002062022521416693</v>
+        <v>0.002062022521416694</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002062022521416693</v>
+        <v>0.002062022521416694</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003357155145296583</v>
+        <v>0.003357155145296579</v>
       </c>
       <c r="H5" t="n">
-        <v>0.006936767293945803</v>
+        <v>0.006936767293945816</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002061999651857636</v>
+        <v>0.002061999651857641</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005839895392467588</v>
+        <v>0.005839895392467582</v>
       </c>
       <c r="K5" t="n">
         <v>0.001969967769906913</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005070683104814427</v>
+        <v>0.005070683104814432</v>
       </c>
     </row>
     <row r="6">
@@ -1467,10 +1467,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001005430836864267</v>
+        <v>0.001005430836864268</v>
       </c>
       <c r="C6" t="n">
-        <v>0.000911496756605876</v>
+        <v>0.0009114967566058763</v>
       </c>
       <c r="D6" t="n">
         <v>0.000993789849391207</v>
@@ -1479,22 +1479,22 @@
         <v>0.0008803037291570067</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008976192074593928</v>
+        <v>0.0008976192074593931</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009687303364455872</v>
+        <v>0.0009687303364455878</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001265602745068647</v>
+        <v>0.001265602745068648</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000897763077338276</v>
+        <v>0.0008977630773382765</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001221925047054791</v>
+        <v>0.001221925047054792</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008927893717145606</v>
+        <v>0.0008927893717145603</v>
       </c>
       <c r="L6" t="n">
         <v>0.001037778018250317</v>
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008343819420351967</v>
+        <v>0.0008343819420351966</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008662268983602555</v>
+        <v>0.000866226898360255</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009431734347636729</v>
+        <v>0.0009431734347636724</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008491299861300385</v>
+        <v>0.0008491299861300391</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008491299861300385</v>
+        <v>0.0008491299861300391</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009198333993869029</v>
+        <v>0.0009198333993869033</v>
       </c>
       <c r="H7" t="n">
         <v>0.001085048708588731</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008488661402795913</v>
+        <v>0.0008488661402795912</v>
       </c>
       <c r="J7" t="n">
         <v>0.001049253698343117</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008465372497371443</v>
+        <v>0.0008465372497371442</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009883121598739304</v>
+        <v>0.0009883121598739302</v>
       </c>
     </row>
     <row r="8">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0009130623530590353</v>
+        <v>0.0009130623530590347</v>
       </c>
       <c r="C8" t="n">
         <v>0.001084693285792965</v>
@@ -1559,10 +1559,10 @@
         <v>0.001029168223954927</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009321408290439613</v>
+        <v>0.0009321408290439615</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001138031543052475</v>
+        <v>0.001138031543052474</v>
       </c>
       <c r="H8" t="n">
         <v>0.001303246852254464</v>
@@ -1574,10 +1574,10 @@
         <v>0.001267479261217618</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009226260472503441</v>
+        <v>0.0009226260472503437</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001352248241546477</v>
+        <v>0.001352248241546476</v>
       </c>
     </row>
     <row r="9">
@@ -1587,34 +1587,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001025363921212444</v>
+        <v>0.001025363921212443</v>
       </c>
       <c r="C9" t="n">
         <v>0.001148991995204103</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001225947217601034</v>
+        <v>0.001225947217601037</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001237569823021035</v>
+        <v>0.001237569823021031</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001131654033081824</v>
+        <v>0.001131654033081823</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001202598496230748</v>
+        <v>0.001202598496230749</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001367813805432577</v>
+        <v>0.001367813805432579</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001131631237123438</v>
+        <v>0.001131631237123437</v>
       </c>
       <c r="J9" t="n">
         <v>0.001332018795186963</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001076122864805661</v>
+        <v>0.001076122864805662</v>
       </c>
       <c r="L9" t="n">
         <v>0.001271077256717777</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008034242888443013</v>
+        <v>0.0008034242888443023</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007709002585494961</v>
+        <v>0.0007709002585494963</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00081144595593482</v>
+        <v>0.0008114459559348207</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000768804916531312</v>
+        <v>0.0007688049165313132</v>
       </c>
       <c r="F2" t="n">
-        <v>0.000768885155955684</v>
+        <v>0.0007688851559556845</v>
       </c>
       <c r="G2" t="n">
-        <v>0.000808854820207333</v>
+        <v>0.000808854820207334</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000815032253891839</v>
+        <v>0.0008150322538918388</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008050522811759177</v>
+        <v>0.0008050522811759179</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008949070679053655</v>
+        <v>0.0008949070679053653</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008887204059936061</v>
+        <v>0.0008887204059936054</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008070680352744942</v>
+        <v>0.000807068035274494</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008164647262343844</v>
+        <v>0.0008164647262343847</v>
       </c>
       <c r="C3" t="n">
         <v>0.0007799837049975878</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008736131748819454</v>
+        <v>0.000873613174881946</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007683250167478369</v>
+        <v>0.0007683250167478373</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007684052561722081</v>
+        <v>0.0007684052561722093</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000855245823439022</v>
+        <v>0.0008552458234390224</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009010439795337517</v>
+        <v>0.0009010439795337514</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008280933209979948</v>
+        <v>0.0008280933209979949</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001042169501005002</v>
+        <v>0.001042169501005003</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009597806610724263</v>
+        <v>0.0009597806610724253</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008434666933363907</v>
+        <v>0.0008434666933363904</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007071109476301048</v>
+        <v>0.000707110947630105</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007303527325139783</v>
+        <v>0.0007303527325139781</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007977193675666794</v>
+        <v>0.0007977193675666788</v>
       </c>
       <c r="E4" t="n">
         <v>0.0007327708856705403</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007327708856705404</v>
+        <v>0.0007327708856705403</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007681119049705948</v>
+        <v>0.000768111904970595</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008404501480123989</v>
+        <v>0.000840450148012399</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007232862493886493</v>
+        <v>0.0007232862493886494</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008606496345902501</v>
+        <v>0.0008606496345902506</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007122645346316788</v>
+        <v>0.0007122645346316791</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007495071552764044</v>
+        <v>0.0007495071552764038</v>
       </c>
     </row>
     <row r="5">
@@ -1826,22 +1826,22 @@
         <v>0.001189045679814625</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001819723288601803</v>
+        <v>0.001819723288601804</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002738440809024567</v>
+        <v>0.002738440809024571</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001517027075410958</v>
+        <v>0.001517027075410959</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001517027075410958</v>
+        <v>0.001517027075410959</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002285595097157371</v>
+        <v>0.002285595097157369</v>
       </c>
       <c r="H5" t="n">
-        <v>0.003819659144679898</v>
+        <v>0.003819659144679894</v>
       </c>
       <c r="I5" t="n">
         <v>0.001517010386064167</v>
@@ -1853,7 +1853,7 @@
         <v>0.001288438910680702</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0021065440640048</v>
+        <v>0.002106544064004802</v>
       </c>
     </row>
     <row r="6">
@@ -1866,34 +1866,34 @@
         <v>0.0009542364694772308</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008733377523454759</v>
+        <v>0.0008733377523454782</v>
       </c>
       <c r="D6" t="n">
         <v>0.001046211041978336</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008432858960051085</v>
+        <v>0.0008432858960051089</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008584715285862858</v>
+        <v>0.000858471528586286</v>
       </c>
       <c r="G6" t="n">
         <v>0.001015237426817721</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001095705710312203</v>
+        <v>0.001095705710312202</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000857639492258242</v>
+        <v>0.0008576394922582414</v>
       </c>
       <c r="J6" t="n">
         <v>0.001005422496414117</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008451927122104572</v>
+        <v>0.0008451927122104585</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008834530275291343</v>
+        <v>0.0008834530275291347</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007918975840391579</v>
+        <v>0.0007918975840391574</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008265452711700014</v>
+        <v>0.0008265452711700015</v>
       </c>
       <c r="D7" t="n">
         <v>0.0008824978858495141</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008096394361615896</v>
+        <v>0.00080963943616159</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008096394361615897</v>
+        <v>0.00080963943616159</v>
       </c>
       <c r="G7" t="n">
         <v>0.0008528985413796483</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009252367844214519</v>
+        <v>0.0009252367844214513</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008080728857977022</v>
+        <v>0.0008080728857977025</v>
       </c>
       <c r="J7" t="n">
         <v>0.0009454362709993035</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007970511710407318</v>
+        <v>0.0007970511710407316</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0008342937916854572</v>
+        <v>0.0008342937916854577</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008642620648972402</v>
+        <v>0.0008642620648972422</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001029897722525612</v>
+        <v>0.001029897722525611</v>
       </c>
       <c r="D8" t="n">
         <v>0.001111188710055023</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009758707445380025</v>
+        <v>0.0009758707445380031</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008854875119511626</v>
+        <v>0.0008854875119511625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001054734494300654</v>
+        <v>0.001054734494300656</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001127072737342778</v>
+        <v>0.001127072737342777</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001009908838718707</v>
+        <v>0.001009908838718706</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001147297668740073</v>
+        <v>0.001147297668740071</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008670106528372102</v>
+        <v>0.0008670106528372103</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001171373523373867</v>
+        <v>0.001171373523373868</v>
       </c>
     </row>
     <row r="9">
@@ -1983,19 +1983,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009348824304835213</v>
+        <v>0.0009348824304835207</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001045413407572</v>
+        <v>0.001045413407572001</v>
       </c>
       <c r="D9" t="n">
         <v>0.001101374189820571</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001114525419888105</v>
+        <v>0.001114525419888104</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001026957676362869</v>
+        <v>0.001026957676362868</v>
       </c>
       <c r="G9" t="n">
         <v>0.001071766677781647</v>
@@ -2004,16 +2004,16 @@
         <v>0.001144104920823451</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001026941022199701</v>
+        <v>0.0010269410221997</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001164304407401301</v>
+        <v>0.001164304407401302</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009719522520202035</v>
+        <v>0.0009719522520202034</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001053161928087456</v>
+        <v>0.001053161928087457</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007776985986412642</v>
+        <v>0.0007776985986412701</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007582078551472506</v>
+        <v>0.0007582078551472509</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007833064042585579</v>
+        <v>0.0007833064042585612</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007536536113134562</v>
+        <v>0.0007536536113134653</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007537341502352622</v>
+        <v>0.0007537341502352642</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007811796849898309</v>
+        <v>0.000781179684989834</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007833677783631631</v>
+        <v>0.0007833677783631637</v>
       </c>
       <c r="I2" t="n">
-        <v>0.000778104279592975</v>
+        <v>0.0007781042795929773</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008337296227810828</v>
+        <v>0.0008337296227810868</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008749103621136205</v>
+        <v>0.0008749103621136218</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007787712032178004</v>
+        <v>0.0007787712032178008</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007781771252442454</v>
+        <v>0.0007781771252442485</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000762930728239505</v>
+        <v>0.0007629307282395053</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008181509703740828</v>
+        <v>0.000818150970374087</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007408128554943722</v>
+        <v>0.0007408128554943745</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007408933944161727</v>
+        <v>0.0007408933944161795</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008030544542391915</v>
+        <v>0.000803054454239195</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000820286878724498</v>
+        <v>0.0008202868787244991</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007811074958157845</v>
+        <v>0.0007811074958157865</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009060055054349054</v>
+        <v>0.0009060055054349124</v>
       </c>
       <c r="K3" t="n">
-        <v>0.000940511388439155</v>
+        <v>0.0009405113884391632</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007866360925168007</v>
+        <v>0.0007866360925168011</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006836141607568965</v>
+        <v>0.000683614160756897</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000707653440528851</v>
+        <v>0.0007076534405288516</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007469569049222654</v>
+        <v>0.0007469569049222657</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006950674375885692</v>
+        <v>0.0006950674375885697</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006950674375885692</v>
+        <v>0.0006950674375885697</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007226210896749655</v>
+        <v>0.0007226210896749646</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007501623131855139</v>
+        <v>0.0007501623131855148</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006861563371098323</v>
+        <v>0.0006861563371098332</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007562006558755372</v>
+        <v>0.0007562006558755383</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006873944773113685</v>
+        <v>0.0006873944773113684</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006969243414627313</v>
+        <v>0.000696924341462732</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008805884294876505</v>
+        <v>0.0008805884294876523</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001503598470040023</v>
+        <v>0.001503598470040024</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001975338560933314</v>
+        <v>0.00197533856093331</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009777499844685006</v>
+        <v>0.0009777499844685032</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009777499844685006</v>
+        <v>0.0009777499844685032</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001592638298861918</v>
+        <v>0.001592638298861923</v>
       </c>
       <c r="H5" t="n">
-        <v>0.002204585638490657</v>
+        <v>0.002204585638490663</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009777353872009306</v>
+        <v>0.0009777353872009319</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002207214282391382</v>
+        <v>0.002207214282391384</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009641867241636896</v>
+        <v>0.0009641867241636912</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0011961571911599</v>
+        <v>0.001196157191159903</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008167373051211127</v>
+        <v>0.0008167373051211135</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008488640325405368</v>
+        <v>0.0008488640325405364</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008804992700611192</v>
+        <v>0.0008804992700611139</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008049218787029166</v>
+        <v>0.0008049218787029175</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008199958848388987</v>
+        <v>0.0008199958848388996</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009655923798022969</v>
+        <v>0.0009655923798022973</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001000292797415245</v>
+        <v>0.001000292797415247</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000929127627237164</v>
+        <v>0.000929127627237165</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001000153363680225</v>
+        <v>0.001000153363680227</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008199373710198018</v>
+        <v>0.0008199373710197465</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008293370921409224</v>
+        <v>0.0008293370921409238</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007652075858473103</v>
+        <v>0.0007652075858473113</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007993746200301964</v>
+        <v>0.0007993746200301973</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008285421523101436</v>
+        <v>0.0008285421523101439</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007696023903793804</v>
+        <v>0.0007696023903793813</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007696023903793804</v>
+        <v>0.0007696023903793813</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008042145147653791</v>
+        <v>0.0008042145147653797</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0008317557382759281</v>
+        <v>0.0008317557382759293</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007677497622002461</v>
+        <v>0.0007677497622002472</v>
       </c>
       <c r="J7" t="n">
-        <v>0.000837794080965952</v>
+        <v>0.0008377940809659526</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007689879024017822</v>
+        <v>0.0007689879024017833</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007785177665531454</v>
+        <v>0.0007785177665531463</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008350068038844877</v>
+        <v>0.0008350068038844875</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000996218488116724</v>
+        <v>0.0009962184881167264</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001049574562169771</v>
+        <v>0.001049574562169769</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009301611305666675</v>
+        <v>0.0009301611305666697</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008426352569753659</v>
+        <v>0.0008426352569753672</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009992667233810224</v>
+        <v>0.0009992667233810239</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001026807946891888</v>
+        <v>0.00102680794689189</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009628019708158912</v>
+        <v>0.0009628019708158918</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001032870905346304</v>
+        <v>0.001032870905346307</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008364604818368877</v>
+        <v>0.0008364604818368888</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001104407197279556</v>
+        <v>0.00110440719727956</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008775578720399254</v>
+        <v>0.0008775578720399275</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000978009380899329</v>
+        <v>0.000978009380899332</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001007185139828636</v>
+        <v>0.001007185139828639</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001022890017057245</v>
+        <v>0.001022890017057247</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009463990996603056</v>
+        <v>0.000946399099660307</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009828492756345111</v>
+        <v>0.0009828492756345129</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001010390499145062</v>
+        <v>0.001010390499145065</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009463845230693799</v>
+        <v>0.0009463845230693822</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001016428841835086</v>
+        <v>0.001016428841835088</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009076590387226993</v>
+        <v>0.0009076590387226995</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009571525274222779</v>
+        <v>0.0009571525274222822</v>
       </c>
     </row>
   </sheetData>
@@ -2498,34 +2498,34 @@
         <v>0.0008032721076161871</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007645590420444175</v>
+        <v>0.000764559042044417</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008097064962909455</v>
+        <v>0.0008097064962909449</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007678804453315182</v>
+        <v>0.0007678804453315196</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007679604625667586</v>
+        <v>0.0007679604625667596</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008098502201413864</v>
+        <v>0.0008098502201413861</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008230106667080461</v>
+        <v>0.0008230106667080469</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008053206860672195</v>
+        <v>0.0008053206860672207</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000898860924146045</v>
+        <v>0.000898860924146046</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008910691752779734</v>
+        <v>0.0008910691752779748</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008193016137717265</v>
+        <v>0.0008193016137717275</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.00081135057025941</v>
+        <v>0.0008113505702594109</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007446658270455662</v>
+        <v>0.0007446658270455651</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008572062925590257</v>
+        <v>0.0008572062925590263</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007642458304357647</v>
+        <v>0.0007642458304357637</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007643258476710042</v>
+        <v>0.0007643258476710034</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008583180712891005</v>
+        <v>0.0008583180712891014</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009537028229947631</v>
+        <v>0.0009537028229947641</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008259843740703114</v>
+        <v>0.0008259843740703132</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001085671381003477</v>
+        <v>0.001085671381003478</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009709335297072199</v>
+        <v>0.0009709335297072225</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0009262115767902446</v>
+        <v>0.000926211576790245</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006964845522407471</v>
+        <v>0.0006964845522407461</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006750301571116857</v>
+        <v>0.0006750301571116852</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007691639322871622</v>
+        <v>0.0007691639322871606</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007219272150426468</v>
+        <v>0.0007219272150426473</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007219272150426469</v>
+        <v>0.0007219272150426473</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000770426947137686</v>
+        <v>0.0007704269471376856</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0009207883037521313</v>
+        <v>0.00092078830375213</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007172680954166977</v>
+        <v>0.0007172680954166979</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009361190391019008</v>
+        <v>0.0009361190391018997</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007266700159325661</v>
+        <v>0.000726670015932565</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008769799597267688</v>
+        <v>0.0008769799597267667</v>
       </c>
     </row>
     <row r="5">
@@ -2618,34 +2618,34 @@
         <v>0.001004626728103</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0009120945975726985</v>
+        <v>0.0009120945975727015</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002321152366164197</v>
+        <v>0.002321152366164196</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001440196811255592</v>
+        <v>0.001440196811255602</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001440196811255592</v>
+        <v>0.001440196811255602</v>
       </c>
       <c r="G5" t="n">
-        <v>0.002398076412065072</v>
+        <v>0.002398076412065075</v>
       </c>
       <c r="H5" t="n">
-        <v>0.005588137808200289</v>
+        <v>0.005588137808200288</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00144017820125125</v>
+        <v>0.00144017820125126</v>
       </c>
       <c r="J5" t="n">
-        <v>0.005542595741103662</v>
+        <v>0.005542595741103664</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001564580403539147</v>
+        <v>0.001564580403539145</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004783357071912021</v>
+        <v>0.004783357071912023</v>
       </c>
     </row>
     <row r="6">
@@ -2655,34 +2655,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.000833850280562235</v>
+        <v>0.0008338502805622376</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008223491772367027</v>
+        <v>0.0008223491772366939</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009070017965816472</v>
+        <v>0.0009070017965816471</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008387095873080867</v>
+        <v>0.0008387095873080888</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008550082269515051</v>
+        <v>0.000855008226951506</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009077926754591738</v>
+        <v>0.0009077926754591731</v>
       </c>
       <c r="H6" t="n">
         <v>0.001185517404891858</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009729923800471203</v>
+        <v>0.0009729923800471215</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0010843647006495</v>
+        <v>0.001084364700649501</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008620866912793892</v>
+        <v>0.0008620866912793901</v>
       </c>
       <c r="L6" t="n">
         <v>0.001015024655546426</v>
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007864465415958409</v>
+        <v>0.00078644654159584</v>
       </c>
       <c r="C7" t="n">
-        <v>0.000779826438301737</v>
+        <v>0.0007798264383017367</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008591175305011077</v>
+        <v>0.000859117530501106</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008095360281298881</v>
+        <v>0.0008095360281298884</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008095360281298881</v>
+        <v>0.0008095360281298884</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008603889364927795</v>
+        <v>0.0008603889364927816</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001010750293107225</v>
+        <v>0.001010750293107227</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008072300847717918</v>
+        <v>0.0008072300847717923</v>
       </c>
       <c r="J7" t="n">
         <v>0.001026081028456995</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008166320052876598</v>
+        <v>0.0008166320052876586</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009669419490818625</v>
+        <v>0.0009669419490818629</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000862878216114673</v>
+        <v>0.0008628782161146738</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009955713781635528</v>
+        <v>0.0009955713781635532</v>
       </c>
       <c r="D8" t="n">
         <v>0.001101074593535893</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009852642302879827</v>
+        <v>0.0009852642302879831</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008893954346677174</v>
+        <v>0.000889395434667718</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001073911019191718</v>
+        <v>0.001073911019191719</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001224272375806093</v>
+        <v>0.001224272375806092</v>
       </c>
       <c r="I8" t="n">
         <v>0.00102075216747073</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001239630053312124</v>
+        <v>0.001239630053312126</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008905171550953576</v>
+        <v>0.0008905171550953593</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00132366642640448</v>
+        <v>0.001323666426404482</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009577092808262696</v>
+        <v>0.0009577092808262702</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001036984240051356</v>
+        <v>0.001036984240051358</v>
       </c>
       <c r="D9" t="n">
         <v>0.001116283761074533</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001163527542639766</v>
+        <v>0.001163527542639767</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001064406441463068</v>
+        <v>0.00106440644146307</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001117546738242399</v>
+        <v>0.0011175467382424</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001267908094856844</v>
+        <v>0.001267908094856846</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001064387886521411</v>
+        <v>0.001064387886521412</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001283238830206614</v>
+        <v>0.001283238830206616</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001024021886327044</v>
+        <v>0.001024021886327045</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001224099750831483</v>
+        <v>0.001224099750831486</v>
       </c>
     </row>
   </sheetData>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007849064117542194</v>
+        <v>0.0007849064117542196</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007554591343105815</v>
+        <v>0.0007554591343105813</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007854547636764588</v>
+        <v>0.0007854547636764579</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000758299099092796</v>
+        <v>0.0007582990990927965</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007583792514622408</v>
+        <v>0.0007583792514622413</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007859479052482762</v>
+        <v>0.0007859479052482758</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007861468924884548</v>
+        <v>0.0007861468924884547</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007865029099869117</v>
+        <v>0.0007865029099869121</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008767584381567565</v>
+        <v>0.000876758438156756</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008787347528041047</v>
+        <v>0.0008787347528041052</v>
       </c>
       <c r="L2" t="n">
         <v>0.0007869123402140799</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007856422161695144</v>
+        <v>0.0007856422161695131</v>
       </c>
       <c r="C3" t="n">
         <v>0.0007372525650494437</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007895834707826484</v>
+        <v>0.0007895834707826478</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007505663789977277</v>
+        <v>0.000750566378997727</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007506465313671723</v>
+        <v>0.0007506465313671712</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007931178206643688</v>
+        <v>0.0007931178206643681</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007960571910790863</v>
+        <v>0.0007960571910790861</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007970581808370152</v>
+        <v>0.0007970581808370142</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009760268559914991</v>
+        <v>0.0009760268559914984</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009421144984479434</v>
+        <v>0.0009421144984479422</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008004340905720332</v>
+        <v>0.0008004340905720329</v>
       </c>
     </row>
     <row r="4">
@@ -2971,34 +2971,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006803359845698505</v>
+        <v>0.0006803359845698502</v>
       </c>
       <c r="C4" t="n">
         <v>0.0006683488434830097</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006865298717858791</v>
+        <v>0.0006865298717858792</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007107744551970254</v>
+        <v>0.0007107744551970253</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007107744551970254</v>
+        <v>0.0007107744551970252</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006917974174834342</v>
+        <v>0.000691797417483434</v>
       </c>
       <c r="H4" t="n">
-        <v>0.000696973030454396</v>
+        <v>0.0006969730304543958</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006963985386620926</v>
+        <v>0.0006963985386620928</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000759979386082426</v>
+        <v>0.0007599793860824258</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006835430903832593</v>
+        <v>0.0006835430903832591</v>
       </c>
       <c r="L4" t="n">
         <v>0.0007035387743785641</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008402151960252739</v>
+        <v>0.0008402151960252734</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008625292417746174</v>
+        <v>0.0008625292417746172</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009640878389632487</v>
+        <v>0.0009640878389632481</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001168429978530845</v>
+        <v>0.001168429978530846</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001168429978530845</v>
+        <v>0.001168429978530846</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001069960578954449</v>
+        <v>0.001069960578954453</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001204560585321701</v>
+        <v>0.001204560585321702</v>
       </c>
       <c r="I5" t="n">
         <v>0.001168424805108132</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002291393464968045</v>
+        <v>0.002291393464968043</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009143976482436257</v>
+        <v>0.0009143976482436251</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001343566987765076</v>
+        <v>0.001343566987765075</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008115718919619312</v>
+        <v>0.0008115718919619304</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008084697037160128</v>
+        <v>0.0008084697037160121</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0009266985396286188</v>
+        <v>0.000926698539628619</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008151353967313104</v>
+        <v>0.0008151353967313122</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008288426191024945</v>
+        <v>0.0008288426191024943</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008230333248755149</v>
+        <v>0.000823033324875515</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009428525608795766</v>
+        <v>0.0009428525608795764</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009356913560380316</v>
+        <v>0.0009356913560380311</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001000051142231937</v>
+        <v>0.001000051142231936</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008142955324059952</v>
+        <v>0.0008142955324059841</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008342303464087112</v>
+        <v>0.0008342303464087111</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007612016437626697</v>
+        <v>0.0007612016437626691</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007609825048294308</v>
+        <v>0.0007609825048294301</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000767387577483458</v>
+        <v>0.0007673875774834576</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007800835459772982</v>
+        <v>0.000780083545977298</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007800835459772982</v>
+        <v>0.000780083545977298</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000772663076676254</v>
+        <v>0.0007726630766762534</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007778386896472151</v>
+        <v>0.0007778386896472144</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007772641978549122</v>
+        <v>0.0007772641978549121</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008408450452752451</v>
+        <v>0.0008408450452752443</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007644087495760785</v>
+        <v>0.0007644087495760777</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007844044335713837</v>
+        <v>0.0007844044335713838</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008298985830997662</v>
+        <v>0.0008298985830997659</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000956504183281452</v>
+        <v>0.0009565041832814516</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009859268853198465</v>
+        <v>0.0009859268853198457</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009385610804116483</v>
+        <v>0.0009385610804116489</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008515836641040979</v>
+        <v>0.000851583664104098</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009654612348503639</v>
+        <v>0.0009654612348503634</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009706368478213849</v>
+        <v>0.0009706368478213843</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009700623560290223</v>
+        <v>0.0009700623560290217</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001033667592850847</v>
+        <v>0.001033667592850846</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008308004450634008</v>
+        <v>0.0008308004450634003</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001106836691955783</v>
+        <v>0.001106836691955782</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008839953344092974</v>
+        <v>0.000883995334409297</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009527523740721536</v>
+        <v>0.0009527523740721533</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009591654497906629</v>
+        <v>0.0009591654497906624</v>
       </c>
       <c r="E9" t="n">
         <v>0.00104863632965492</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009690392379251257</v>
+        <v>0.0009690392379251254</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009644329459189777</v>
+        <v>0.0009644329459189771</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009696085588899389</v>
+        <v>0.0009696085588899396</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009690340670976358</v>
+        <v>0.0009690340670976356</v>
       </c>
       <c r="J9" t="n">
         <v>0.001032614914517969</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009162135708986334</v>
+        <v>0.0009162135708986325</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009761743028141068</v>
+        <v>0.000976174302814107</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007600835140207434</v>
+        <v>0.0007600835140207439</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007472794554028429</v>
+        <v>0.0007472794554028427</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007605528762742339</v>
+        <v>0.0007605528762742338</v>
       </c>
       <c r="E2" t="n">
         <v>0.0007473746515701823</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007474551477949689</v>
+        <v>0.0007474551477949699</v>
       </c>
       <c r="G2" t="n">
         <v>0.0007604829706555529</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007605008314015023</v>
+        <v>0.0007605008314015022</v>
       </c>
       <c r="I2" t="n">
         <v>0.0007608770205969617</v>
       </c>
       <c r="J2" t="n">
-        <v>0.000820515382289043</v>
+        <v>0.0008205153822890433</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008676759125080157</v>
+        <v>0.0008676759125080167</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007602663034642927</v>
+        <v>0.000760266303464293</v>
       </c>
     </row>
     <row r="3">
@@ -3330,31 +3330,31 @@
         <v>0.0007540720566896588</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007336787055430838</v>
+        <v>0.0007336787055430836</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007574524666967067</v>
+        <v>0.0007574524666967068</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007375447942416368</v>
+        <v>0.0007375447942416355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007376252904664243</v>
+        <v>0.0007376252904664254</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007569685163168242</v>
+        <v>0.0007569685163168246</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000758558155741798</v>
+        <v>0.0007585581557417981</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007597674298211181</v>
+        <v>0.0007597674298211177</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008618599019064542</v>
+        <v>0.0008618599019064541</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009316087218730823</v>
+        <v>0.0009316087218730832</v>
       </c>
       <c r="L3" t="n">
         <v>0.0007558589927347042</v>
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000675510841675885</v>
+        <v>0.0006755108416758825</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006661457046200681</v>
+        <v>0.0006661457046200669</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006808125042463632</v>
+        <v>0.0006808125042463618</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006933507670463465</v>
+        <v>0.0006933507670463462</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006933507670463465</v>
+        <v>0.0006933507670463463</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006797358940924521</v>
+        <v>0.0006797358940924369</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0006828076500520214</v>
+        <v>0.0006828076500520229</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006826117741108855</v>
+        <v>0.0006826117741108881</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0006919254021749817</v>
+        <v>0.0006919254021749804</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006752975567090011</v>
+        <v>0.0006752975567090008</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006782760602575458</v>
+        <v>0.000678276060257547</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008100450432008541</v>
+        <v>0.0008100450432008511</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008518559774307533</v>
+        <v>0.0008518559774307532</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000919644528026697</v>
+        <v>0.0009196445280266964</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009833374241179091</v>
+        <v>0.0009833374241179017</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009833374241179091</v>
+        <v>0.0009833374241179013</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0009131494371280025</v>
+        <v>0.0009131494371279953</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009931413054634706</v>
+        <v>0.0009931413054634691</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009833319505977254</v>
+        <v>0.0009833319505977173</v>
       </c>
       <c r="J5" t="n">
         <v>0.001132076983863156</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0008266442122680923</v>
+        <v>0.0008266442122680932</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009116807779232954</v>
+        <v>0.0009116807779232941</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009139080739916384</v>
+        <v>0.0009139080739916388</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008055762269515682</v>
+        <v>0.0008055762269515681</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008115013214217192</v>
+        <v>0.0008115013214217213</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008009986321076061</v>
+        <v>0.0008009986321076067</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008150568635152163</v>
+        <v>0.0008150568635152161</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009181331264081901</v>
+        <v>0.0009181331264081934</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0008137682128243909</v>
+        <v>0.0008137682128243897</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009210090064266448</v>
+        <v>0.0009210090064266452</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008328688056170946</v>
+        <v>0.0008328688056170936</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008068814693804229</v>
+        <v>0.0008068814693804227</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008090287017837678</v>
+        <v>0.000809028701783768</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007539686064334283</v>
+        <v>0.0007539686064334286</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007548576665568515</v>
+        <v>0.0007548576665568508</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007592621538587807</v>
+        <v>0.0007592621538587816</v>
       </c>
       <c r="E7" t="n">
-        <v>0.000763337132383503</v>
+        <v>0.0007633371323835026</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000763337132383503</v>
+        <v>0.0007633371323835026</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007581936588499823</v>
+        <v>0.0007581936588499813</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000761265414809568</v>
+        <v>0.0007612654148095688</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000761069538868434</v>
+        <v>0.0007610695388684338</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007703831669325259</v>
+        <v>0.0007703831669325261</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007537553214665445</v>
+        <v>0.0007537553214665468</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007567338250150916</v>
+        <v>0.0007567338250150929</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008210875734168045</v>
+        <v>0.0008210875734168052</v>
       </c>
       <c r="C8" t="n">
-        <v>0.000945138981916143</v>
+        <v>0.0009451389819161425</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009724386319922256</v>
+        <v>0.0009724386319922268</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009180388737066105</v>
+        <v>0.0009180388737066104</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008333827283506407</v>
+        <v>0.0008333827283506408</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009462788808429026</v>
+        <v>0.000946278880842904</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009493506368026678</v>
+        <v>0.0009493506368026674</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009491547608613555</v>
+        <v>0.0009491547608613551</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009584921622204763</v>
+        <v>0.0009584921622204782</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008186272781622976</v>
+        <v>0.0008186272781622996</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001071178415362753</v>
+        <v>0.001071178415362755</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008569020770090086</v>
+        <v>0.0008569020770090093</v>
       </c>
       <c r="C9" t="n">
         <v>0.0009203467666075093</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009247594151673311</v>
+        <v>0.0009247594151673343</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0009987520206385823</v>
+        <v>0.0009987520206385827</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009265641096339205</v>
+        <v>0.0009265641096339215</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009236827589006386</v>
+        <v>0.0009236827589006407</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009267545148602275</v>
+        <v>0.0009267545148602271</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009265586389190924</v>
+        <v>0.0009265586389190932</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009358722669831834</v>
+        <v>0.0009358722669831843</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008829994635194184</v>
+        <v>0.0008829994635194181</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009222229250657502</v>
+        <v>0.0009222229250657507</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.000792196854071122</v>
+        <v>0.0007921968540711333</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007589903763613065</v>
+        <v>0.0007589903763613171</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007933637136430412</v>
+        <v>0.0007933637136430382</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007621565511366872</v>
+        <v>0.0007621565511367031</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007622365204153273</v>
+        <v>0.0007622365204153394</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007948257916768368</v>
+        <v>0.0007948257916768349</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008086439385082116</v>
+        <v>0.0008086439385082199</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007941593666653668</v>
+        <v>0.0007941593666653663</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008727967387203812</v>
+        <v>0.0008727967387203868</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008824559517703033</v>
+        <v>0.00088245595177031</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008051608752930932</v>
+        <v>0.0008051608752930929</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007974017273270617</v>
+        <v>0.0007974017273270632</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007405223636899553</v>
+        <v>0.0007405223636899555</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008057436405866105</v>
+        <v>0.0008057436405866102</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007586596471920865</v>
+        <v>0.0007586596471920846</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007587396164707232</v>
+        <v>0.0007587396164707215</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008162002306849789</v>
+        <v>0.0008162002306849798</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009159623495837504</v>
+        <v>0.0009159623495837506</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008114229918600963</v>
+        <v>0.0008114229918600981</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009507455072664845</v>
+        <v>0.0009507455072664834</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009508188581781893</v>
+        <v>0.0009508188581781905</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008900770672942056</v>
+        <v>0.0008900770672942054</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006898990483352614</v>
+        <v>0.0006898990483352626</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006702768840350169</v>
+        <v>0.0006702768840350167</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007030792639818625</v>
+        <v>0.0007030792639818632</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007161956948354447</v>
+        <v>0.0007161956948354448</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007161956948354447</v>
+        <v>0.0007161956948354446</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007192611502649889</v>
+        <v>0.0007192611502649895</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008766853250888505</v>
+        <v>0.0008766853250888525</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007098944815853273</v>
+        <v>0.000709894481585327</v>
       </c>
       <c r="J4" t="n">
-        <v>0.000731538682550397</v>
+        <v>0.0007315386825503964</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006989682153941663</v>
+        <v>0.0006989682153941658</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008354530191092485</v>
+        <v>0.000835453019109246</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0009455010584602751</v>
+        <v>0.0009455010584602738</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0008816037166826228</v>
+        <v>0.0008816037166826235</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001198528345955046</v>
+        <v>0.001198528345955049</v>
       </c>
       <c r="E5" t="n">
-        <v>0.00136408574660821</v>
+        <v>0.001364085746608209</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00136408574660821</v>
+        <v>0.001364085746608209</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001517510569253237</v>
+        <v>0.001517510569253257</v>
       </c>
       <c r="H5" t="n">
-        <v>0.00476698590911145</v>
+        <v>0.004766985909111451</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001364077182603116</v>
+        <v>0.001364077182603115</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001761175401740788</v>
+        <v>0.001761175401740789</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001126896164334653</v>
+        <v>0.00112689616433465</v>
       </c>
       <c r="L5" t="n">
-        <v>0.003999418966828196</v>
+        <v>0.003999418966828194</v>
       </c>
     </row>
     <row r="6">
@@ -3846,34 +3846,34 @@
         <v>0.0008244446217777428</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008156446598777188</v>
+        <v>0.0008156446598777182</v>
       </c>
       <c r="D6" t="n">
         <v>0.0008370233362165731</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008298977000022512</v>
+        <v>0.0008298977000022508</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008449822273774442</v>
+        <v>0.0008449822273774445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008538067237074705</v>
+        <v>0.0008538067237074699</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001135855105056556</v>
+        <v>0.001135855105056555</v>
       </c>
       <c r="I6" t="n">
         <v>0.0008444400550278076</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008756329741489338</v>
+        <v>0.000875632974148934</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008317646142536714</v>
+        <v>0.0008317646142536883</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0009704555300501384</v>
+        <v>0.0009704555300501374</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007769420996140387</v>
+        <v>0.0007769420996140378</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007719425449435512</v>
+        <v>0.0007719425449435518</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007901140179081973</v>
+        <v>0.0007901140179081968</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007995779417762892</v>
+        <v>0.0007995779417762895</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007995779417762892</v>
+        <v>0.0007995779417762895</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008063042015437635</v>
+        <v>0.000806304201543765</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0009637283763676271</v>
+        <v>0.0009637283763676283</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007969375328641024</v>
+        <v>0.0007969375328641026</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008185817338291704</v>
+        <v>0.0008185817338291716</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007860112666729426</v>
+        <v>0.0007860112666729412</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0009224960703880217</v>
+        <v>0.0009224960703880219</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008512052118447788</v>
+        <v>0.0008512052118447785</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009822835389519239</v>
+        <v>0.0009822835389519241</v>
       </c>
       <c r="D8" t="n">
         <v>0.001025599697919415</v>
       </c>
       <c r="E8" t="n">
-        <v>0.000970497740357964</v>
+        <v>0.0009704977403579645</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008770167707513598</v>
+        <v>0.0008770167707513605</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001014093963532825</v>
+        <v>0.001014093963532824</v>
       </c>
       <c r="H8" t="n">
         <v>0.001171518138356541</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001004727294853162</v>
+        <v>0.001004727294853163</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001026397737588022</v>
+        <v>0.001026397737588026</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008577940528354509</v>
+        <v>0.0008577940528354514</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001269765583326964</v>
+        <v>0.001269765583326967</v>
       </c>
     </row>
     <row r="9">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009325476843258771</v>
+        <v>0.0009325476843258768</v>
       </c>
       <c r="C9" t="n">
         <v>0.001008161732659006</v>
@@ -3972,25 +3972,25 @@
         <v>0.001026341522984165</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001126191632330986</v>
+        <v>0.001126191632330987</v>
       </c>
       <c r="F9" t="n">
         <v>0.00103316523744654</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001042523389259219</v>
+        <v>0.00104252338925922</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00119994756408308</v>
+        <v>0.001199947564083083</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001033156720579557</v>
+        <v>0.001033156720579558</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001054800921544626</v>
+        <v>0.001054800921544627</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009755226246295134</v>
+        <v>0.0009755226246295142</v>
       </c>
       <c r="L9" t="n">
         <v>0.001158715258103477</v>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007636040907642135</v>
+        <v>0.0007636040907642105</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007539310462914284</v>
+        <v>0.00075393104629142</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007639690381240902</v>
+        <v>0.0007639690381240876</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007569637105399237</v>
+        <v>0.0007569637105399219</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007570438539092515</v>
+        <v>0.0007570438539092502</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007640035826221472</v>
+        <v>0.0007640035826221442</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007639554027768126</v>
+        <v>0.0007639554027768131</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007649727235907292</v>
+        <v>0.0007649727235907261</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008698674675199501</v>
+        <v>0.0008698674675199489</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008777980519725301</v>
+        <v>0.0008777980519725291</v>
       </c>
       <c r="L2" t="n">
-        <v>0.000763694303115533</v>
+        <v>0.0007636943031155333</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007537105224266037</v>
+        <v>0.0007537105224266021</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007377523629657141</v>
+        <v>0.0007377523629657178</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000756344270323637</v>
+        <v>0.0007563442703236356</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007503448138126703</v>
+        <v>0.0007503448138126702</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007504249571819969</v>
+        <v>0.0007504249571819979</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007566066841063093</v>
+        <v>0.0007566066841063091</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007577547117254377</v>
+        <v>0.000757754711725438</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007635018431324406</v>
+        <v>0.0007635018431324397</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009384962107623929</v>
+        <v>0.0009384962107623923</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009435973892772255</v>
+        <v>0.0009435973892772247</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007548609094583018</v>
+        <v>0.0007548609094583021</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006814487451174023</v>
+        <v>0.0006814487451174065</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0006688168804272514</v>
+        <v>0.0006688168804272533</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006855709934312918</v>
+        <v>0.0006855709934312943</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007114651241014372</v>
+        <v>0.0007114651241014385</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007114651241014371</v>
+        <v>0.0007114651241014385</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006856648282952735</v>
+        <v>0.0006856648282952748</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0006880429504236414</v>
+        <v>0.000688042950423643</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006949782676048907</v>
+        <v>0.0006949782676048944</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007006270243394498</v>
+        <v>0.0007006270243394507</v>
       </c>
       <c r="K4" t="n">
-        <v>0.00068424008992057</v>
+        <v>0.0006842400899205759</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006832015321396145</v>
+        <v>0.0006832015321396179</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008583864113638105</v>
+        <v>0.0008583864113638157</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000873370107567404</v>
+        <v>0.0008733701075674044</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009463757185177574</v>
+        <v>0.0009463757185177604</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001141969711357604</v>
+        <v>0.001141969711357609</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001141969711357604</v>
+        <v>0.001141969711357609</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000961203795215471</v>
+        <v>0.0009612037952154954</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001032079274081181</v>
+        <v>0.001032079274081188</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001141965485159324</v>
+        <v>0.001141965485159325</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001230423930204111</v>
+        <v>0.001230423930204116</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0009248740616947245</v>
+        <v>0.0009248740616947246</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009452780581577914</v>
+        <v>0.0009452780581577918</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009209549285455071</v>
+        <v>0.0009209549285455098</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008091401565591482</v>
+        <v>0.0008091401565591468</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008162326649512103</v>
+        <v>0.0008162326649512145</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008139561326502221</v>
+        <v>0.0008139561326502241</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008274306259907402</v>
+        <v>0.0008274306259907445</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008167858854117539</v>
+        <v>0.0008167858854117561</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009339370752695108</v>
+        <v>0.0009339370752695155</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009344844510329949</v>
+        <v>0.0009344844510329959</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0008411536764194235</v>
+        <v>0.0008411536764194262</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008150368593963377</v>
+        <v>0.0008150368593963451</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008136434839138875</v>
+        <v>0.0008136434839138931</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007620893627545352</v>
+        <v>0.0007620893627545424</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007614629180278684</v>
+        <v>0.0007614629180278699</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000766203730327468</v>
+        <v>0.0007662037303274717</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007790283224482691</v>
+        <v>0.0007790283224482714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007790283224482692</v>
+        <v>0.0007790283224482714</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007663054459324066</v>
+        <v>0.0007663054459324119</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007686835680607742</v>
+        <v>0.0007686835680607783</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007756188852420235</v>
+        <v>0.0007756188852420281</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007812676419765829</v>
+        <v>0.0007812676419765845</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007648807075577029</v>
+        <v>0.0007648807075577082</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007638421497767472</v>
+        <v>0.0007638421497767495</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008303560801225318</v>
+        <v>0.0008303560801225321</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009568688492995328</v>
+        <v>0.0009568688492995357</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009840106181703665</v>
+        <v>0.0009840106181703697</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009368078961636049</v>
+        <v>0.0009368078961636076</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008498517886199923</v>
+        <v>0.0008498517886199947</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009584231451394982</v>
+        <v>0.0009584231451395025</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009608012672678489</v>
+        <v>0.0009608012672678557</v>
       </c>
       <c r="I8" t="n">
-        <v>0.000967736584449114</v>
+        <v>0.0009677365844491166</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009734096813998695</v>
+        <v>0.000973409681399874</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008308468293573105</v>
+        <v>0.0008308468293573145</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001085332555718943</v>
+        <v>0.001085332555718945</v>
       </c>
     </row>
     <row r="9">
@@ -4359,37 +4359,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008834448690851344</v>
+        <v>0.0008834448690851373</v>
       </c>
       <c r="C9" t="n">
-        <v>0.000951406930009567</v>
+        <v>0.0009514069300095672</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009561556719159636</v>
+        <v>0.0009561556719159692</v>
       </c>
       <c r="E9" t="n">
-        <v>0.00104471684877783</v>
+        <v>0.001044716848777835</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009655671233992965</v>
+        <v>0.0009655671233993026</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009562494579141043</v>
+        <v>0.0009562494579141079</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000958627580042472</v>
+        <v>0.0009586275800424753</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009655628972237209</v>
+        <v>0.0009655628972237262</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009712116539582803</v>
+        <v>0.0009712116539582812</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008684595352549005</v>
+        <v>0.0008684595352549057</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009537861617584455</v>
+        <v>0.0009537861617584486</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.00074745051010869</v>
+        <v>0.0007474505101086898</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0007418703781937421</v>
+        <v>0.0007418703781937422</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007477902220771938</v>
+        <v>0.0007477902220771932</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0007422870928939157</v>
+        <v>0.0007422870928939161</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007423675913011186</v>
+        <v>0.0007423675913011188</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007477473294930571</v>
+        <v>0.0007477473294930567</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007477399323952425</v>
+        <v>0.0007477399323952427</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007481443161478068</v>
+        <v>0.0007481443161478065</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0008155027449351102</v>
+        <v>0.00081550274493511</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0008629602111570324</v>
+        <v>0.0008629602111570326</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007475617832223138</v>
+        <v>0.000747561783222314</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007426296523659599</v>
+        <v>0.0007426296523659604</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0007338247562478932</v>
+        <v>0.0007338247562478933</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007450858049250078</v>
+        <v>0.0007450858049250074</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0007380108923384956</v>
+        <v>0.0007380108923384954</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0007380913907456989</v>
+        <v>0.000738091390745699</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007447939553029499</v>
+        <v>0.0007447939553029493</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000746200914889793</v>
+        <v>0.0007462009148897931</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000747613982244564</v>
+        <v>0.0007476139822445635</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0008624071318646683</v>
+        <v>0.0008624071318646676</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0009342971709505428</v>
+        <v>0.0009342971709505425</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007439062719419397</v>
+        <v>0.0007439062719419399</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0006766207484117188</v>
+        <v>0.0006766207484117187</v>
       </c>
       <c r="C4" t="n">
         <v>0.0006663411212872212</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0006804579513711935</v>
+        <v>0.0006804579513711932</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0006945573870817102</v>
+        <v>0.0006945573870817106</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0006945573870817103</v>
+        <v>0.0006945573870817105</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0006796937743836187</v>
+        <v>0.0006796937743836186</v>
       </c>
       <c r="H4" t="n">
         <v>0.0006824718126233535</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0006826436272777201</v>
+        <v>0.0006826436272777205</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0006918220426805809</v>
+        <v>0.0006918220426805803</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0006786007276781716</v>
+        <v>0.0006786007276781712</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006785776499284503</v>
+        <v>0.0006785776499284498</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0008249306988237544</v>
+        <v>0.000824930698823754</v>
       </c>
       <c r="C5" t="n">
-        <v>0.000854742596638057</v>
+        <v>0.0008547425966380571</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0009091797231567968</v>
+        <v>0.000909179723156797</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0009786250376274412</v>
+        <v>0.0009786250376274416</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0009786250376274412</v>
+        <v>0.0009786250376274416</v>
       </c>
       <c r="G5" t="n">
-        <v>0.000907729642839287</v>
+        <v>0.0009077296428392997</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009817105282020283</v>
+        <v>0.0009817105282020279</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0009786194407933946</v>
+        <v>0.0009786194407933949</v>
       </c>
       <c r="J5" t="n">
-        <v>0.001125568807257448</v>
+        <v>0.001125568807257449</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0008785574519660554</v>
+        <v>0.0008785574519660555</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0009124642042949637</v>
+        <v>0.0009124642042949618</v>
       </c>
     </row>
     <row r="6">
@@ -4635,34 +4635,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009157005189651378</v>
+        <v>0.0009157005189651369</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008063158186734896</v>
+        <v>0.0008063158186734894</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008114559177671598</v>
+        <v>0.0008114559177671594</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008015055128124133</v>
+        <v>0.0008015055128124135</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008155245975540467</v>
+        <v>0.0008155245975540468</v>
       </c>
       <c r="G6" t="n">
-        <v>0.000811590583283638</v>
+        <v>0.0008115905832836374</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009276044887165306</v>
+        <v>0.0009276044887165304</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0008145404361777388</v>
+        <v>0.0008145404361777393</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009316460134965928</v>
+        <v>0.0009316460134965922</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008106845862573184</v>
+        <v>0.0008106845862573174</v>
       </c>
       <c r="L6" t="n">
         <v>0.0008096846899540617</v>
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007549641922684447</v>
+        <v>0.0007549641922684438</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0007551669883572761</v>
+        <v>0.0007551669883572768</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0007587933209515399</v>
+        <v>0.0007587933209515394</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0007636033677426248</v>
+        <v>0.0007636033677426252</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0007636033677426248</v>
+        <v>0.0007636033677426252</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0007580372182403444</v>
+        <v>0.000758037218240344</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007608152564800794</v>
+        <v>0.0007608152564800788</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0007609870711344459</v>
+        <v>0.0007609870711344461</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0007701654865373063</v>
+        <v>0.000770165486537306</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0007569441715348976</v>
+        <v>0.0007569441715348968</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007569210937851756</v>
+        <v>0.0007569210937851751</v>
       </c>
     </row>
     <row r="8">
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008217343022540211</v>
+        <v>0.0008217343022540206</v>
       </c>
       <c r="C8" t="n">
-        <v>0.0009452676571096396</v>
+        <v>0.00094526765710964</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009714217738493677</v>
+        <v>0.0009714217738493681</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009177857437420772</v>
+        <v>0.0009177857437420773</v>
       </c>
       <c r="F8" t="n">
         <v>0.0008331542193379268</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009456086548432662</v>
+        <v>0.0009456086548432661</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009483866930831487</v>
+        <v>0.000948386693083148</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009485585077373677</v>
+        <v>0.0009485585077373681</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0009577606640175711</v>
+        <v>0.0009577606640175705</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008214703348628743</v>
+        <v>0.000821470334862873</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001070679617241767</v>
+        <v>0.001070679617241766</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0008578483880649303</v>
+        <v>0.0008578483880649308</v>
       </c>
       <c r="C9" t="n">
-        <v>0.0009206178787829754</v>
+        <v>0.0009206178787829763</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009242523319258473</v>
+        <v>0.0009242523319258479</v>
       </c>
       <c r="E9" t="n">
-        <v>0.000998644236682851</v>
+        <v>0.0009986442366828523</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0009264435563823973</v>
+        <v>0.0009264435563823984</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0009234881086660435</v>
+        <v>0.0009234881086660436</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009262661469057778</v>
+        <v>0.0009262661469057787</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0009264379615601444</v>
+        <v>0.000926437961560146</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0009356163769630049</v>
+        <v>0.0009356163769630057</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0008846729271209506</v>
+        <v>0.000884672927120951</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009223719842108744</v>
+        <v>0.0009223719842108751</v>
       </c>
     </row>
   </sheetData>
@@ -4871,28 +4871,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008189702122502112</v>
+        <v>0.0008189702122502114</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009220846881111005</v>
+        <v>0.0009220846881111007</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008225222719988376</v>
+        <v>0.0008225222719988384</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009537131105051964</v>
+        <v>0.0009537131105051967</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008286632392175996</v>
+        <v>0.0008286632392176001</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008225757248864197</v>
+        <v>0.0008225757248864201</v>
       </c>
       <c r="H2" t="n">
-        <v>0.000851591763618782</v>
+        <v>0.0008515917636187824</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008064792180369409</v>
+        <v>0.0008064792180369415</v>
       </c>
       <c r="J2" t="n">
         <v>0.001003794174675506</v>
@@ -4901,7 +4901,7 @@
         <v>0.0009571411087426632</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008861341994380921</v>
+        <v>0.0008861341994380925</v>
       </c>
     </row>
     <row r="3">
@@ -4911,19 +4911,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.000893358582142787</v>
+        <v>0.000893358582142786</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009958553665298626</v>
+        <v>0.0009958553665298624</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009188079697645677</v>
+        <v>0.0009188079697645681</v>
       </c>
       <c r="E3" t="n">
         <v>0.001047677570620918</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008412075493055741</v>
+        <v>0.0008412075493055743</v>
       </c>
       <c r="G3" t="n">
         <v>0.0009193859724446193</v>
@@ -4932,7 +4932,7 @@
         <v>0.001128177813546975</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000804575381894674</v>
+        <v>0.0008045753818946744</v>
       </c>
       <c r="J3" t="n">
         <v>0.001244675456427499</v>
@@ -4951,34 +4951,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0009224663764832424</v>
+        <v>0.0009224663764832409</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007663515836492989</v>
+        <v>0.0007663515836492995</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009625885253721976</v>
+        <v>0.0009625885253721977</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007694322283103002</v>
+        <v>0.0007694322283103007</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007694322283103002</v>
+        <v>0.0007694322283103007</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009627804142822729</v>
+        <v>0.0009627804142822719</v>
       </c>
       <c r="H4" t="n">
         <v>0.001291163538901472</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007786752118676561</v>
+        <v>0.0007786752118676567</v>
       </c>
       <c r="J4" t="n">
         <v>0.001016333052969894</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008140333614268284</v>
+        <v>0.0008140333614268288</v>
       </c>
       <c r="L4" t="n">
         <v>0.001672474408458695</v>
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00459644167527508</v>
+        <v>0.004596441675275064</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002129401608653938</v>
+        <v>0.002129401608653941</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005409659406127385</v>
+        <v>0.005409659406127392</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002129401908249456</v>
+        <v>0.002129401908249459</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002129401908249456</v>
+        <v>0.002129401908249459</v>
       </c>
       <c r="G5" t="n">
-        <v>0.005529951314476333</v>
+        <v>0.005529951314476346</v>
       </c>
       <c r="H5" t="n">
         <v>0.01261169749910946</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002129352984894602</v>
+        <v>0.002129352984894605</v>
       </c>
       <c r="J5" t="n">
         <v>0.006726477619423252</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002759825400090329</v>
+        <v>0.002759825400090325</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006536886143663435</v>
+        <v>0.006536886143663439</v>
       </c>
     </row>
     <row r="6">
@@ -5031,34 +5031,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.001069033624856967</v>
+        <v>0.001069033624856966</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009185855138767896</v>
+        <v>0.0009185855138767917</v>
       </c>
       <c r="D6" t="n">
         <v>0.001111638614804956</v>
       </c>
       <c r="E6" t="n">
-        <v>0.00090377847872672</v>
+        <v>0.0009037784787267205</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000924387513215226</v>
+        <v>0.0009243875132152265</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001109347662655996</v>
+        <v>0.001109347662655997</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001584170847917221</v>
+        <v>0.001584170847917222</v>
       </c>
       <c r="I6" t="n">
         <v>0.001063025631416876</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001174467296074853</v>
+        <v>0.001174467296074854</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009566900432216414</v>
+        <v>0.0009566900432216445</v>
       </c>
       <c r="L6" t="n">
         <v>0.00182420051892463</v>
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.001021642191131544</v>
+        <v>0.001021642191131543</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008778996502752941</v>
+        <v>0.000877899650275295</v>
       </c>
       <c r="D7" t="n">
         <v>0.001061754802168117</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008777505040784674</v>
+        <v>0.0008777505040784686</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008777505040784674</v>
+        <v>0.0008777505040784685</v>
       </c>
       <c r="G7" t="n">
         <v>0.001061956228930574</v>
       </c>
       <c r="H7" t="n">
-        <v>0.001390339353549775</v>
+        <v>0.001390339353549776</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000877851026515958</v>
+        <v>0.0008778510265159589</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001115508867618196</v>
+        <v>0.001115508867618197</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0009132091760751305</v>
+        <v>0.0009132091760751309</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001771650223106995</v>
+        <v>0.001771650223106996</v>
       </c>
     </row>
     <row r="8">
@@ -5111,25 +5111,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001107212689752737</v>
+        <v>0.001107212689752735</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001113518452313253</v>
+        <v>0.001113518452313254</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001328619280022972</v>
+        <v>0.001328619280022971</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001072462515833129</v>
+        <v>0.00107246251583313</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009681465061251657</v>
+        <v>0.0009681465061251658</v>
       </c>
       <c r="G8" t="n">
         <v>0.001297676612214279</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001626059736833484</v>
+        <v>0.001626059736833485</v>
       </c>
       <c r="I8" t="n">
         <v>0.001113571409799663</v>
@@ -5138,10 +5138,10 @@
         <v>0.001351258759633388</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009959905635034412</v>
+        <v>0.0009959905635034405</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002164214716228716</v>
+        <v>0.002164214716228719</v>
       </c>
     </row>
     <row r="9">
@@ -5151,10 +5151,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001258979687133266</v>
+        <v>0.001258979687133265</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001222562331772346</v>
+        <v>0.001222562331772347</v>
       </c>
       <c r="D9" t="n">
         <v>0.001406427041048066</v>
@@ -5163,25 +5163,25 @@
         <v>0.001346413435015253</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001222562469441224</v>
+        <v>0.001222562469441225</v>
       </c>
       <c r="G9" t="n">
         <v>0.001406618910427626</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001735002035046828</v>
+        <v>0.001735002035046827</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001222513708013011</v>
+        <v>0.001222513708013012</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00146017154911525</v>
+        <v>0.001460171549115249</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001195687231812269</v>
+        <v>0.001195687231812268</v>
       </c>
       <c r="L9" t="n">
-        <v>0.002116312904604052</v>
+        <v>0.002116312904604053</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008118622111206691</v>
+        <v>0.0008118622111206693</v>
       </c>
       <c r="C2" t="n">
         <v>0.0009201713354569388</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008192610655129993</v>
+        <v>0.0008192610655129995</v>
       </c>
       <c r="E2" t="n">
         <v>0.0009523284555193418</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008261711522222978</v>
+        <v>0.0008261711522222981</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008183878586194525</v>
+        <v>0.0008183878586194527</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008401461350272102</v>
+        <v>0.0008401461350272104</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008045245544326208</v>
+        <v>0.0008045245544326212</v>
       </c>
       <c r="J2" t="n">
         <v>0.0009946745664093125</v>
       </c>
       <c r="K2" t="n">
-        <v>0.000954182100584842</v>
+        <v>0.0009541821005848422</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008769783442692357</v>
+        <v>0.0008769783442692366</v>
       </c>
     </row>
     <row r="3">
@@ -5310,10 +5310,10 @@
         <v>0.0008597597708565018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009987968525911601</v>
+        <v>0.0009987968525911606</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009123328401993659</v>
+        <v>0.000912332840199366</v>
       </c>
       <c r="E3" t="n">
         <v>0.001051518893477591</v>
@@ -5322,13 +5322,13 @@
         <v>0.0008432207823422734</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0009063294645801733</v>
+        <v>0.0009063294645801734</v>
       </c>
       <c r="H3" t="n">
-        <v>0.001063663333129732</v>
+        <v>0.001063663333129733</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008074754546423271</v>
+        <v>0.0008074754546423275</v>
       </c>
       <c r="J3" t="n">
         <v>0.001191237792244451</v>
@@ -5337,7 +5337,7 @@
         <v>0.001065363941664081</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001323907659104364</v>
+        <v>0.001323907659104365</v>
       </c>
     </row>
     <row r="4">
@@ -5347,34 +5347,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008674938961226255</v>
+        <v>0.0008674938961226253</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007726897089311892</v>
+        <v>0.0007726897089311886</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009510673601251701</v>
+        <v>0.0009510673601251703</v>
       </c>
       <c r="E4" t="n">
-        <v>0.000775416841569821</v>
+        <v>0.0007754168415698207</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000775416841569821</v>
+        <v>0.0007754168415698206</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009408227078983272</v>
+        <v>0.0009408227078983268</v>
       </c>
       <c r="H4" t="n">
         <v>0.001188015368714943</v>
       </c>
       <c r="I4" t="n">
-        <v>0.000782115274777114</v>
+        <v>0.0007821152747771139</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0009278305642639297</v>
+        <v>0.0009278305642639301</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008071669669256028</v>
+        <v>0.0008071669669256032</v>
       </c>
       <c r="L4" t="n">
         <v>0.001595111467626416</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003563330614436495</v>
+        <v>0.003563330614436496</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002138968498426323</v>
+        <v>0.002138968498426328</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004920758629004072</v>
+        <v>0.004920758629004077</v>
       </c>
       <c r="E5" t="n">
-        <v>0.002138968741179375</v>
+        <v>0.002138968741179377</v>
       </c>
       <c r="F5" t="n">
-        <v>0.002138968741179375</v>
+        <v>0.002138968741179377</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004864470550606161</v>
+        <v>0.004864470550606162</v>
       </c>
       <c r="H5" t="n">
-        <v>0.009996091732606141</v>
+        <v>0.009996091732606169</v>
       </c>
       <c r="I5" t="n">
-        <v>0.00213892564627243</v>
+        <v>0.002138925646272434</v>
       </c>
       <c r="J5" t="n">
         <v>0.004841078880747599</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002486395606260521</v>
+        <v>0.002486395606260514</v>
       </c>
       <c r="L5" t="n">
-        <v>0.006813442862113476</v>
+        <v>0.006813442862113463</v>
       </c>
     </row>
     <row r="6">
@@ -5430,13 +5430,13 @@
         <v>0.001007054267292327</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009163285463472761</v>
+        <v>0.0009163285463472763</v>
       </c>
       <c r="D6" t="n">
         <v>0.001093051586949555</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0009021938084968671</v>
+        <v>0.0009021938084968672</v>
       </c>
       <c r="F6" t="n">
         <v>0.0009210675354636097</v>
@@ -5445,19 +5445,19 @@
         <v>0.001080383079068028</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001461791763385957</v>
+        <v>0.001461791763385958</v>
       </c>
       <c r="I6" t="n">
         <v>0.001049150820653794</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001078116622847922</v>
+        <v>0.001078116622847923</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009443150986646379</v>
+        <v>0.0009443150986646378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.001738545462738909</v>
+        <v>0.001738545462738908</v>
       </c>
     </row>
     <row r="7">
@@ -5467,19 +5467,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009583574582032158</v>
+        <v>0.0009583574582032155</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008730216890115962</v>
+        <v>0.0008730216890115956</v>
       </c>
       <c r="D7" t="n">
         <v>0.001041922001250378</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008728507508748235</v>
+        <v>0.0008728507508748234</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008728507508748235</v>
+        <v>0.0008728507508748234</v>
       </c>
       <c r="G7" t="n">
         <v>0.001031686269978917</v>
@@ -5488,13 +5488,13 @@
         <v>0.001278878930795532</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008729788368577044</v>
+        <v>0.0008729788368577045</v>
       </c>
       <c r="J7" t="n">
         <v>0.00101869412634452</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008980305290061936</v>
+        <v>0.0008980305290061934</v>
       </c>
       <c r="L7" t="n">
         <v>0.001685975029707008</v>
@@ -5510,7 +5510,7 @@
         <v>0.001036290057647529</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001088291686469915</v>
+        <v>0.001088291686469914</v>
       </c>
       <c r="D8" t="n">
         <v>0.001285830469263262</v>
@@ -5519,7 +5519,7 @@
         <v>0.001050708184462174</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009552151027392989</v>
+        <v>0.0009552151027392988</v>
       </c>
       <c r="G8" t="n">
         <v>0.001247081951483936</v>
@@ -5528,16 +5528,16 @@
         <v>0.001494274612300569</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001088374518362724</v>
+        <v>0.001088374518362723</v>
       </c>
       <c r="J8" t="n">
         <v>0.001234116823261685</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009734096811293641</v>
+        <v>0.0009734096811293643</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002044962394880106</v>
+        <v>0.002044962394880105</v>
       </c>
     </row>
     <row r="9">
@@ -5550,10 +5550,10 @@
         <v>0.001149016348277347</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001154686871456982</v>
+        <v>0.001154686871456981</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001323596135692207</v>
+        <v>0.001323596135692208</v>
       </c>
       <c r="E9" t="n">
         <v>0.001259706316573065</v>
@@ -5562,22 +5562,22 @@
         <v>0.0011546869882507</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001313351452424302</v>
+        <v>0.001313351452424303</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001560544113240917</v>
+        <v>0.001560544113240918</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001154644019303089</v>
+        <v>0.00115464401930309</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001300359308789904</v>
+        <v>0.001300359308789905</v>
       </c>
       <c r="K9" t="n">
         <v>0.001126966321298275</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001967640212152389</v>
+        <v>0.00196764021215239</v>
       </c>
     </row>
   </sheetData>
@@ -5663,34 +5663,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008049108562669006</v>
+        <v>0.0008049108562669005</v>
       </c>
       <c r="C2" t="n">
         <v>0.0008972774148949569</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008106507155265244</v>
+        <v>0.0008106507155265252</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009197171740228668</v>
+        <v>0.0009197171740228666</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008237469354063073</v>
+        <v>0.0008237469354063074</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008106317171308903</v>
+        <v>0.0008106317171308909</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008227696826700789</v>
+        <v>0.0008227696826700791</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0008020880030829855</v>
+        <v>0.0008020880030829861</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009347743587399863</v>
+        <v>0.0009347743587399854</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009479185600269702</v>
+        <v>0.0009479185600269703</v>
       </c>
       <c r="L2" t="n">
         <v>0.0008644710465590122</v>
@@ -5703,34 +5703,34 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008408790835488014</v>
+        <v>0.0008408790835488016</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009782636529157573</v>
+        <v>0.0009782636529157575</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008815916619467955</v>
+        <v>0.0008815916619467962</v>
       </c>
       <c r="E3" t="n">
         <v>0.001014996044551077</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008565271749681288</v>
+        <v>0.0008565271749681282</v>
       </c>
       <c r="G3" t="n">
-        <v>0.000881683407614436</v>
+        <v>0.0008816834076144364</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0009701965995840243</v>
+        <v>0.0009701965995840242</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0008207612841660563</v>
+        <v>0.0008207612841660551</v>
       </c>
       <c r="J3" t="n">
         <v>0.001055404717724103</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001052012991811006</v>
+        <v>0.001052012991811007</v>
       </c>
       <c r="L3" t="n">
         <v>0.001265031391473118</v>
@@ -5743,22 +5743,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0008422583529563626</v>
+        <v>0.0008422583529563636</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0008003148293849535</v>
+        <v>0.0008003148293849534</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009070927037595337</v>
+        <v>0.0009070927037595342</v>
       </c>
       <c r="E4" t="n">
-        <v>0.00080293307917688</v>
+        <v>0.0008029330791768797</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0008029330791768801</v>
+        <v>0.0008029330791768797</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009065241199633432</v>
+        <v>0.0009065241199633436</v>
       </c>
       <c r="H4" t="n">
         <v>0.001046060611194429</v>
@@ -5767,13 +5767,13 @@
         <v>0.0008080626959221873</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008416049602648408</v>
+        <v>0.0008416049602648414</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007909672397275019</v>
+        <v>0.0007909672397275029</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001507739973783417</v>
+        <v>0.001507739973783418</v>
       </c>
     </row>
     <row r="5">
@@ -5783,13 +5783,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00308312692009406</v>
+        <v>0.003083126920094064</v>
       </c>
       <c r="C5" t="n">
-        <v>0.002531950961388523</v>
+        <v>0.002531950961388522</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004098675397331034</v>
+        <v>0.004098675397331033</v>
       </c>
       <c r="E5" t="n">
         <v>0.002531951165860385</v>
@@ -5798,22 +5798,22 @@
         <v>0.002531951165860385</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004212338178551274</v>
+        <v>0.004212338178551293</v>
       </c>
       <c r="H5" t="n">
-        <v>0.007065407705402081</v>
+        <v>0.007065407705402077</v>
       </c>
       <c r="I5" t="n">
-        <v>0.002531921912600154</v>
+        <v>0.002531921912600152</v>
       </c>
       <c r="J5" t="n">
         <v>0.003320065245145403</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002168880728911757</v>
+        <v>0.002168880728911763</v>
       </c>
       <c r="L5" t="n">
-        <v>0.004956211323771136</v>
+        <v>0.00495621132377116</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009820866852280074</v>
+        <v>0.0009820866852280048</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009444308726259618</v>
+        <v>0.0009444308726259614</v>
       </c>
       <c r="D6" t="n">
         <v>0.001048042507127328</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000930200499605345</v>
+        <v>0.0009302004996053451</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009477797591588134</v>
+        <v>0.0009477797591588138</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001171792472840739</v>
+        <v>0.001171792472840743</v>
       </c>
       <c r="H6" t="n">
         <v>0.001317620042728717</v>
       </c>
       <c r="I6" t="n">
-        <v>0.000947891028193833</v>
+        <v>0.0009478910281938307</v>
       </c>
       <c r="J6" t="n">
         <v>0.001108258965281306</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009289916904707424</v>
+        <v>0.0009289916904707429</v>
       </c>
       <c r="L6" t="n">
-        <v>0.00165176554686195</v>
+        <v>0.001651765546861951</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009314685392237507</v>
+        <v>0.0009314685392237508</v>
       </c>
       <c r="C7" t="n">
         <v>0.0008973019309779464</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009962939158953492</v>
+        <v>0.0009962939158953512</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008971337915983301</v>
+        <v>0.0008971337915983299</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00089713379159833</v>
+        <v>0.0008971337915983299</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009957343062307301</v>
+        <v>0.0009957343062307331</v>
       </c>
       <c r="H7" t="n">
         <v>0.001135270797461816</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008972728821895769</v>
+        <v>0.0008972728821895767</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009308151465322286</v>
+        <v>0.0009308151465322289</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008801774259948896</v>
+        <v>0.0008801774259948905</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001596950160050802</v>
+        <v>0.001596950160050803</v>
       </c>
     </row>
     <row r="8">
@@ -5906,7 +5906,7 @@
         <v>0.001007145819060263</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001107483194805722</v>
+        <v>0.001107483194805723</v>
       </c>
       <c r="D8" t="n">
         <v>0.001234523400550495</v>
@@ -5915,25 +5915,25 @@
         <v>0.001070674868925754</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009771518232365274</v>
+        <v>0.000977151823236527</v>
       </c>
       <c r="G8" t="n">
         <v>0.001206038954827589</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001345575446058697</v>
+        <v>0.001345575446058698</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001107577530786433</v>
+        <v>0.001107577530786432</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001141146253242979</v>
+        <v>0.00114114625324298</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009533539333406134</v>
+        <v>0.0009533539333406144</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001947884352655684</v>
+        <v>0.001947884352655685</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001092006967629683</v>
+        <v>0.001092006967629685</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001139906139168588</v>
+        <v>0.001139906139168589</v>
       </c>
       <c r="D9" t="n">
         <v>0.001238907141043484</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001234608439287886</v>
+        <v>0.001234608439287887</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001139906253350341</v>
+        <v>0.00113990625335034</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001238338514421373</v>
+        <v>0.001238338514421375</v>
       </c>
       <c r="H9" t="n">
         <v>0.00137787500565246</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001139877090380218</v>
+        <v>0.001139877090380219</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001173419354722872</v>
+        <v>0.001173419354722873</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001075232417093639</v>
+        <v>0.001075232417093641</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001839554368241448</v>
+        <v>0.001839554368241447</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007761842492108784</v>
+        <v>0.0007761842492108786</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008910747504161828</v>
+        <v>0.0008910747504161829</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007794404272031075</v>
+        <v>0.0007794404272031077</v>
       </c>
       <c r="E2" t="n">
         <v>0.0009214419917416661</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007994941768644828</v>
+        <v>0.0007994941768644829</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007807943870115982</v>
+        <v>0.0007807943870115981</v>
       </c>
       <c r="H2" t="n">
         <v>0.0007898002923994885</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007756247554492449</v>
+        <v>0.0007756247554492451</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009589441456548791</v>
+        <v>0.0009589441456548806</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009262342168979159</v>
+        <v>0.0009262342168979162</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007930346006130711</v>
+        <v>0.000793034600613071</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007617838548868913</v>
+        <v>0.0007617838548868908</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009486692969833048</v>
+        <v>0.0009486692969833049</v>
       </c>
       <c r="D3" t="n">
         <v>0.0007848064490363425</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009985803625043028</v>
+        <v>0.0009985803625043033</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000797230968050472</v>
+        <v>0.0007972309680504715</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007945466130629718</v>
+        <v>0.0007945466130629716</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0008598835264881492</v>
+        <v>0.0008598835264881494</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007578164105158168</v>
+        <v>0.0007578164105158164</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001126045970516743</v>
+        <v>0.001126045970516745</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001024135591017872</v>
+        <v>0.001024135591017873</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0008821404317392124</v>
+        <v>0.0008821404317392127</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000729878808336006</v>
+        <v>0.0007298788083360058</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007104699910547817</v>
+        <v>0.0007104699910547818</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007666588366741065</v>
+        <v>0.0007666588366741069</v>
       </c>
       <c r="E4" t="n">
         <v>0.0007133764867126172</v>
       </c>
       <c r="F4" t="n">
-        <v>0.000713376486712617</v>
+        <v>0.0007133764867126171</v>
       </c>
       <c r="G4" t="n">
         <v>0.0007816187959619916</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0008855385257467936</v>
+        <v>0.0008855385257467935</v>
       </c>
       <c r="I4" t="n">
         <v>0.0007213865335467837</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008584146526077681</v>
+        <v>0.0008584146526077683</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007603713726981371</v>
+        <v>0.0007603713726981372</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009192043200943904</v>
+        <v>0.0009192043200943905</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001542144058547292</v>
+        <v>0.001542144058547283</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001434786420866808</v>
+        <v>0.001434786420866809</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002116942054699265</v>
+        <v>0.002116942054699263</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001434786710191527</v>
+        <v>0.001434786710191526</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001434786710191527</v>
+        <v>0.001434786710191526</v>
       </c>
       <c r="G5" t="n">
-        <v>0.00244853829738277</v>
+        <v>0.002448538297382774</v>
       </c>
       <c r="H5" t="n">
-        <v>0.004435614047445923</v>
+        <v>0.004435614047445918</v>
       </c>
       <c r="I5" t="n">
         <v>0.001434766322655493</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004056882176401864</v>
+        <v>0.004056882176401866</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002038675026260256</v>
+        <v>0.002038675026260252</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005478875658944961</v>
+        <v>0.005478875658944956</v>
       </c>
     </row>
     <row r="6">
@@ -6219,34 +6219,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009873166149974063</v>
+        <v>0.0009873166149974041</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008570616329959493</v>
+        <v>0.0008570616329959505</v>
       </c>
       <c r="D6" t="n">
         <v>0.001026890062806341</v>
       </c>
       <c r="E6" t="n">
-        <v>0.000842601124192842</v>
+        <v>0.0008426011241928422</v>
       </c>
       <c r="F6" t="n">
         <v>0.0008601049693290353</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001039056602623392</v>
+        <v>0.001039056602623391</v>
       </c>
       <c r="H6" t="n">
         <v>0.001025453953195413</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009788243402081842</v>
+        <v>0.0009788243402081816</v>
       </c>
       <c r="J6" t="n">
-        <v>0.001118548714831797</v>
+        <v>0.001118548714831798</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008985886045440948</v>
+        <v>0.000898588604544095</v>
       </c>
       <c r="L6" t="n">
         <v>0.001059520160298302</v>
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008160960535636708</v>
+        <v>0.0008160960535636711</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008076238769857641</v>
+        <v>0.0008076238769857643</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0008528666842743046</v>
+        <v>0.0008528666842743051</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008074863123508909</v>
+        <v>0.0008074863123508913</v>
       </c>
       <c r="F7" t="n">
-        <v>0.000807486312350891</v>
+        <v>0.0008074863123508913</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008678360411896576</v>
+        <v>0.000867836041189658</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00097175577097446</v>
+        <v>0.0009717557709744603</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008076037787744492</v>
+        <v>0.0008076037787744493</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009446318978354335</v>
+        <v>0.0009446318978354343</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000846588617925802</v>
+        <v>0.0008465886179258027</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001005421565322055</v>
+        <v>0.001005421565322056</v>
       </c>
     </row>
     <row r="8">
@@ -6299,7 +6299,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008903274021480555</v>
+        <v>0.0008903274021480556</v>
       </c>
       <c r="C8" t="n">
         <v>0.001013899436492834</v>
@@ -6311,25 +6311,25 @@
         <v>0.0009777686984334766</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008859674677982514</v>
+        <v>0.0008859674677982518</v>
       </c>
       <c r="G8" t="n">
         <v>0.001074205792481378</v>
       </c>
       <c r="H8" t="n">
-        <v>0.00117812552226618</v>
+        <v>0.001178125522266181</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001013973530066171</v>
+        <v>0.00101397353006617</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001151027618091777</v>
+        <v>0.001151027618091779</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009183654278411937</v>
+        <v>0.0009183654278411934</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001349820927459084</v>
+        <v>0.001349820927459086</v>
       </c>
     </row>
     <row r="9">
@@ -6339,7 +6339,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009956805924671956</v>
+        <v>0.0009956805924671952</v>
       </c>
       <c r="C9" t="n">
         <v>0.001073858046065492</v>
@@ -6348,19 +6348,19 @@
         <v>0.001119110290266155</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001173850136259886</v>
+        <v>0.001173850136259885</v>
       </c>
       <c r="F9" t="n">
         <v>0.001073858278912095</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001134070210269384</v>
+        <v>0.001134070210269385</v>
       </c>
       <c r="H9" t="n">
         <v>0.001237989940054187</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001073837947854177</v>
+        <v>0.001073837947854176</v>
       </c>
       <c r="J9" t="n">
         <v>0.001210866066915161</v>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007710133796579636</v>
+        <v>0.0007710133796579631</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008890473727665362</v>
+        <v>0.000889047372766536</v>
       </c>
       <c r="D2" t="n">
-        <v>0.000771999212378602</v>
+        <v>0.0007719992123786017</v>
       </c>
       <c r="E2" t="n">
-        <v>0.000919875386640291</v>
+        <v>0.0009198753866402907</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007970032386190632</v>
+        <v>0.0007970032386190629</v>
       </c>
       <c r="G2" t="n">
         <v>0.0007735695625247413</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007699721906623126</v>
+        <v>0.0007699721906623123</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007728733626150386</v>
+        <v>0.0007728733626150381</v>
       </c>
       <c r="J2" t="n">
         <v>0.0009514141886859524</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009219111515385043</v>
+        <v>0.0009219111515385038</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007687115005760672</v>
+        <v>0.0007687115005760668</v>
       </c>
     </row>
     <row r="3">
@@ -6495,31 +6495,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007528382139408724</v>
+        <v>0.0007528382139408721</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009579960074230395</v>
+        <v>0.0009579960074230393</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007597567864754885</v>
+        <v>0.000759756786475488</v>
       </c>
       <c r="E3" t="n">
-        <v>0.001008715455421559</v>
+        <v>0.00100871545542156</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000805840223173519</v>
+        <v>0.0008058402231735187</v>
       </c>
       <c r="G3" t="n">
         <v>0.0007709546200619675</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007472947651477517</v>
+        <v>0.0007472947651477513</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007659954607696906</v>
+        <v>0.0007659954607696903</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0010920279812489</v>
+        <v>0.001092027981248899</v>
       </c>
       <c r="K3" t="n">
         <v>0.001020117905003368</v>
@@ -6535,34 +6535,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007164810135788041</v>
+        <v>0.0007164810135788042</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007279624127913858</v>
+        <v>0.0007279624127913857</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0007276164476638673</v>
+        <v>0.0007276164476638674</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007304692329726685</v>
+        <v>0.000730469232972668</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007304692329726685</v>
+        <v>0.000730469232972668</v>
       </c>
       <c r="G4" t="n">
-        <v>0.00074506634908182</v>
+        <v>0.0007450663490818193</v>
       </c>
       <c r="H4" t="n">
         <v>0.0007080070590934116</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007356236510647708</v>
+        <v>0.0007356236510647706</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008019628233139403</v>
+        <v>0.0008019628233139405</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007543649476596339</v>
+        <v>0.0007543649476596341</v>
       </c>
       <c r="L4" t="n">
         <v>0.0006921106905106379</v>
@@ -6575,22 +6575,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.00134755536698899</v>
+        <v>0.001347555366988991</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001656368084883495</v>
+        <v>0.001656368084883494</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001483682590017369</v>
+        <v>0.001483682590017367</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001656368310251658</v>
+        <v>0.001656368310251656</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001656368310251658</v>
+        <v>0.001656368310251656</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001792021347988922</v>
+        <v>0.001792021347988913</v>
       </c>
       <c r="H5" t="n">
         <v>0.001250439713793767</v>
@@ -6599,10 +6599,10 @@
         <v>0.001656359561076433</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002800087987075722</v>
+        <v>0.002800087987075719</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001911112576618846</v>
+        <v>0.001911112576618847</v>
       </c>
       <c r="L5" t="n">
         <v>0.001386087491829733</v>
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009563945512613733</v>
+        <v>0.0009563945512613735</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008666589807745534</v>
+        <v>0.0008666589807745511</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008603522150580887</v>
+        <v>0.0008603522150580886</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008528158056921964</v>
+        <v>0.0008528158056921962</v>
       </c>
       <c r="F6" t="n">
-        <v>0.000868275415126146</v>
+        <v>0.0008682754151261455</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0009849798867643876</v>
+        <v>0.000984979886764388</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009531522928008321</v>
+        <v>0.0009531522928008319</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009755371887473402</v>
+        <v>0.00097553718874734</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009446540341064929</v>
+        <v>0.000944654034106493</v>
       </c>
       <c r="K6" t="n">
         <v>0.0008877376893729203</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008241859356270649</v>
+        <v>0.0008241859356270646</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007944682928648023</v>
+        <v>0.0007944682928648021</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008136194541578315</v>
+        <v>0.000813619454157831</v>
       </c>
       <c r="D7" t="n">
-        <v>0.00080559488108854</v>
+        <v>0.0008055948810885396</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008135001358303451</v>
+        <v>0.0008135001358303445</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008135001358303451</v>
+        <v>0.0008135001358303445</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0008230536283678184</v>
+        <v>0.0008230536283678171</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007859943383794095</v>
+        <v>0.0007859943383794093</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008136109303507687</v>
+        <v>0.0008136109303507686</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008799501025999381</v>
+        <v>0.0008799501025999379</v>
       </c>
       <c r="K7" t="n">
-        <v>0.000832352226945632</v>
+        <v>0.0008323522269456318</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0007700979697966358</v>
+        <v>0.0007700979697966354</v>
       </c>
     </row>
     <row r="8">
@@ -6695,34 +6695,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008607153547149951</v>
+        <v>0.0008607153547149948</v>
       </c>
       <c r="C8" t="n">
         <v>0.000998979487023995</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001015759167555025</v>
+        <v>0.001015759167555024</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009663878356031781</v>
+        <v>0.0009663878356031774</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008835789370674227</v>
+        <v>0.0008835789370674225</v>
       </c>
       <c r="G8" t="n">
         <v>0.001008493635334316</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009714343453458905</v>
+        <v>0.0009714343453458904</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0009990509373172677</v>
+        <v>0.0009990509373172672</v>
       </c>
       <c r="J8" t="n">
         <v>0.001065413534380515</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008963852186476234</v>
+        <v>0.0008963852186476236</v>
       </c>
       <c r="L8" t="n">
         <v>0.001080044974675511</v>
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009347589371369291</v>
+        <v>0.000934758937136928</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001026266321316025</v>
+        <v>0.001026266321316023</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001018250653201916</v>
+        <v>0.001018250653201915</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001109764136897734</v>
+        <v>0.001109764136897733</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001026266538510413</v>
+        <v>0.001026266538510412</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001035700495526011</v>
+        <v>0.001035700495526009</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009986412055376028</v>
+        <v>0.0009986412055376015</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001026257797508962</v>
+        <v>0.001026257797508961</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001092596969758132</v>
+        <v>0.001092596969758131</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001003075639253606</v>
+        <v>0.001003075639253605</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009827448369548295</v>
+        <v>0.0009827448369548282</v>
       </c>
     </row>
   </sheetData>
@@ -6854,34 +6854,34 @@
         <v>0.0007717301520037091</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0008669456563126382</v>
+        <v>0.0008669456563126381</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0007692918783354842</v>
+        <v>0.0007692918783354844</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0008883967074404416</v>
+        <v>0.0008883967074404411</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0007948855531401528</v>
+        <v>0.0007948855531401515</v>
       </c>
       <c r="G2" t="n">
         <v>0.0007715802839112415</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007683316120356576</v>
+        <v>0.0007683316120356575</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007721639549400951</v>
+        <v>0.0007721639549400949</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009013261827591769</v>
+        <v>0.0009013261827591762</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009191882196292881</v>
+        <v>0.0009191882196292879</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0007682960033553144</v>
+        <v>0.0007682960033553142</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0007664626472659432</v>
+        <v>0.0007664626472659423</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009261958459465796</v>
+        <v>0.0009261958459465797</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0007491296361926624</v>
+        <v>0.0007491296361926623</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0009614507148512476</v>
+        <v>0.000961450714851247</v>
       </c>
       <c r="F3" t="n">
         <v>0.0008070411170810138</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0007654106149605221</v>
+        <v>0.0007654106149605214</v>
       </c>
       <c r="H3" t="n">
-        <v>0.000744154427127074</v>
+        <v>0.0007441544271270743</v>
       </c>
       <c r="I3" t="n">
         <v>0.0007695208102491498</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0009987849512452947</v>
+        <v>0.0009987849512452949</v>
       </c>
       <c r="K3" t="n">
         <v>0.001011838753183106</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0007429241567370121</v>
+        <v>0.0007429241567370119</v>
       </c>
     </row>
     <row r="4">
@@ -6931,10 +6931,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007395168270678603</v>
+        <v>0.00073951682706786</v>
       </c>
       <c r="C4" t="n">
-        <v>0.000736070916930446</v>
+        <v>0.0007360709169304461</v>
       </c>
       <c r="D4" t="n">
         <v>0.0007119754043239546</v>
@@ -6946,22 +6946,22 @@
         <v>0.0007385023345927398</v>
       </c>
       <c r="G4" t="n">
-        <v>0.000737533611397625</v>
+        <v>0.0007375336113976249</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007043224844559767</v>
+        <v>0.0007043224844559766</v>
       </c>
       <c r="I4" t="n">
-        <v>0.00074253468865646</v>
+        <v>0.0007425346886564598</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0007772754602034258</v>
+        <v>0.0007772754602034256</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007438214313091635</v>
+        <v>0.000743821431309163</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0007020624855210065</v>
+        <v>0.0007020624855210061</v>
       </c>
     </row>
     <row r="5">
@@ -6971,13 +6971,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001713608409417528</v>
+        <v>0.001713608409417527</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001778750172406407</v>
+        <v>0.001778750172406408</v>
       </c>
       <c r="D5" t="n">
-        <v>0.001262286498140819</v>
+        <v>0.001262286498140816</v>
       </c>
       <c r="E5" t="n">
         <v>0.001778750362973598</v>
@@ -6986,19 +6986,19 @@
         <v>0.001778750362973598</v>
       </c>
       <c r="G5" t="n">
-        <v>0.001692489876604936</v>
+        <v>0.001692489876604944</v>
       </c>
       <c r="H5" t="n">
-        <v>0.001201059878447698</v>
+        <v>0.001201059878447697</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001778744918322874</v>
+        <v>0.001778744918322875</v>
       </c>
       <c r="J5" t="n">
-        <v>0.002412743758052274</v>
+        <v>0.002412743758052277</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001726914014677138</v>
+        <v>0.001726914014677139</v>
       </c>
       <c r="L5" t="n">
         <v>0.001531397301590063</v>
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0008736252914156551</v>
+        <v>0.0008736252914156549</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008750545927311171</v>
+        <v>0.0008750545927311176</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0008446365458388201</v>
+        <v>0.0008446365458388197</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008610921407206071</v>
+        <v>0.0008610921407206078</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0008762911612156539</v>
+        <v>0.000876291161215654</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008716420757454201</v>
+        <v>0.0008716420757454196</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0009506330805177565</v>
+        <v>0.0009506330805177566</v>
       </c>
       <c r="I6" t="n">
         <v>0.0008766431530042549</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0009208458733581433</v>
+        <v>0.0009208458733581431</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008782893338058654</v>
+        <v>0.0008782893338058643</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0008358100517965644</v>
+        <v>0.000835810051796564</v>
       </c>
     </row>
     <row r="7">
@@ -7051,7 +7051,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0008171871887928409</v>
+        <v>0.0008171871887928407</v>
       </c>
       <c r="C7" t="n">
         <v>0.0008202103044649757</v>
@@ -7060,28 +7060,28 @@
         <v>0.0007896368784250439</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008200891578405414</v>
+        <v>0.000820089157840541</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008200891578405414</v>
+        <v>0.000820089157840541</v>
       </c>
       <c r="G7" t="n">
-        <v>0.000815203973122606</v>
+        <v>0.0008152039731226062</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007819928461809574</v>
+        <v>0.0007819928461809572</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008202050503814408</v>
+        <v>0.0008202050503814404</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008549458219284063</v>
+        <v>0.0008549458219284062</v>
       </c>
       <c r="K7" t="n">
         <v>0.0008214917930341438</v>
       </c>
       <c r="L7" t="n">
-        <v>0.000779732847245987</v>
+        <v>0.0007797328472459867</v>
       </c>
     </row>
     <row r="8">
@@ -7091,34 +7091,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.0008828910455298966</v>
+        <v>0.0008828910455298959</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001004429592626965</v>
+        <v>0.001004429592626964</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0009985386172220116</v>
+        <v>0.0009985386172220111</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009720009649195559</v>
+        <v>0.0009720009649195565</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008896066154414577</v>
+        <v>0.0008896066154414578</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0009995049407626104</v>
+        <v>0.0009995049407626098</v>
       </c>
       <c r="H8" t="n">
-        <v>0.0009662938138209416</v>
+        <v>0.0009662938138209419</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001004506018021446</v>
+        <v>0.001004506018021444</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001039270097284766</v>
+        <v>0.001039270097284765</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008849926475493433</v>
+        <v>0.0008849926475493428</v>
       </c>
       <c r="L8" t="n">
         <v>0.001087918414140395</v>
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.0009381397839871859</v>
+        <v>0.0009381397839871863</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001008061979081529</v>
+        <v>0.001008061979081528</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0009774974947477687</v>
+        <v>0.0009774974947477691</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001085262328826908</v>
+        <v>0.001085262328826909</v>
       </c>
       <c r="F9" t="n">
-        <v>0.001008062162548674</v>
+        <v>0.001008062162548673</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001003055647739159</v>
+        <v>0.00100305564773916</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0009698445207975109</v>
+        <v>0.000969844520797511</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001008056724997995</v>
+        <v>0.001008056724997994</v>
       </c>
       <c r="J9" t="n">
-        <v>0.00104279749654496</v>
+        <v>0.001042797496544959</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0009690092931328477</v>
+        <v>0.0009690092931328483</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0009675845218625402</v>
+        <v>0.0009675845218625416</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008055104239159719</v>
+        <v>0.0008055104239159715</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0009138556707151808</v>
+        <v>0.00091385567071518</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0008153325878363297</v>
+        <v>0.0008153325878363293</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009449062255669975</v>
+        <v>0.0009449062255669964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008213324346602316</v>
+        <v>0.000821332434660231</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0008134974971275065</v>
+        <v>0.0008134974971275061</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008442399454558416</v>
+        <v>0.0008442399454558415</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007991775663557954</v>
+        <v>0.0007991775663557948</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009846487548265661</v>
+        <v>0.0009846487548265657</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0009503177247281129</v>
+        <v>0.0009503177247281138</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0008682154652122363</v>
+        <v>0.0008682154652122361</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0008371409591139935</v>
+        <v>0.0008371409591139932</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009818605183154793</v>
+        <v>0.0009818605183154808</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0009068381963821116</v>
+        <v>0.0009068381963821122</v>
       </c>
       <c r="E3" t="n">
         <v>0.001032763456796494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0008287300005795778</v>
+        <v>0.0008287300005795788</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0008940764782934031</v>
+        <v>0.0008940764782934036</v>
       </c>
       <c r="H3" t="n">
         <v>0.001113474953060914</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007921458748424082</v>
+        <v>0.0007921458748424078</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001167640478365753</v>
+        <v>0.001167640478365752</v>
       </c>
       <c r="K3" t="n">
-        <v>0.001061487876237522</v>
+        <v>0.00106148787623752</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001283955025156622</v>
+        <v>0.001283955025156623</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.000836482803195431</v>
+        <v>0.0008364828031954309</v>
       </c>
       <c r="C4" t="n">
         <v>0.0007502161585543789</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009474286630945132</v>
+        <v>0.0009474286630945133</v>
       </c>
       <c r="E4" t="n">
-        <v>0.0007532639289870737</v>
+        <v>0.0007532639289870739</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0007532639289870737</v>
+        <v>0.0007532639289870739</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0009263014008381061</v>
+        <v>0.0009263014008381071</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00127375586885205</v>
+        <v>0.001273755868852051</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007623367827040534</v>
+        <v>0.0007623367827040535</v>
       </c>
       <c r="J4" t="n">
         <v>0.0009072586934166819</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008060060496788816</v>
+        <v>0.0008060060496788818</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001537423952037334</v>
+        <v>0.001537423952037333</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.003159874146008562</v>
+        <v>0.003159874146008559</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001917581810824942</v>
+        <v>0.001917581810824935</v>
       </c>
       <c r="D5" t="n">
-        <v>0.00503292218037758</v>
+        <v>0.00503292218037759</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001917582109464496</v>
+        <v>0.00191758210946449</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001917582109464496</v>
+        <v>0.00191758210946449</v>
       </c>
       <c r="G5" t="n">
-        <v>0.004827138647049191</v>
+        <v>0.004827138647049195</v>
       </c>
       <c r="H5" t="n">
         <v>0.011441834658398</v>
       </c>
       <c r="I5" t="n">
-        <v>0.001917537851525965</v>
+        <v>0.001917537851525961</v>
       </c>
       <c r="J5" t="n">
-        <v>0.004732819320972569</v>
+        <v>0.004732819320972567</v>
       </c>
       <c r="K5" t="n">
-        <v>0.002649778653941016</v>
+        <v>0.002649778653941017</v>
       </c>
       <c r="L5" t="n">
-        <v>0.005042197372738456</v>
+        <v>0.005042197372738482</v>
       </c>
     </row>
     <row r="6">
@@ -7407,34 +7407,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009809695945136386</v>
+        <v>0.0009809695945136388</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0009006669451188429</v>
+        <v>0.0009006669451188414</v>
       </c>
       <c r="D6" t="n">
-        <v>0.001094872538058705</v>
+        <v>0.001094872538058707</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008860059432145254</v>
+        <v>0.0008860059432145269</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0009060077365437104</v>
+        <v>0.0009060077365437107</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001204292141848629</v>
+        <v>0.00120429214184863</v>
       </c>
       <c r="H6" t="n">
-        <v>0.00156139486514256</v>
+        <v>0.001561394865142561</v>
       </c>
       <c r="I6" t="n">
-        <v>0.001040327523714576</v>
+        <v>0.001040327523714577</v>
       </c>
       <c r="J6" t="n">
         <v>0.001188348393610618</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0009473151307542099</v>
+        <v>0.0009473151307542124</v>
       </c>
       <c r="L6" t="n">
         <v>0.001686358116443581</v>
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0009321394627656589</v>
+        <v>0.0009321394627656597</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008580374015732616</v>
+        <v>0.0008580374015732619</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001043075833538867</v>
+        <v>0.001043075833538868</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008578839229368916</v>
+        <v>0.0008578839229368919</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008578839229368916</v>
+        <v>0.0008578839229368919</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001021958060408334</v>
+        <v>0.001021958060408335</v>
       </c>
       <c r="H7" t="n">
-        <v>0.00136941252842228</v>
+        <v>0.001369412528422281</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0008579934422742818</v>
+        <v>0.0008579934422742819</v>
       </c>
       <c r="J7" t="n">
-        <v>0.001002915352986909</v>
+        <v>0.00100291535298691</v>
       </c>
       <c r="K7" t="n">
-        <v>0.00090166270924911</v>
+        <v>0.0009016627092491103</v>
       </c>
       <c r="L7" t="n">
-        <v>0.001633080611607565</v>
+        <v>0.001633080611607566</v>
       </c>
     </row>
     <row r="8">
@@ -7487,7 +7487,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001014833558482079</v>
+        <v>0.00101483355848208</v>
       </c>
       <c r="C8" t="n">
         <v>0.001086051870408482</v>
@@ -7496,28 +7496,28 @@
         <v>0.001301361751378207</v>
       </c>
       <c r="E8" t="n">
-        <v>0.00104628812859464</v>
+        <v>0.001046288128594641</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0009452555349541006</v>
+        <v>0.0009452555349541004</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001250079236614423</v>
+        <v>0.001250079236614424</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001597533704628382</v>
+        <v>0.001597533704628383</v>
       </c>
       <c r="I8" t="n">
         <v>0.001086114618480371</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001231065109759102</v>
+        <v>0.001231065109759103</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0009816554222847576</v>
+        <v>0.0009816554222847585</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002013112533779579</v>
+        <v>0.00201311253377958</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.001158115105956633</v>
+        <v>0.001158115105956634</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001186935930468869</v>
+        <v>0.001186935930468871</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001371983859315358</v>
+        <v>0.001371983859315359</v>
       </c>
       <c r="E9" t="n">
-        <v>0.001305706867774248</v>
+        <v>0.001305706867774249</v>
       </c>
       <c r="F9" t="n">
         <v>0.001186936072204083</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001350856589303943</v>
+        <v>0.001350856589303944</v>
       </c>
       <c r="H9" t="n">
-        <v>0.001698311057317889</v>
+        <v>0.00169831105731789</v>
       </c>
       <c r="I9" t="n">
-        <v>0.001186891971169889</v>
+        <v>0.00118689197116989</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001331813881882516</v>
+        <v>0.001331813881882518</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001170927317219966</v>
+        <v>0.001170927317219967</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00196197914050317</v>
+        <v>0.001961979140503172</v>
       </c>
     </row>
   </sheetData>
@@ -7643,7 +7643,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0007803510834247427</v>
+        <v>0.0007803510834247424</v>
       </c>
       <c r="C2" t="n">
         <v>0.0008975941439555896</v>
@@ -7652,22 +7652,22 @@
         <v>0.0007985297413124692</v>
       </c>
       <c r="E2" t="n">
-        <v>0.0009289592380447034</v>
+        <v>0.0009289592380447038</v>
       </c>
       <c r="F2" t="n">
-        <v>0.0008047797144919469</v>
+        <v>0.000804779714491947</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0007910606069911626</v>
+        <v>0.0007910606069911625</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0007850072361080226</v>
+        <v>0.0007850072361080225</v>
       </c>
       <c r="I2" t="n">
-        <v>0.0007827571895355289</v>
+        <v>0.000782757189535529</v>
       </c>
       <c r="J2" t="n">
-        <v>0.0009647748131973147</v>
+        <v>0.0009647748131973151</v>
       </c>
       <c r="K2" t="n">
         <v>0.0009276898732656048</v>
@@ -7686,34 +7686,34 @@
         <v>0.000751469237628819</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0009584279420991814</v>
+        <v>0.0009584279420991817</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0008802680469604512</v>
+        <v>0.0008802680469604513</v>
       </c>
       <c r="E3" t="n">
         <v>0.001009944070861502</v>
       </c>
       <c r="F3" t="n">
-        <v>0.000804910720446333</v>
+        <v>0.0008049107204463332</v>
       </c>
       <c r="G3" t="n">
-        <v>0.00082754916440325</v>
+        <v>0.0008275491644032503</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007869063773122055</v>
+        <v>0.0007869063773122059</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0007685446462941628</v>
+        <v>0.0007685446462941631</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001114799862369511</v>
+        <v>0.001114799862369512</v>
       </c>
       <c r="K3" t="n">
         <v>0.001007604827370836</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001057900461152102</v>
+        <v>0.001057900461152103</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0007057118850428177</v>
+        <v>0.0007057118850428178</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0007220113386568844</v>
+        <v>0.0007220113386568846</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009110481884804841</v>
+        <v>0.0009110481884804837</v>
       </c>
       <c r="E4" t="n">
+        <v>0.0007246181381831535</v>
+      </c>
+      <c r="F4" t="n">
         <v>0.0007246181381831534</v>
       </c>
-      <c r="F4" t="n">
-        <v>0.0007246181381831533</v>
-      </c>
       <c r="G4" t="n">
-        <v>0.0008263406444391833</v>
+        <v>0.000826340644439183</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0007623274190611353</v>
+        <v>0.0007623274190611358</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0007306700845769884</v>
+        <v>0.0007306700845769883</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0008268485207697573</v>
+        <v>0.0008268485207697579</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0007325729725084055</v>
+        <v>0.0007325729725084061</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001187987049943681</v>
+        <v>0.00118798704994368</v>
       </c>
     </row>
     <row r="5">
@@ -7763,22 +7763,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.001082103815442198</v>
+        <v>0.001082103815442197</v>
       </c>
       <c r="C5" t="n">
-        <v>0.001510286608102666</v>
+        <v>0.001510286608102667</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004225036926179699</v>
+        <v>0.004225036926179698</v>
       </c>
       <c r="E5" t="n">
-        <v>0.001510286841441467</v>
+        <v>0.001510286841441468</v>
       </c>
       <c r="F5" t="n">
-        <v>0.001510286841441467</v>
+        <v>0.001510286841441468</v>
       </c>
       <c r="G5" t="n">
-        <v>0.003037601245582744</v>
+        <v>0.003037601245582736</v>
       </c>
       <c r="H5" t="n">
         <v>0.002094135222527935</v>
@@ -7787,13 +7787,13 @@
         <v>0.001510258307908604</v>
       </c>
       <c r="J5" t="n">
-        <v>0.003259687157191946</v>
+        <v>0.003259687157191948</v>
       </c>
       <c r="K5" t="n">
-        <v>0.001494547996855272</v>
+        <v>0.001494547996855273</v>
       </c>
       <c r="L5" t="n">
-        <v>0.01030901267226446</v>
+        <v>0.01030901267226444</v>
       </c>
     </row>
     <row r="6">
@@ -7803,34 +7803,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0009562763119689827</v>
+        <v>0.000956276311968983</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0008614655624559291</v>
+        <v>0.0008614655624559276</v>
       </c>
       <c r="D6" t="n">
         <v>0.001049777621127212</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0008475708219457137</v>
+        <v>0.0008475708219457139</v>
       </c>
       <c r="F6" t="n">
         <v>0.0008648074502879161</v>
       </c>
       <c r="G6" t="n">
-        <v>0.001076905071365349</v>
+        <v>0.001076905071365348</v>
       </c>
       <c r="H6" t="n">
-        <v>0.001018669412259497</v>
+        <v>0.001018669412259498</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0009812345115031531</v>
+        <v>0.0009812345115031533</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000971545480361263</v>
+        <v>0.0009715454803612631</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0008653905560013855</v>
+        <v>0.0008653905560013853</v>
       </c>
       <c r="L6" t="n">
         <v>0.001324502099317804</v>
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0007884552277882468</v>
+        <v>0.0007884552277882466</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0008134417275164788</v>
+        <v>0.0008134417275164792</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0009937826852335328</v>
+        <v>0.0009937826852335326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0008132970091295709</v>
+        <v>0.0008132970091295717</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0008132970091295709</v>
+        <v>0.0008132970091295717</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0009090839871846121</v>
+        <v>0.0009090839871846116</v>
       </c>
       <c r="H7" t="n">
-        <v>0.000845070761806564</v>
+        <v>0.0008450707618065642</v>
       </c>
       <c r="I7" t="n">
-        <v>0.000813413427322417</v>
+        <v>0.0008134134273224172</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0009095918635151866</v>
+        <v>0.0009095918635151867</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0008153163152538345</v>
+        <v>0.0008153163152538342</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00127073039268911</v>
+        <v>0.001270730392689109</v>
       </c>
     </row>
     <row r="8">
@@ -7883,34 +7883,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.000859768670996019</v>
+        <v>0.0008597686709960195</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001011144998459469</v>
+        <v>0.001011144998459471</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00121782671989635</v>
+        <v>0.001217826719896351</v>
       </c>
       <c r="E8" t="n">
-        <v>0.0009765593780346492</v>
+        <v>0.0009765593780346501</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0008886838326215151</v>
+        <v>0.0008886838326215158</v>
       </c>
       <c r="G8" t="n">
-        <v>0.001106890097341277</v>
+        <v>0.001106890097341278</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001042876871963215</v>
+        <v>0.001042876871963216</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001011219537479081</v>
+        <v>0.001011219537479083</v>
       </c>
       <c r="J8" t="n">
-        <v>0.001107422833087674</v>
+        <v>0.001107422833087675</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0008842800922329685</v>
+        <v>0.0008842800922329691</v>
       </c>
       <c r="L8" t="n">
         <v>0.001600668670602606</v>
@@ -7926,10 +7926,10 @@
         <v>0.0009493496799460113</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001054166563283225</v>
+        <v>0.001054166563283224</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001234516449443565</v>
+        <v>0.001234516449443564</v>
       </c>
       <c r="E9" t="n">
         <v>0.001146289406984112</v>
@@ -7941,19 +7941,19 @@
         <v>0.001149808822951357</v>
       </c>
       <c r="H9" t="n">
-        <v>0.00108579559757331</v>
+        <v>0.001085795597573309</v>
       </c>
       <c r="I9" t="n">
         <v>0.001054138263089162</v>
       </c>
       <c r="J9" t="n">
-        <v>0.001150316699281932</v>
+        <v>0.001150316699281931</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001009787147918096</v>
+        <v>0.001009787147918094</v>
       </c>
       <c r="L9" t="n">
-        <v>0.001511455228455855</v>
+        <v>0.001511455228455854</v>
       </c>
     </row>
   </sheetData>
